--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet name="Priorização" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Resumo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Como revisar" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revisões" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Como revisar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$K$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$M$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revisões'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,12 +51,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001D5FCC"/>
+      <color rgb="00B97A10"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00B97A10"/>
+      <color rgb="001D5FCC"/>
       <sz val="10"/>
     </font>
     <font>
@@ -137,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -163,11 +165,11 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -176,6 +178,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -550,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K193"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -559,11 +570,13 @@
     <col width="58" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -599,25 +612,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Faixa proposta</t>
+          <t>Faixa atual</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Faixa anterior</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Revisto por</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Prioridade</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Faixa revisada</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Concorda?</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Comentário do revisor</t>
         </is>
@@ -658,9 +681,11 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr"/>
-      <c r="K2" s="7" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr"/>
+      <c r="L2" s="6" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -697,9 +722,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr"/>
-      <c r="K3" s="7" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -736,9 +763,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr"/>
-      <c r="K4" s="7" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -775,9 +804,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -814,9 +845,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="7" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -853,9 +886,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -892,9 +927,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="7" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -931,9 +968,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -970,9 +1009,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr"/>
-      <c r="K10" s="7" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1009,9 +1050,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="7" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1048,9 +1091,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="7" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1087,9 +1132,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1126,9 +1173,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="7" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1159,15 +1208,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1204,9 +1263,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="7" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1243,9 +1304,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="7" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1282,9 +1345,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="7" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1321,9 +1386,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="7" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1360,9 +1427,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="7" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1399,9 +1468,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="7" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1438,9 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="6" t="inlineStr"/>
-      <c r="K22" s="7" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1477,9 +1550,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="6" t="inlineStr"/>
-      <c r="K23" s="7" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1510,15 +1585,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="6" t="inlineStr"/>
-      <c r="K24" s="7" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1549,15 +1626,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="7" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1594,9 +1673,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="7" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1627,15 +1708,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="7" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1672,9 +1755,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="6" t="inlineStr"/>
-      <c r="J28" s="6" t="inlineStr"/>
-      <c r="K28" s="7" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1711,9 +1796,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="6" t="inlineStr"/>
-      <c r="K29" s="7" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1750,9 +1837,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="6" t="inlineStr"/>
-      <c r="K30" s="7" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -1789,9 +1878,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="7" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1822,15 +1913,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="7" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -1861,15 +1962,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="7" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -1900,15 +2003,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="6" t="inlineStr"/>
-      <c r="K34" s="7" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -1945,9 +2050,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="6" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -1984,9 +2091,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="6" t="inlineStr"/>
-      <c r="K36" s="7" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -2017,15 +2126,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="6" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -2056,15 +2167,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="6" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -2095,15 +2208,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="6" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr"/>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -2140,9 +2263,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="6" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -2179,9 +2304,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="6" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -2218,9 +2345,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="6" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -2257,9 +2386,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="6" t="inlineStr"/>
-      <c r="K43" s="7" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -2296,9 +2427,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="6" t="inlineStr"/>
-      <c r="K44" s="7" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -2335,9 +2468,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="6" t="inlineStr"/>
-      <c r="K45" s="7" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -2368,15 +2503,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="6" t="inlineStr"/>
-      <c r="K46" s="7" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -2413,9 +2558,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="6" t="inlineStr"/>
-      <c r="K47" s="7" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
+      <c r="L47" s="6" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -2446,15 +2593,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="6" t="inlineStr"/>
-      <c r="K48" s="7" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -2485,15 +2634,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="6" t="inlineStr"/>
-      <c r="K49" s="7" t="inlineStr"/>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr"/>
+      <c r="L49" s="6" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -2530,9 +2689,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr"/>
-      <c r="J50" s="6" t="inlineStr"/>
-      <c r="K50" s="7" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr"/>
+      <c r="L50" s="6" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -2569,9 +2730,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="6" t="inlineStr"/>
-      <c r="J51" s="6" t="inlineStr"/>
-      <c r="K51" s="7" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
+      <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -2608,9 +2771,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="6" t="inlineStr"/>
-      <c r="K52" s="7" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
+      <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -2647,9 +2812,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="6" t="inlineStr"/>
-      <c r="K53" s="7" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -2686,9 +2853,11 @@
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="6" t="inlineStr"/>
-      <c r="K54" s="7" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr"/>
+      <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -2725,9 +2894,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="6" t="inlineStr"/>
-      <c r="J55" s="6" t="inlineStr"/>
-      <c r="K55" s="7" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
+      <c r="L55" s="6" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -2764,9 +2935,11 @@
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="6" t="inlineStr"/>
-      <c r="J56" s="6" t="inlineStr"/>
-      <c r="K56" s="7" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr"/>
+      <c r="L56" s="6" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -2803,9 +2976,11 @@
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="6" t="inlineStr"/>
-      <c r="J57" s="6" t="inlineStr"/>
-      <c r="K57" s="7" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr"/>
+      <c r="L57" s="6" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -2842,9 +3017,11 @@
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="6" t="inlineStr"/>
-      <c r="J58" s="6" t="inlineStr"/>
-      <c r="K58" s="7" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
+      <c r="L58" s="6" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -2881,9 +3058,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="6" t="inlineStr"/>
-      <c r="K59" s="7" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr"/>
+      <c r="L59" s="6" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -2920,9 +3099,11 @@
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="6" t="inlineStr"/>
-      <c r="J60" s="6" t="inlineStr"/>
-      <c r="K60" s="7" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
+      <c r="L60" s="6" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -2959,9 +3140,11 @@
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="6" t="inlineStr"/>
-      <c r="K61" s="7" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -2998,9 +3181,11 @@
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="6" t="inlineStr"/>
-      <c r="J62" s="6" t="inlineStr"/>
-      <c r="K62" s="7" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
+      <c r="L62" s="6" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -3037,9 +3222,11 @@
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="6" t="inlineStr"/>
-      <c r="J63" s="6" t="inlineStr"/>
-      <c r="K63" s="7" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr"/>
+      <c r="L63" s="6" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -3070,15 +3257,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="6" t="inlineStr"/>
-      <c r="J64" s="6" t="inlineStr"/>
-      <c r="K64" s="7" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr"/>
+      <c r="L64" s="6" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -3109,15 +3306,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="6" t="inlineStr"/>
-      <c r="J65" s="6" t="inlineStr"/>
-      <c r="K65" s="7" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr"/>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -3148,15 +3355,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="6" t="inlineStr"/>
-      <c r="J66" s="6" t="inlineStr"/>
-      <c r="K66" s="7" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr"/>
+      <c r="L66" s="6" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -3187,15 +3404,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="7" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr"/>
+      <c r="L67" s="6" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -3226,15 +3453,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="6" t="inlineStr"/>
-      <c r="J68" s="6" t="inlineStr"/>
-      <c r="K68" s="7" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr"/>
+      <c r="L68" s="6" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -3271,9 +3508,11 @@
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="6" t="inlineStr"/>
-      <c r="K69" s="7" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr"/>
+      <c r="L69" s="6" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -3310,9 +3549,11 @@
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="6" t="inlineStr"/>
-      <c r="J70" s="6" t="inlineStr"/>
-      <c r="K70" s="7" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr"/>
+      <c r="L70" s="6" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -3349,9 +3590,11 @@
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="6" t="inlineStr"/>
-      <c r="J71" s="6" t="inlineStr"/>
-      <c r="K71" s="7" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr"/>
+      <c r="L71" s="6" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -3388,9 +3631,11 @@
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr"/>
-      <c r="I72" s="6" t="inlineStr"/>
-      <c r="J72" s="6" t="inlineStr"/>
-      <c r="K72" s="7" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr"/>
+      <c r="L72" s="6" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -3427,9 +3672,11 @@
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr"/>
-      <c r="I73" s="6" t="inlineStr"/>
-      <c r="J73" s="6" t="inlineStr"/>
-      <c r="K73" s="7" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr"/>
+      <c r="L73" s="6" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -3466,9 +3713,11 @@
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="6" t="inlineStr"/>
-      <c r="J74" s="6" t="inlineStr"/>
-      <c r="K74" s="7" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr"/>
+      <c r="L74" s="6" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -3499,15 +3748,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="6" t="inlineStr"/>
-      <c r="J75" s="6" t="inlineStr"/>
-      <c r="K75" s="7" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr"/>
+      <c r="L75" s="6" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -3538,15 +3789,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="6" t="inlineStr"/>
-      <c r="J76" s="6" t="inlineStr"/>
-      <c r="K76" s="7" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr"/>
+      <c r="L76" s="6" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -3583,9 +3844,11 @@
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="6" t="inlineStr"/>
-      <c r="J77" s="6" t="inlineStr"/>
-      <c r="K77" s="7" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr"/>
+      <c r="L77" s="6" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -3622,9 +3885,11 @@
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="6" t="inlineStr"/>
-      <c r="J78" s="6" t="inlineStr"/>
-      <c r="K78" s="7" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -3655,15 +3920,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G79" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="6" t="inlineStr"/>
-      <c r="J79" s="6" t="inlineStr"/>
-      <c r="K79" s="7" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr"/>
+      <c r="L79" s="6" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -3700,9 +3967,11 @@
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="6" t="inlineStr"/>
-      <c r="J80" s="6" t="inlineStr"/>
-      <c r="K80" s="7" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -3739,9 +4008,11 @@
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="6" t="inlineStr"/>
-      <c r="J81" s="6" t="inlineStr"/>
-      <c r="K81" s="7" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr"/>
+      <c r="L81" s="6" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -3778,9 +4049,11 @@
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="6" t="inlineStr"/>
-      <c r="J82" s="6" t="inlineStr"/>
-      <c r="K82" s="7" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr"/>
+      <c r="L82" s="6" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
@@ -3817,9 +4090,11 @@
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr"/>
-      <c r="I83" s="6" t="inlineStr"/>
-      <c r="J83" s="6" t="inlineStr"/>
-      <c r="K83" s="7" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr"/>
+      <c r="L83" s="6" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -3850,15 +4125,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr"/>
-      <c r="I84" s="6" t="inlineStr"/>
-      <c r="J84" s="6" t="inlineStr"/>
-      <c r="K84" s="7" t="inlineStr"/>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr"/>
+      <c r="L84" s="6" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -3895,9 +4180,11 @@
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="6" t="inlineStr"/>
-      <c r="J85" s="6" t="inlineStr"/>
-      <c r="K85" s="7" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr"/>
+      <c r="L85" s="6" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -3934,9 +4221,11 @@
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="6" t="inlineStr"/>
-      <c r="J86" s="6" t="inlineStr"/>
-      <c r="K86" s="7" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="6" t="inlineStr"/>
+      <c r="L86" s="6" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
@@ -3967,15 +4256,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr"/>
-      <c r="I87" s="6" t="inlineStr"/>
-      <c r="J87" s="6" t="inlineStr"/>
-      <c r="K87" s="7" t="inlineStr"/>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr"/>
+      <c r="L87" s="6" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -4012,9 +4311,11 @@
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="6" t="inlineStr"/>
-      <c r="J88" s="6" t="inlineStr"/>
-      <c r="K88" s="7" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="6" t="inlineStr"/>
+      <c r="L88" s="6" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
@@ -4051,9 +4352,11 @@
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="6" t="inlineStr"/>
-      <c r="J89" s="6" t="inlineStr"/>
-      <c r="K89" s="7" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr"/>
+      <c r="L89" s="6" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
@@ -4090,9 +4393,11 @@
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr"/>
-      <c r="I90" s="6" t="inlineStr"/>
-      <c r="J90" s="6" t="inlineStr"/>
-      <c r="K90" s="7" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="6" t="inlineStr"/>
+      <c r="L90" s="6" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
@@ -4129,9 +4434,11 @@
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr"/>
-      <c r="I91" s="6" t="inlineStr"/>
-      <c r="J91" s="6" t="inlineStr"/>
-      <c r="K91" s="7" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr"/>
+      <c r="L91" s="6" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
@@ -4168,9 +4475,11 @@
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr"/>
-      <c r="I92" s="6" t="inlineStr"/>
-      <c r="J92" s="6" t="inlineStr"/>
-      <c r="K92" s="7" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="6" t="inlineStr"/>
+      <c r="L92" s="6" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
@@ -4201,15 +4510,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G93" s="9" t="inlineStr">
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr"/>
-      <c r="I93" s="6" t="inlineStr"/>
-      <c r="J93" s="6" t="inlineStr"/>
-      <c r="K93" s="7" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -4246,9 +4557,11 @@
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr"/>
-      <c r="I94" s="6" t="inlineStr"/>
-      <c r="J94" s="6" t="inlineStr"/>
-      <c r="K94" s="7" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr"/>
+      <c r="K94" s="6" t="inlineStr"/>
+      <c r="L94" s="6" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
@@ -4285,9 +4598,11 @@
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="6" t="inlineStr"/>
-      <c r="J95" s="6" t="inlineStr"/>
-      <c r="K95" s="7" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr"/>
+      <c r="L95" s="6" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
@@ -4318,15 +4633,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr"/>
-      <c r="I96" s="6" t="inlineStr"/>
-      <c r="J96" s="6" t="inlineStr"/>
-      <c r="K96" s="7" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
+      <c r="K96" s="6" t="inlineStr"/>
+      <c r="L96" s="6" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
@@ -4357,15 +4674,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G97" s="9" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr"/>
-      <c r="I97" s="6" t="inlineStr"/>
-      <c r="J97" s="6" t="inlineStr"/>
-      <c r="K97" s="7" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr"/>
+      <c r="L97" s="6" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
@@ -4396,15 +4723,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G98" s="9" t="inlineStr">
+      <c r="G98" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr"/>
-      <c r="I98" s="6" t="inlineStr"/>
-      <c r="J98" s="6" t="inlineStr"/>
-      <c r="K98" s="7" t="inlineStr"/>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="6" t="inlineStr"/>
+      <c r="L98" s="6" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -4435,15 +4764,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G99" s="9" t="inlineStr">
+      <c r="G99" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr"/>
-      <c r="I99" s="6" t="inlineStr"/>
-      <c r="J99" s="6" t="inlineStr"/>
-      <c r="K99" s="7" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr"/>
+      <c r="L99" s="6" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
@@ -4474,15 +4805,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr"/>
-      <c r="I100" s="6" t="inlineStr"/>
-      <c r="J100" s="6" t="inlineStr"/>
-      <c r="K100" s="7" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="6" t="inlineStr"/>
+      <c r="L100" s="6" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
@@ -4519,9 +4852,11 @@
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr"/>
-      <c r="I101" s="6" t="inlineStr"/>
-      <c r="J101" s="6" t="inlineStr"/>
-      <c r="K101" s="7" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr"/>
+      <c r="L101" s="6" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
@@ -4552,15 +4887,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G102" s="9" t="inlineStr">
+      <c r="G102" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr"/>
-      <c r="I102" s="6" t="inlineStr"/>
-      <c r="J102" s="6" t="inlineStr"/>
-      <c r="K102" s="7" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="6" t="inlineStr"/>
+      <c r="L102" s="6" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
@@ -4591,15 +4928,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G103" s="9" t="inlineStr">
+      <c r="G103" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr"/>
-      <c r="I103" s="6" t="inlineStr"/>
-      <c r="J103" s="6" t="inlineStr"/>
-      <c r="K103" s="7" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr"/>
+      <c r="K103" s="6" t="inlineStr"/>
+      <c r="L103" s="6" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -4636,9 +4975,11 @@
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr"/>
-      <c r="I104" s="6" t="inlineStr"/>
-      <c r="J104" s="6" t="inlineStr"/>
-      <c r="K104" s="7" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="6" t="inlineStr"/>
+      <c r="L104" s="6" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
@@ -4669,15 +5010,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
+      <c r="G105" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr"/>
-      <c r="I105" s="6" t="inlineStr"/>
-      <c r="J105" s="6" t="inlineStr"/>
-      <c r="K105" s="7" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="6" t="inlineStr"/>
+      <c r="L105" s="6" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -4703,7 +5046,7 @@
           <t>Analítico</t>
         </is>
       </c>
-      <c r="F106" s="10" t="inlineStr">
+      <c r="F106" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -4714,9 +5057,11 @@
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr"/>
-      <c r="I106" s="6" t="inlineStr"/>
-      <c r="J106" s="6" t="inlineStr"/>
-      <c r="K106" s="7" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="6" t="inlineStr"/>
+      <c r="L106" s="6" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
@@ -4742,7 +5087,7 @@
           <t>Listagem</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -4753,9 +5098,11 @@
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr"/>
-      <c r="I107" s="6" t="inlineStr"/>
-      <c r="J107" s="6" t="inlineStr"/>
-      <c r="K107" s="7" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr"/>
+      <c r="L107" s="6" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
@@ -4792,9 +5139,11 @@
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr"/>
-      <c r="I108" s="6" t="inlineStr"/>
-      <c r="J108" s="6" t="inlineStr"/>
-      <c r="K108" s="7" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="6" t="inlineStr"/>
+      <c r="L108" s="6" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
@@ -4831,9 +5180,11 @@
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr"/>
-      <c r="I109" s="6" t="inlineStr"/>
-      <c r="J109" s="6" t="inlineStr"/>
-      <c r="K109" s="7" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr"/>
+      <c r="L109" s="6" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
@@ -4870,9 +5221,11 @@
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr"/>
-      <c r="I110" s="6" t="inlineStr"/>
-      <c r="J110" s="6" t="inlineStr"/>
-      <c r="K110" s="7" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="6" t="inlineStr"/>
+      <c r="L110" s="6" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
@@ -4909,9 +5262,11 @@
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr"/>
-      <c r="I111" s="6" t="inlineStr"/>
-      <c r="J111" s="6" t="inlineStr"/>
-      <c r="K111" s="7" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr"/>
+      <c r="L111" s="6" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
@@ -4948,9 +5303,11 @@
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr"/>
-      <c r="I112" s="6" t="inlineStr"/>
-      <c r="J112" s="6" t="inlineStr"/>
-      <c r="K112" s="7" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="6" t="inlineStr"/>
+      <c r="L112" s="6" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
@@ -4987,9 +5344,11 @@
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr"/>
-      <c r="I113" s="6" t="inlineStr"/>
-      <c r="J113" s="6" t="inlineStr"/>
-      <c r="K113" s="7" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr"/>
+      <c r="L113" s="6" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
@@ -5026,9 +5385,11 @@
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr"/>
-      <c r="I114" s="6" t="inlineStr"/>
-      <c r="J114" s="6" t="inlineStr"/>
-      <c r="K114" s="7" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+      <c r="K114" s="6" t="inlineStr"/>
+      <c r="L114" s="6" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
@@ -5065,9 +5426,11 @@
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr"/>
-      <c r="I115" s="6" t="inlineStr"/>
-      <c r="J115" s="6" t="inlineStr"/>
-      <c r="K115" s="7" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="inlineStr"/>
+      <c r="K115" s="6" t="inlineStr"/>
+      <c r="L115" s="6" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -5104,9 +5467,11 @@
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr"/>
-      <c r="I116" s="6" t="inlineStr"/>
-      <c r="J116" s="6" t="inlineStr"/>
-      <c r="K116" s="7" t="inlineStr"/>
+      <c r="I116" s="3" t="inlineStr"/>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="6" t="inlineStr"/>
+      <c r="L116" s="6" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -5143,9 +5508,11 @@
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr"/>
-      <c r="I117" s="6" t="inlineStr"/>
-      <c r="J117" s="6" t="inlineStr"/>
-      <c r="K117" s="7" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr"/>
+      <c r="K117" s="6" t="inlineStr"/>
+      <c r="L117" s="6" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -5182,9 +5549,11 @@
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr"/>
-      <c r="I118" s="6" t="inlineStr"/>
-      <c r="J118" s="6" t="inlineStr"/>
-      <c r="K118" s="7" t="inlineStr"/>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="6" t="inlineStr"/>
+      <c r="L118" s="6" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
@@ -5221,9 +5590,11 @@
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr"/>
-      <c r="I119" s="6" t="inlineStr"/>
-      <c r="J119" s="6" t="inlineStr"/>
-      <c r="K119" s="7" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="6" t="inlineStr"/>
+      <c r="L119" s="6" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
@@ -5249,7 +5620,7 @@
           <t>Ação</t>
         </is>
       </c>
-      <c r="F120" s="10" t="inlineStr">
+      <c r="F120" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -5260,9 +5631,11 @@
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr"/>
-      <c r="I120" s="6" t="inlineStr"/>
-      <c r="J120" s="6" t="inlineStr"/>
-      <c r="K120" s="7" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="6" t="inlineStr"/>
+      <c r="L120" s="6" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
@@ -5299,9 +5672,11 @@
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr"/>
-      <c r="I121" s="6" t="inlineStr"/>
-      <c r="J121" s="6" t="inlineStr"/>
-      <c r="K121" s="7" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="6" t="inlineStr"/>
+      <c r="L121" s="6" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
@@ -5332,15 +5707,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G122" s="9" t="inlineStr">
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr"/>
-      <c r="I122" s="6" t="inlineStr"/>
-      <c r="J122" s="6" t="inlineStr"/>
-      <c r="K122" s="7" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="6" t="inlineStr"/>
+      <c r="L122" s="6" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
@@ -5371,15 +5756,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G123" s="9" t="inlineStr">
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr"/>
-      <c r="I123" s="6" t="inlineStr"/>
-      <c r="J123" s="6" t="inlineStr"/>
-      <c r="K123" s="7" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr"/>
+      <c r="K123" s="6" t="inlineStr"/>
+      <c r="L123" s="6" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
@@ -5410,15 +5805,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G124" s="9" t="inlineStr">
+      <c r="G124" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr"/>
-      <c r="I124" s="6" t="inlineStr"/>
-      <c r="J124" s="6" t="inlineStr"/>
-      <c r="K124" s="7" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="6" t="inlineStr"/>
+      <c r="L124" s="6" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
@@ -5449,15 +5846,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G125" s="9" t="inlineStr">
+      <c r="G125" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr"/>
-      <c r="I125" s="6" t="inlineStr"/>
-      <c r="J125" s="6" t="inlineStr"/>
-      <c r="K125" s="7" t="inlineStr"/>
+      <c r="I125" s="3" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr"/>
+      <c r="K125" s="6" t="inlineStr"/>
+      <c r="L125" s="6" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -5488,15 +5887,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G126" s="9" t="inlineStr">
+      <c r="G126" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr"/>
-      <c r="I126" s="6" t="inlineStr"/>
-      <c r="J126" s="6" t="inlineStr"/>
-      <c r="K126" s="7" t="inlineStr"/>
+      <c r="I126" s="3" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="6" t="inlineStr"/>
+      <c r="L126" s="6" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -5533,9 +5934,11 @@
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr"/>
-      <c r="I127" s="6" t="inlineStr"/>
-      <c r="J127" s="6" t="inlineStr"/>
-      <c r="K127" s="7" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="6" t="inlineStr"/>
+      <c r="L127" s="6" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
@@ -5572,9 +5975,11 @@
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr"/>
-      <c r="I128" s="6" t="inlineStr"/>
-      <c r="J128" s="6" t="inlineStr"/>
-      <c r="K128" s="7" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="6" t="inlineStr"/>
+      <c r="L128" s="6" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
@@ -5605,15 +6010,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G129" s="9" t="inlineStr">
+      <c r="G129" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr"/>
-      <c r="I129" s="6" t="inlineStr"/>
-      <c r="J129" s="6" t="inlineStr"/>
-      <c r="K129" s="7" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr"/>
+      <c r="K129" s="6" t="inlineStr"/>
+      <c r="L129" s="6" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
@@ -5644,15 +6051,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G130" s="9" t="inlineStr">
+      <c r="G130" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr"/>
-      <c r="I130" s="6" t="inlineStr"/>
-      <c r="J130" s="6" t="inlineStr"/>
-      <c r="K130" s="7" t="inlineStr"/>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="6" t="inlineStr"/>
+      <c r="L130" s="6" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
@@ -5683,15 +6092,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G131" s="9" t="inlineStr">
+      <c r="G131" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr"/>
-      <c r="I131" s="6" t="inlineStr"/>
-      <c r="J131" s="6" t="inlineStr"/>
-      <c r="K131" s="7" t="inlineStr"/>
+      <c r="I131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="6" t="inlineStr"/>
+      <c r="L131" s="6" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
@@ -5728,9 +6139,11 @@
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr"/>
-      <c r="I132" s="6" t="inlineStr"/>
-      <c r="J132" s="6" t="inlineStr"/>
-      <c r="K132" s="7" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="6" t="inlineStr"/>
+      <c r="L132" s="6" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -5761,15 +6174,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G133" s="9" t="inlineStr">
+      <c r="G133" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr"/>
-      <c r="I133" s="6" t="inlineStr"/>
-      <c r="J133" s="6" t="inlineStr"/>
-      <c r="K133" s="7" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="6" t="inlineStr"/>
+      <c r="L133" s="6" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
@@ -5800,15 +6215,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G134" s="9" t="inlineStr">
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr"/>
-      <c r="I134" s="6" t="inlineStr"/>
-      <c r="J134" s="6" t="inlineStr"/>
-      <c r="K134" s="7" t="inlineStr"/>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="6" t="inlineStr"/>
+      <c r="L134" s="6" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
@@ -5839,15 +6264,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G135" s="9" t="inlineStr">
+      <c r="G135" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr"/>
-      <c r="I135" s="6" t="inlineStr"/>
-      <c r="J135" s="6" t="inlineStr"/>
-      <c r="K135" s="7" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="6" t="inlineStr"/>
+      <c r="L135" s="6" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
@@ -5878,15 +6305,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G136" s="9" t="inlineStr">
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr"/>
-      <c r="I136" s="6" t="inlineStr"/>
-      <c r="J136" s="6" t="inlineStr"/>
-      <c r="K136" s="7" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="6" t="inlineStr"/>
+      <c r="L136" s="6" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -5917,15 +6354,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G137" s="9" t="inlineStr">
+      <c r="G137" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="6" t="inlineStr"/>
-      <c r="J137" s="6" t="inlineStr"/>
-      <c r="K137" s="7" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="6" t="inlineStr"/>
+      <c r="L137" s="6" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -5956,15 +6395,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G138" s="9" t="inlineStr">
+      <c r="G138" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr"/>
-      <c r="I138" s="6" t="inlineStr"/>
-      <c r="J138" s="6" t="inlineStr"/>
-      <c r="K138" s="7" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr"/>
+      <c r="J138" s="3" t="inlineStr"/>
+      <c r="K138" s="6" t="inlineStr"/>
+      <c r="L138" s="6" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -5995,15 +6436,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G139" s="9" t="inlineStr">
+      <c r="G139" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr"/>
-      <c r="I139" s="6" t="inlineStr"/>
-      <c r="J139" s="6" t="inlineStr"/>
-      <c r="K139" s="7" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="6" t="inlineStr"/>
+      <c r="L139" s="6" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
@@ -6034,15 +6477,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G140" s="9" t="inlineStr">
+      <c r="G140" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr"/>
-      <c r="I140" s="6" t="inlineStr"/>
-      <c r="J140" s="6" t="inlineStr"/>
-      <c r="K140" s="7" t="inlineStr"/>
+      <c r="I140" s="3" t="inlineStr"/>
+      <c r="J140" s="3" t="inlineStr"/>
+      <c r="K140" s="6" t="inlineStr"/>
+      <c r="L140" s="6" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
@@ -6073,15 +6518,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G141" s="9" t="inlineStr">
+      <c r="G141" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr"/>
-      <c r="I141" s="6" t="inlineStr"/>
-      <c r="J141" s="6" t="inlineStr"/>
-      <c r="K141" s="7" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr"/>
+      <c r="J141" s="3" t="inlineStr"/>
+      <c r="K141" s="6" t="inlineStr"/>
+      <c r="L141" s="6" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
@@ -6112,15 +6559,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G142" s="9" t="inlineStr">
+      <c r="G142" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr"/>
-      <c r="I142" s="6" t="inlineStr"/>
-      <c r="J142" s="6" t="inlineStr"/>
-      <c r="K142" s="7" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr"/>
+      <c r="K142" s="6" t="inlineStr"/>
+      <c r="L142" s="6" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
@@ -6151,15 +6600,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G143" s="9" t="inlineStr">
+      <c r="G143" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr"/>
-      <c r="I143" s="6" t="inlineStr"/>
-      <c r="J143" s="6" t="inlineStr"/>
-      <c r="K143" s="7" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr"/>
+      <c r="J143" s="3" t="inlineStr"/>
+      <c r="K143" s="6" t="inlineStr"/>
+      <c r="L143" s="6" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
@@ -6190,15 +6641,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G144" s="9" t="inlineStr">
+      <c r="G144" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr"/>
-      <c r="I144" s="6" t="inlineStr"/>
-      <c r="J144" s="6" t="inlineStr"/>
-      <c r="K144" s="7" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr"/>
+      <c r="K144" s="6" t="inlineStr"/>
+      <c r="L144" s="6" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
@@ -6229,15 +6682,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G145" s="9" t="inlineStr">
+      <c r="G145" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr"/>
-      <c r="I145" s="6" t="inlineStr"/>
-      <c r="J145" s="6" t="inlineStr"/>
-      <c r="K145" s="7" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr"/>
+      <c r="K145" s="6" t="inlineStr"/>
+      <c r="L145" s="6" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
@@ -6268,15 +6723,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G146" s="9" t="inlineStr">
+      <c r="G146" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr"/>
-      <c r="I146" s="6" t="inlineStr"/>
-      <c r="J146" s="6" t="inlineStr"/>
-      <c r="K146" s="7" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr"/>
+      <c r="J146" s="3" t="inlineStr"/>
+      <c r="K146" s="6" t="inlineStr"/>
+      <c r="L146" s="6" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -6307,15 +6764,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G147" s="9" t="inlineStr">
+      <c r="G147" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr"/>
-      <c r="I147" s="6" t="inlineStr"/>
-      <c r="J147" s="6" t="inlineStr"/>
-      <c r="K147" s="7" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr"/>
+      <c r="K147" s="6" t="inlineStr"/>
+      <c r="L147" s="6" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -6346,15 +6805,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G148" s="9" t="inlineStr">
+      <c r="G148" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr"/>
-      <c r="I148" s="6" t="inlineStr"/>
-      <c r="J148" s="6" t="inlineStr"/>
-      <c r="K148" s="7" t="inlineStr"/>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="3" t="inlineStr"/>
+      <c r="K148" s="6" t="inlineStr"/>
+      <c r="L148" s="6" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
@@ -6385,15 +6846,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G149" s="9" t="inlineStr">
+      <c r="G149" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr"/>
-      <c r="I149" s="6" t="inlineStr"/>
-      <c r="J149" s="6" t="inlineStr"/>
-      <c r="K149" s="7" t="inlineStr"/>
+      <c r="I149" s="3" t="inlineStr"/>
+      <c r="J149" s="3" t="inlineStr"/>
+      <c r="K149" s="6" t="inlineStr"/>
+      <c r="L149" s="6" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
@@ -6424,15 +6887,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G150" s="9" t="inlineStr">
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr"/>
-      <c r="I150" s="6" t="inlineStr"/>
-      <c r="J150" s="6" t="inlineStr"/>
-      <c r="K150" s="7" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="6" t="inlineStr"/>
+      <c r="L150" s="6" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
@@ -6463,15 +6936,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G151" s="9" t="inlineStr">
+      <c r="G151" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr"/>
-      <c r="I151" s="6" t="inlineStr"/>
-      <c r="J151" s="6" t="inlineStr"/>
-      <c r="K151" s="7" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="6" t="inlineStr"/>
+      <c r="L151" s="6" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -6497,7 +6972,7 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="F152" s="10" t="inlineStr">
+      <c r="F152" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -6508,9 +6983,11 @@
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr"/>
-      <c r="I152" s="6" t="inlineStr"/>
-      <c r="J152" s="6" t="inlineStr"/>
-      <c r="K152" s="7" t="inlineStr"/>
+      <c r="I152" s="3" t="inlineStr"/>
+      <c r="J152" s="3" t="inlineStr"/>
+      <c r="K152" s="6" t="inlineStr"/>
+      <c r="L152" s="6" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
@@ -6536,7 +7013,7 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="F153" s="10" t="inlineStr">
+      <c r="F153" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -6547,9 +7024,11 @@
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr"/>
-      <c r="I153" s="6" t="inlineStr"/>
-      <c r="J153" s="6" t="inlineStr"/>
-      <c r="K153" s="7" t="inlineStr"/>
+      <c r="I153" s="3" t="inlineStr"/>
+      <c r="J153" s="3" t="inlineStr"/>
+      <c r="K153" s="6" t="inlineStr"/>
+      <c r="L153" s="6" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
@@ -6575,7 +7054,7 @@
           <t>Ação</t>
         </is>
       </c>
-      <c r="F154" s="10" t="inlineStr">
+      <c r="F154" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -6586,9 +7065,11 @@
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr"/>
-      <c r="I154" s="6" t="inlineStr"/>
-      <c r="J154" s="6" t="inlineStr"/>
-      <c r="K154" s="7" t="inlineStr"/>
+      <c r="I154" s="3" t="inlineStr"/>
+      <c r="J154" s="3" t="inlineStr"/>
+      <c r="K154" s="6" t="inlineStr"/>
+      <c r="L154" s="6" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
@@ -6614,7 +7095,7 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="F155" s="10" t="inlineStr">
+      <c r="F155" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -6625,9 +7106,11 @@
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr"/>
-      <c r="I155" s="6" t="inlineStr"/>
-      <c r="J155" s="6" t="inlineStr"/>
-      <c r="K155" s="7" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr"/>
+      <c r="J155" s="3" t="inlineStr"/>
+      <c r="K155" s="6" t="inlineStr"/>
+      <c r="L155" s="6" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
@@ -6664,9 +7147,11 @@
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr"/>
-      <c r="I156" s="6" t="inlineStr"/>
-      <c r="J156" s="6" t="inlineStr"/>
-      <c r="K156" s="7" t="inlineStr"/>
+      <c r="I156" s="3" t="inlineStr"/>
+      <c r="J156" s="3" t="inlineStr"/>
+      <c r="K156" s="6" t="inlineStr"/>
+      <c r="L156" s="6" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
@@ -6703,9 +7188,11 @@
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr"/>
-      <c r="I157" s="6" t="inlineStr"/>
-      <c r="J157" s="6" t="inlineStr"/>
-      <c r="K157" s="7" t="inlineStr"/>
+      <c r="I157" s="3" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr"/>
+      <c r="K157" s="6" t="inlineStr"/>
+      <c r="L157" s="6" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
@@ -6742,9 +7229,11 @@
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr"/>
-      <c r="I158" s="6" t="inlineStr"/>
-      <c r="J158" s="6" t="inlineStr"/>
-      <c r="K158" s="7" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr"/>
+      <c r="J158" s="3" t="inlineStr"/>
+      <c r="K158" s="6" t="inlineStr"/>
+      <c r="L158" s="6" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -6781,9 +7270,11 @@
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr"/>
-      <c r="I159" s="6" t="inlineStr"/>
-      <c r="J159" s="6" t="inlineStr"/>
-      <c r="K159" s="7" t="inlineStr"/>
+      <c r="I159" s="3" t="inlineStr"/>
+      <c r="J159" s="3" t="inlineStr"/>
+      <c r="K159" s="6" t="inlineStr"/>
+      <c r="L159" s="6" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
@@ -6814,15 +7305,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G160" s="9" t="inlineStr">
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr"/>
-      <c r="I160" s="6" t="inlineStr"/>
-      <c r="J160" s="6" t="inlineStr"/>
-      <c r="K160" s="7" t="inlineStr"/>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr"/>
+      <c r="K160" s="6" t="inlineStr"/>
+      <c r="L160" s="6" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -6859,9 +7360,11 @@
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr"/>
-      <c r="I161" s="6" t="inlineStr"/>
-      <c r="J161" s="6" t="inlineStr"/>
-      <c r="K161" s="7" t="inlineStr"/>
+      <c r="I161" s="3" t="inlineStr"/>
+      <c r="J161" s="3" t="inlineStr"/>
+      <c r="K161" s="6" t="inlineStr"/>
+      <c r="L161" s="6" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
@@ -6898,9 +7401,11 @@
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr"/>
-      <c r="I162" s="6" t="inlineStr"/>
-      <c r="J162" s="6" t="inlineStr"/>
-      <c r="K162" s="7" t="inlineStr"/>
+      <c r="I162" s="3" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr"/>
+      <c r="K162" s="6" t="inlineStr"/>
+      <c r="L162" s="6" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
@@ -6931,15 +7436,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G163" s="9" t="inlineStr">
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr"/>
-      <c r="I163" s="6" t="inlineStr"/>
-      <c r="J163" s="6" t="inlineStr"/>
-      <c r="K163" s="7" t="inlineStr"/>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr"/>
+      <c r="K163" s="6" t="inlineStr"/>
+      <c r="L163" s="6" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
@@ -6976,9 +7491,11 @@
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr"/>
-      <c r="I164" s="6" t="inlineStr"/>
-      <c r="J164" s="6" t="inlineStr"/>
-      <c r="K164" s="7" t="inlineStr"/>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="3" t="inlineStr"/>
+      <c r="K164" s="6" t="inlineStr"/>
+      <c r="L164" s="6" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -7009,15 +7526,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G165" s="9" t="inlineStr">
+      <c r="G165" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr"/>
-      <c r="I165" s="6" t="inlineStr"/>
-      <c r="J165" s="6" t="inlineStr"/>
-      <c r="K165" s="7" t="inlineStr"/>
+      <c r="I165" s="3" t="inlineStr"/>
+      <c r="J165" s="3" t="inlineStr"/>
+      <c r="K165" s="6" t="inlineStr"/>
+      <c r="L165" s="6" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
@@ -7054,9 +7573,11 @@
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr"/>
-      <c r="I166" s="6" t="inlineStr"/>
-      <c r="J166" s="6" t="inlineStr"/>
-      <c r="K166" s="7" t="inlineStr"/>
+      <c r="I166" s="3" t="inlineStr"/>
+      <c r="J166" s="3" t="inlineStr"/>
+      <c r="K166" s="6" t="inlineStr"/>
+      <c r="L166" s="6" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -7093,9 +7614,11 @@
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr"/>
-      <c r="I167" s="6" t="inlineStr"/>
-      <c r="J167" s="6" t="inlineStr"/>
-      <c r="K167" s="7" t="inlineStr"/>
+      <c r="I167" s="3" t="inlineStr"/>
+      <c r="J167" s="3" t="inlineStr"/>
+      <c r="K167" s="6" t="inlineStr"/>
+      <c r="L167" s="6" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
@@ -7132,9 +7655,11 @@
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr"/>
-      <c r="I168" s="6" t="inlineStr"/>
-      <c r="J168" s="6" t="inlineStr"/>
-      <c r="K168" s="7" t="inlineStr"/>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="3" t="inlineStr"/>
+      <c r="K168" s="6" t="inlineStr"/>
+      <c r="L168" s="6" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
@@ -7171,9 +7696,11 @@
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr"/>
-      <c r="I169" s="6" t="inlineStr"/>
-      <c r="J169" s="6" t="inlineStr"/>
-      <c r="K169" s="7" t="inlineStr"/>
+      <c r="I169" s="3" t="inlineStr"/>
+      <c r="J169" s="3" t="inlineStr"/>
+      <c r="K169" s="6" t="inlineStr"/>
+      <c r="L169" s="6" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -7204,15 +7731,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G170" s="9" t="inlineStr">
+      <c r="G170" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr"/>
-      <c r="I170" s="6" t="inlineStr"/>
-      <c r="J170" s="6" t="inlineStr"/>
-      <c r="K170" s="7" t="inlineStr"/>
+      <c r="I170" s="3" t="inlineStr"/>
+      <c r="J170" s="3" t="inlineStr"/>
+      <c r="K170" s="6" t="inlineStr"/>
+      <c r="L170" s="6" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -7249,9 +7778,11 @@
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr"/>
-      <c r="I171" s="6" t="inlineStr"/>
-      <c r="J171" s="6" t="inlineStr"/>
-      <c r="K171" s="7" t="inlineStr"/>
+      <c r="I171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="inlineStr"/>
+      <c r="K171" s="6" t="inlineStr"/>
+      <c r="L171" s="6" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
@@ -7288,9 +7819,11 @@
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr"/>
-      <c r="I172" s="6" t="inlineStr"/>
-      <c r="J172" s="6" t="inlineStr"/>
-      <c r="K172" s="7" t="inlineStr"/>
+      <c r="I172" s="3" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr"/>
+      <c r="K172" s="6" t="inlineStr"/>
+      <c r="L172" s="6" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
@@ -7327,9 +7860,11 @@
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr"/>
-      <c r="I173" s="6" t="inlineStr"/>
-      <c r="J173" s="6" t="inlineStr"/>
-      <c r="K173" s="7" t="inlineStr"/>
+      <c r="I173" s="3" t="inlineStr"/>
+      <c r="J173" s="3" t="inlineStr"/>
+      <c r="K173" s="6" t="inlineStr"/>
+      <c r="L173" s="6" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
@@ -7366,9 +7901,11 @@
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr"/>
-      <c r="I174" s="6" t="inlineStr"/>
-      <c r="J174" s="6" t="inlineStr"/>
-      <c r="K174" s="7" t="inlineStr"/>
+      <c r="I174" s="3" t="inlineStr"/>
+      <c r="J174" s="3" t="inlineStr"/>
+      <c r="K174" s="6" t="inlineStr"/>
+      <c r="L174" s="6" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
@@ -7399,15 +7936,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G175" s="9" t="inlineStr">
+      <c r="G175" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr"/>
-      <c r="I175" s="6" t="inlineStr"/>
-      <c r="J175" s="6" t="inlineStr"/>
-      <c r="K175" s="7" t="inlineStr"/>
+      <c r="I175" s="3" t="inlineStr"/>
+      <c r="J175" s="3" t="inlineStr"/>
+      <c r="K175" s="6" t="inlineStr"/>
+      <c r="L175" s="6" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
@@ -7438,15 +7977,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G176" s="9" t="inlineStr">
+      <c r="G176" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr"/>
-      <c r="I176" s="6" t="inlineStr"/>
-      <c r="J176" s="6" t="inlineStr"/>
-      <c r="K176" s="7" t="inlineStr"/>
+      <c r="I176" s="3" t="inlineStr"/>
+      <c r="J176" s="3" t="inlineStr"/>
+      <c r="K176" s="6" t="inlineStr"/>
+      <c r="L176" s="6" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -7477,15 +8018,25 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G177" s="9" t="inlineStr">
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr"/>
-      <c r="I177" s="6" t="inlineStr"/>
-      <c r="J177" s="6" t="inlineStr"/>
-      <c r="K177" s="7" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J177" s="3" t="inlineStr"/>
+      <c r="K177" s="6" t="inlineStr"/>
+      <c r="L177" s="6" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
@@ -7516,15 +8067,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G178" s="9" t="inlineStr">
+      <c r="G178" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr"/>
-      <c r="I178" s="6" t="inlineStr"/>
-      <c r="J178" s="6" t="inlineStr"/>
-      <c r="K178" s="7" t="inlineStr"/>
+      <c r="I178" s="3" t="inlineStr"/>
+      <c r="J178" s="3" t="inlineStr"/>
+      <c r="K178" s="6" t="inlineStr"/>
+      <c r="L178" s="6" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
@@ -7555,15 +8108,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G179" s="9" t="inlineStr">
+      <c r="G179" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr"/>
-      <c r="I179" s="6" t="inlineStr"/>
-      <c r="J179" s="6" t="inlineStr"/>
-      <c r="K179" s="7" t="inlineStr"/>
+      <c r="I179" s="3" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr"/>
+      <c r="K179" s="6" t="inlineStr"/>
+      <c r="L179" s="6" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
@@ -7600,9 +8155,11 @@
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr"/>
-      <c r="I180" s="6" t="inlineStr"/>
-      <c r="J180" s="6" t="inlineStr"/>
-      <c r="K180" s="7" t="inlineStr"/>
+      <c r="I180" s="3" t="inlineStr"/>
+      <c r="J180" s="3" t="inlineStr"/>
+      <c r="K180" s="6" t="inlineStr"/>
+      <c r="L180" s="6" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
@@ -7639,9 +8196,11 @@
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr"/>
-      <c r="I181" s="6" t="inlineStr"/>
-      <c r="J181" s="6" t="inlineStr"/>
-      <c r="K181" s="7" t="inlineStr"/>
+      <c r="I181" s="3" t="inlineStr"/>
+      <c r="J181" s="3" t="inlineStr"/>
+      <c r="K181" s="6" t="inlineStr"/>
+      <c r="L181" s="6" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
@@ -7678,9 +8237,11 @@
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr"/>
-      <c r="I182" s="6" t="inlineStr"/>
-      <c r="J182" s="6" t="inlineStr"/>
-      <c r="K182" s="7" t="inlineStr"/>
+      <c r="I182" s="3" t="inlineStr"/>
+      <c r="J182" s="3" t="inlineStr"/>
+      <c r="K182" s="6" t="inlineStr"/>
+      <c r="L182" s="6" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n">
@@ -7717,9 +8278,11 @@
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr"/>
-      <c r="I183" s="6" t="inlineStr"/>
-      <c r="J183" s="6" t="inlineStr"/>
-      <c r="K183" s="7" t="inlineStr"/>
+      <c r="I183" s="3" t="inlineStr"/>
+      <c r="J183" s="3" t="inlineStr"/>
+      <c r="K183" s="6" t="inlineStr"/>
+      <c r="L183" s="6" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
@@ -7756,9 +8319,11 @@
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr"/>
-      <c r="I184" s="6" t="inlineStr"/>
-      <c r="J184" s="6" t="inlineStr"/>
-      <c r="K184" s="7" t="inlineStr"/>
+      <c r="I184" s="3" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr"/>
+      <c r="K184" s="6" t="inlineStr"/>
+      <c r="L184" s="6" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
@@ -7795,9 +8360,11 @@
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr"/>
-      <c r="I185" s="6" t="inlineStr"/>
-      <c r="J185" s="6" t="inlineStr"/>
-      <c r="K185" s="7" t="inlineStr"/>
+      <c r="I185" s="3" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr"/>
+      <c r="K185" s="6" t="inlineStr"/>
+      <c r="L185" s="6" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n">
@@ -7823,7 +8390,7 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="F186" s="10" t="inlineStr">
+      <c r="F186" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -7834,9 +8401,11 @@
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr"/>
-      <c r="I186" s="6" t="inlineStr"/>
-      <c r="J186" s="6" t="inlineStr"/>
-      <c r="K186" s="7" t="inlineStr"/>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr"/>
+      <c r="K186" s="6" t="inlineStr"/>
+      <c r="L186" s="6" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n">
@@ -7862,7 +8431,7 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="F187" s="10" t="inlineStr">
+      <c r="F187" s="9" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>
@@ -7873,9 +8442,11 @@
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr"/>
-      <c r="I187" s="6" t="inlineStr"/>
-      <c r="J187" s="6" t="inlineStr"/>
-      <c r="K187" s="7" t="inlineStr"/>
+      <c r="I187" s="3" t="inlineStr"/>
+      <c r="J187" s="3" t="inlineStr"/>
+      <c r="K187" s="6" t="inlineStr"/>
+      <c r="L187" s="6" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n">
@@ -7906,15 +8477,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G188" s="9" t="inlineStr">
+      <c r="G188" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr"/>
-      <c r="I188" s="6" t="inlineStr"/>
-      <c r="J188" s="6" t="inlineStr"/>
-      <c r="K188" s="7" t="inlineStr"/>
+      <c r="I188" s="3" t="inlineStr"/>
+      <c r="J188" s="3" t="inlineStr"/>
+      <c r="K188" s="6" t="inlineStr"/>
+      <c r="L188" s="6" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n">
@@ -7945,15 +8518,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G189" s="9" t="inlineStr">
+      <c r="G189" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr"/>
-      <c r="I189" s="6" t="inlineStr"/>
-      <c r="J189" s="6" t="inlineStr"/>
-      <c r="K189" s="7" t="inlineStr"/>
+      <c r="I189" s="3" t="inlineStr"/>
+      <c r="J189" s="3" t="inlineStr"/>
+      <c r="K189" s="6" t="inlineStr"/>
+      <c r="L189" s="6" t="inlineStr"/>
+      <c r="M189" s="7" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
@@ -7984,15 +8559,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G190" s="9" t="inlineStr">
+      <c r="G190" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr"/>
-      <c r="I190" s="6" t="inlineStr"/>
-      <c r="J190" s="6" t="inlineStr"/>
-      <c r="K190" s="7" t="inlineStr"/>
+      <c r="I190" s="3" t="inlineStr"/>
+      <c r="J190" s="3" t="inlineStr"/>
+      <c r="K190" s="6" t="inlineStr"/>
+      <c r="L190" s="6" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
@@ -8023,15 +8600,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G191" s="9" t="inlineStr">
+      <c r="G191" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr"/>
-      <c r="I191" s="6" t="inlineStr"/>
-      <c r="J191" s="6" t="inlineStr"/>
-      <c r="K191" s="7" t="inlineStr"/>
+      <c r="I191" s="3" t="inlineStr"/>
+      <c r="J191" s="3" t="inlineStr"/>
+      <c r="K191" s="6" t="inlineStr"/>
+      <c r="L191" s="6" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n">
@@ -8062,15 +8641,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G192" s="9" t="inlineStr">
+      <c r="G192" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr"/>
-      <c r="I192" s="6" t="inlineStr"/>
-      <c r="J192" s="6" t="inlineStr"/>
-      <c r="K192" s="7" t="inlineStr"/>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr"/>
+      <c r="K192" s="6" t="inlineStr"/>
+      <c r="L192" s="6" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
@@ -8107,17 +8688,23 @@
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr"/>
-      <c r="I193" s="6" t="inlineStr"/>
-      <c r="J193" s="6" t="inlineStr"/>
-      <c r="K193" s="7" t="inlineStr"/>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J193" s="3" t="inlineStr"/>
+      <c r="K193" s="6" t="inlineStr"/>
+      <c r="L193" s="6" t="inlineStr"/>
+      <c r="M193" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K193"/>
+  <autoFilter ref="A1:M193"/>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I193" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
+    <dataValidation sqref="K2:K193" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
       <formula1>"M0,M1,M2,Fora"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J193" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
+    <dataValidation sqref="L2:L193" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8230,13 +8817,13 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -8246,7 +8833,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>O módulo que a tese defende entra quase inteiro. Ficam fora os quatro gráficos analíticos — eles explicam o crédito, não o garantem.</t>
+          <t>O módulo que a tese defende entra quase inteiro: 11 de 14. Ficam fora três gráficos analíticos — eles explicam o crédito, não o garantem. O Top 5 e Top 10 de fornecedores subiu na revisão de 15/09: saber de quem cobrar primeiro é operação, não análise.</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8897,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Entra a guia, o comprovante e o rastro dos três status. A entrega ao ERP passa ao M0 junto com a API. Fica fora o que depende de execução programada.</t>
+          <t>Entra a guia, o comprovante e o rastro dos três status. A entrega ao ERP passa ao M0 junto com a API. Na revisão de 15/09 a aba Execução Programada entrou e a gestão de colunas saiu: o piloto precisa ver o que está agendado, não configurar a própria grade.</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8929,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>A inconsistência é o que impede o crédito de morrer em silêncio. Fica fora só o que distribui trabalho entre pessoas.</t>
+          <t>A inconsistência é o que impede o crédito de morrer em silêncio. Na revisão de 15/09 a atribuição de responsável entrou — inconsistência sem dono não é tratada — e os filtros multiselect saíram.</t>
         </is>
       </c>
     </row>
@@ -8422,13 +9009,13 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -8438,7 +9025,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Score de fornecedor é argumento de renovação, não de adoção.</t>
+          <t>Reclassificado em 15/09: 5 de 6 no M0. O score, o critério, o badge, o ranking e o mapa de bolhas deixam de ser argumento de renovação e passam a ser o que diz de quem cobrar primeiro. Só a evolução histórica do score fica para depois — ela exige série que o piloto ainda não tem.</t>
         </is>
       </c>
     </row>
@@ -8454,13 +9041,13 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -8470,7 +9057,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Os três métodos de pagamento são pré-requisito: sem saber quem recolhe, não há cadeia. O contrato como recorte de política acompanha Execução RAD.</t>
+          <t>Dois dos três métodos são pré-requisito: sem saber quem recolhe, não há cadeia. Na revisão de 15/09 o Split Payment foi para M2 — o piloto cobre RAD e Fornecedor. O contrato como recorte de política acompanha Execução RAD.</t>
         </is>
       </c>
     </row>
@@ -8486,10 +9073,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
@@ -8502,7 +9089,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Deixou de ser só cadastro: ganhou a gestão de acesso do fornecedor e a importação em massa, implementadas em 14/09. Score de conformidade e trilha de auditoria seguem depois.</t>
+          <t>Deixou de ser só cadastro: ganhou a gestão de acesso do fornecedor e a importação em massa, implementadas em 14/09. Na revisão de 15/09 saíram a revogação com motivo e a pré-visualização da importação — são refinamentos do fluxo, não o fluxo. Score de conformidade e trilha de auditoria seguem depois.</t>
         </is>
       </c>
     </row>
@@ -8550,10 +9137,10 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -8566,7 +9153,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Recortado em 14/09: entram o painel inicial, a listagem dos documentos contra o comprador, os comprovantes de pagamento e o acesso por convite. O resto do portal — inclusive o que já está implementado — fica para depois. Ver seção 05.</t>
+          <t>Recortado em 14/09 e ampliado em 15/09: entram o painel inicial, a listagem dos documentos contra o comprador, os comprovantes de pagamento, o acesso por convite e — pela revisão — o envio de comprovante RAD/PIX. O fornecedor deixa de só se informar e passa a responder. Ver seção 06.</t>
         </is>
       </c>
     </row>
@@ -8614,10 +9201,10 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -8630,7 +9217,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>O corte mais duro: 4 de 15. O MVP precisa conseguir gerar a guia, não otimizar quando gerá-la. O vínculo com a conexão de destino volta ao M1: sem tela de conexões, não há o que vincular.</t>
+          <t>O corte mais duro, afrouxado em 15/09: de 4 para 7 de 15. Entram a orquestração por CNPJ, por contrato e a auditoria com diff campo a campo — decidir de quem gerar a guia passa a ser do MVP; decidir quando, por faixa de valor e base de comparação, continua fora.</t>
         </is>
       </c>
     </row>
@@ -8646,10 +9233,10 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
@@ -8662,7 +9249,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Nenhuma das 16 no M0, por revisão de 14/09: no primeiro momento a configuração é por variável de ambiente, e não por tela. As quatro integrações externas a desenvolver seguem em M0 — ver seção 06.</t>
+          <t>Duas das 16 no M0, pelas revisões de 14 e 15/09: o catálogo dos contextos e os comprovantes recebidos do ERP. O resto da gestão — conexões, credenciais, escopos, log — fica em M1, com a configuração por variável de ambiente. As quatro integrações externas a desenvolver seguem em M0 — ver seção 07.</t>
         </is>
       </c>
     </row>
@@ -8678,10 +9265,10 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -8694,7 +9281,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>A prova de que o recolhimento aconteceu. Sem conciliação, o crédito é uma afirmação sem lastro.</t>
+          <t>A prova de que o recolhimento aconteceu. Sem conciliação, o crédito é uma afirmação sem lastro. Com a revisão de 15/09 o módulo entra inteiro: a próxima ação sugerida e o recorte por múltiplos períodos completam o que faltava.</t>
         </is>
       </c>
     </row>
@@ -8777,10 +9364,10 @@
         <v>8</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0</v>
@@ -8790,7 +9377,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>A régua de cobrança entra no M0 por decisão de 14/09: cobrança não feita é crédito perdido. Relatórios agendados e ITSM ficam em M1 — esses automatizam trabalho, não protegem crédito.</t>
+          <t>A régua de cobrança entra no M0 por decisão de 14/09: cobrança não feita é crédito perdido. Relatórios agendados ficam em M1 e a integração ITSM desceu a M2 em 15/09 — abrir chamado é rotina de time grande, não do piloto.</t>
         </is>
       </c>
     </row>
@@ -8822,7 +9409,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Multiusuário interno é consequência de adoção. A exceção é o painel de acessos externos, que entrou no M0 junto com o acesso do fornecedor.</t>
+          <t>Multiusuário interno é consequência de adoção. A exceção é o painel de acessos externos, que entrou no M0 junto com o acesso do fornecedor — e foi confirmado na revisão de 15/09.</t>
         </is>
       </c>
     </row>
@@ -8833,13 +9420,13 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>2</v>
@@ -8859,7 +9446,1040 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Revisão</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Revisor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Módulo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Funcionalidade</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>De</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Para</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Movimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Créditos IBS/CBS</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Top 5 e Top 10 fornecedores</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Pagamentos RAD</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Gestão de colunas e exportação CSV</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>adiada</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Pagamentos RAD</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Aba Execução Programada</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Inconsistências</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Filtros multiselect por tipo e DF</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>adiada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Inconsistências</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Atribuição de responsável</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Inteligência</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Score de risco por fornecedor (0–100)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Inteligência</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Critério: créditos em risco ÷ total</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Inteligência</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Score ≥ 70 → badge verde (baixo risco)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Inteligência</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Ranking Top 5 Melhores e Top 5 Piores</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Inteligência</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Mapa de bolhas risco × volume</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Contratos</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Split Payment — retenção na liquidação</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>adiada</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Fornecedores</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Revogação com motivo e trilha</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>adiada</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Fornecedores</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Pré-visualização e relatório da importação</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>adiada</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Portal Fornecedor</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Envio de comprovante RAD/PIX</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Execução RAD</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Orquestração por CNPJ</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Execução RAD</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Orquestração por contrato</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Execução RAD</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Auditoria com diff campo a campo</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Integrações</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Catálogo dos seis contextos da API</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Integrações</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Comprovantes recebidos do ERP</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Conciliação</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Próxima ação sugerida por documento</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Conciliação</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Recorte por múltiplos períodos</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>antecipada</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Automações</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Integração ITSM por evento</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>adiada</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Revisão de priorização</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Toshio</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Usuários e Acessos</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Painel de acessos externos</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>mantida</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8867,250 +10487,262 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>O critério</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr"/>
+      <c r="B1" s="18" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr"/>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr"/>
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Uma funcionalidade entra no MVP se a cadeia mínima do crédito não se fecha sem ela: o documento entra · o método de pagamento é conhecido · o tributo é recolhido · o recolhimento é confirmado · o crédito é apropriado · o que falhou vira tratável.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Consequência</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Analytics, FCT e Inteligência ficam fora do MVP mesmo estando prontos. Eles explicam o crédito; não o garantem. Prontidão não é argumento de prioridade.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>As quatro faixas</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr"/>
+      <c r="B5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>MVP — a cadeia do crédito, ponta a ponta, para uma operação e um time pequeno.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Escala — o que tira o operador do meio: orquestração, ERP, portal, automações, multiusuário.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Inteligência — projeção, score e assistente, sobre a base que o M0 e o M1 produzem.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Fora</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Qualidade de engenharia transversal. Entra junto com o que precisa dela.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Como preencher</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr"/>
+      <c r="B11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Faixa revisada</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Só quando discordar da proposta. Escolha M0, M1, M2 ou Fora na lista.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Concorda?</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Sim ou Não. Em branco significa "ainda não revisei" — é assim que se sabe o que falta.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Comentário</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>O porquê. Uma linha basta; é ela que sustenta a mudança de faixa na próxima versão.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>"Mapa" está no Mapa de Funcionalidades. "Nova" ainda não existe no produto e entra na priorização mesmo assim.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Prioridade</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Ordem de construção dentro do M0, onde o módulo é grande demais para entrar de uma vez.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Faixa anterior</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Preenchida quando a faixa já foi revisada uma vez. A coluna ao lado diz quem revisou e quando; o registro completo está na aba Revisões.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Depois de revisar</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr"/>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr"/>
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Devolva a planilha preenchida. As faixas revisadas voltam para tools/gerar-priorizacao.py, que regenera a página — a planilha é a entrada da revisão, nunca a fonte da verdade.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Fonte da verdade</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>O inventário é o Mapa de Funcionalidades; a priorização é o gerador. Esta planilha é uma fotografia dos dois, tirada na data abaixo.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Esta fotografia</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Versão</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>v2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>15/09/2026</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Mapa de Funcionalidades v2.1</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>192 funcionalidades · 20 módulos · 183 do mapa + 9 novas</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>M0 · M1 · M2 · Fora</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>102 · 62 · 26 · 2</t>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>113 · 55 · 22 · 2</t>
         </is>
       </c>
     </row>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Como revisar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$M$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$M$194</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revisões'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2280,17 +2280,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Inconsistências</t>
+          <t>Pagamentos RAD</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Cards DF-cêntricos (rfId opcional)</t>
+          <t>Aviso ao fornecedor do recolhimento</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Múltiplas inconsistências por DF</t>
+          <t>Cards DF-cêntricos (rfId opcional)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Taxonomia CAPUR IBS/CBS por imposto</t>
+          <t>Múltiplas inconsistências por DF</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Taxonomia CFIN IBS/CBS por imposto</t>
+          <t>Taxonomia CAPUR IBS/CBS por imposto</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Kanban: Aberta → Resolvida / Glosada</t>
+          <t>Taxonomia CFIN IBS/CBS por imposto</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Atribuição de responsável</t>
+          <t>Kanban: Aberta → Resolvida / Glosada</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2508,16 +2508,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr"/>
       <c r="K46" s="6" t="inlineStr"/>
       <c r="L46" s="6" t="inlineStr"/>
@@ -2539,7 +2531,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Histórico de alterações</t>
+          <t>Atribuição de responsável</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2557,8 +2549,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="3" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="6" t="inlineStr"/>
       <c r="L47" s="6" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Diagnóstico guiado — árvore de decisão</t>
+          <t>Histórico de alterações</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2593,9 +2593,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr"/>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Filtros multiselect por tipo e DF</t>
+          <t>Diagnóstico guiado — árvore de decisão</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2639,16 +2639,8 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="6" t="inlineStr"/>
       <c r="L49" s="6" t="inlineStr"/>
@@ -2665,17 +2657,17 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Ingestão de DFs</t>
+          <t>Inconsistências</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Upload CSV posicional (NF-e · CT-e · NFS-e)</t>
+          <t>Filtros multiselect por tipo e DF</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2683,13 +2675,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="3" t="inlineStr"/>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J50" s="3" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr"/>
       <c r="L50" s="6" t="inlineStr"/>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Suporte a Entrada e Saída</t>
+          <t>Upload CSV posicional (NF-e · CT-e · NFS-e)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Pré-visualização antes de confirmar</t>
+          <t>Suporte a Entrada e Saída</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Validação binária: Importado / Inconsistência</t>
+          <t>Pré-visualização antes de confirmar</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Stub DF para documentos rejeitados</t>
+          <t>Validação binária: Importado / Inconsistência</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Card de inconsistência automático</t>
+          <t>Stub DF para documentos rejeitados</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Ingestão por API com credencial própria</t>
+          <t>Card de inconsistência automático</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2947,22 +2947,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>FCT — Fluxo de Caixa Tributário</t>
+          <t>Ingestão de DFs</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Forecast de Fluxo Fiscal</t>
+          <t>Ingestão por API com credencial própria</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2970,9 +2970,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Média móvel progressiva</t>
+          <t>Forecast de Fluxo Fiscal</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Corte realizado / projeção na data atual</t>
+          <t>Média móvel progressiva</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Forecast de Aproveitamento de Crédito</t>
+          <t>Corte realizado / projeção na data atual</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Insights: melhor mês · tendência · perda projetada</t>
+          <t>Forecast de Aproveitamento de Crédito</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Tabela mensal de aproveitamento</t>
+          <t>Insights: melhor mês · tendência · perda projetada</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Retry automático de renderização</t>
+          <t>Tabela mensal de aproveitamento</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Inteligência</t>
+          <t>FCT — Fluxo de Caixa Tributário</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Score de risco por fornecedor (0–100)</t>
+          <t>Retry automático de renderização</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3257,21 +3257,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="3" t="inlineStr"/>
       <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
@@ -3293,7 +3285,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Critério: créditos em risco ÷ total</t>
+          <t>Score de risco por fornecedor (0–100)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -3342,7 +3334,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Score ≥ 70 → badge verde (baixo risco)</t>
+          <t>Critério: créditos em risco ÷ total</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3391,7 +3383,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Ranking Top 5 Melhores e Top 5 Piores</t>
+          <t>Score ≥ 70 → badge verde (baixo risco)</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -3440,7 +3432,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Mapa de bolhas risco × volume</t>
+          <t>Ranking Top 5 Melhores e Top 5 Piores</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -3489,7 +3481,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Tabela mensal de crédito por fornecedor</t>
+          <t>Mapa de bolhas risco × volume</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -3502,13 +3494,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
@@ -3520,22 +3520,22 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Contratos</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Modelo RAD — adquirente recolhe o tributo</t>
+          <t>Tabela mensal de crédito por fornecedor</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3543,9 +3543,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr"/>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Modelo Fornecedor — fornecedor recolhe</t>
+          <t>Modelo RAD — adquirente recolhe o tributo</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Multi-contratos por fornecedor</t>
+          <t>Modelo Fornecedor — fornecedor recolhe</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Vínculo contrato → obrigações de comprovante</t>
+          <t>Multi-contratos por fornecedor</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Listagem com filtros padronizados</t>
+          <t>Vínculo contrato → obrigações de comprovante</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Contrato como recorte de política RAD</t>
+          <t>Listagem com filtros padronizados</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3748,9 +3748,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Modelo Split Payment — retenção na liquidação</t>
+          <t>Contrato como recorte de política RAD</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3789,21 +3789,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
       <c r="J76" s="3" t="inlineStr"/>
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
@@ -3820,12 +3812,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Cadastro com razão social anonimizada</t>
+          <t>Modelo Split Payment — retenção na liquidação</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -3838,13 +3830,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr"/>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="6" t="inlineStr"/>
       <c r="L77" s="6" t="inlineStr"/>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>CNPJ formatado XX.XXX.XXX/XXXX-XX</t>
+          <t>Cadastro com razão social anonimizada</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Edição com trilha de auditoria</t>
+          <t>CNPJ formatado XX.XXX.XXX/XXXX-XX</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3920,9 +3920,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr"/>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Multi-contratos no cadastro</t>
+          <t>Edição com trilha de auditoria</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3961,9 +3961,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr"/>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Score de conformidade no cadastro</t>
+          <t>Multi-contratos no cadastro</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -4002,9 +4002,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr"/>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Aba Acessos no cadastro</t>
+          <t>Score de conformidade no cadastro</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -4043,9 +4043,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr"/>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Convite, reenvio e cancelamento</t>
+          <t>Aba Acessos no cadastro</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Revogação com motivo e trilha</t>
+          <t>Convite, reenvio e cancelamento</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -4125,21 +4125,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
       <c r="J84" s="3" t="inlineStr"/>
       <c r="K84" s="6" t="inlineStr"/>
       <c r="L84" s="6" t="inlineStr"/>
@@ -4161,7 +4153,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Importação de fornecedores e grupos por CSV</t>
+          <t>Revogação com motivo e trilha</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -4174,13 +4166,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="3" t="inlineStr"/>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="6" t="inlineStr"/>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Importação de status e de convites em massa</t>
+          <t>Importação de fornecedores e grupos por CSV</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Pré-visualização e relatório da importação</t>
+          <t>Importação de status e de convites em massa</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4256,21 +4256,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G87" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr"/>
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="6" t="inlineStr"/>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4292,12 +4284,12 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Histórico de lotes de importação</t>
+          <t>Pré-visualização e relatório da importação</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4305,13 +4297,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="3" t="inlineStr"/>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J88" s="3" t="inlineStr"/>
       <c r="K88" s="6" t="inlineStr"/>
       <c r="L88" s="6" t="inlineStr"/>
@@ -4328,12 +4328,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Organização</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Hierarquia CNPJ: Matriz + Filiais</t>
+          <t>Histórico de lotes de importação</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Status de conformidade por entidade</t>
+          <t>Hierarquia CNPJ: Matriz + Filiais</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4387,9 +4387,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr"/>
@@ -4415,12 +4415,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Apuração Assistida na sidebar</t>
+          <t>Status de conformidade por entidade</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4428,9 +4428,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr"/>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Filtro Grupo Econômico — sincroniza tudo</t>
+          <t>Apuração Assistida na sidebar</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Auditoria de alterações cadastrais</t>
+          <t>Filtro Grupo Econômico — sincroniza tudo</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4510,9 +4510,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G93" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr"/>
@@ -4528,22 +4528,22 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>DFs filtrados pelo CNPJ próprio</t>
+          <t>Auditoria de alterações cadastrais</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4551,9 +4551,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr"/>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>IBS e CBS separados por RF</t>
+          <t>DFs filtrados pelo CNPJ próprio</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Grupo econômico: Matriz + Filiais</t>
+          <t>IBS e CBS separados por RF</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -4633,9 +4633,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr"/>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Envio de comprovante RAD/PIX</t>
+          <t>Grupo econômico: Matriz + Filiais</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4674,21 +4674,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
+      <c r="G97" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr"/>
       <c r="K97" s="6" t="inlineStr"/>
       <c r="L97" s="6" t="inlineStr"/>
@@ -4710,7 +4702,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Contestação de DFs vencidos</t>
+          <t>Envio de comprovante RAD/PIX</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -4723,13 +4715,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr"/>
-      <c r="I98" s="3" t="inlineStr"/>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J98" s="3" t="inlineStr"/>
       <c r="K98" s="6" t="inlineStr"/>
       <c r="L98" s="6" t="inlineStr"/>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Chat com adquirente</t>
+          <t>Contestação de DFs vencidos</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Score de conformidade próprio</t>
+          <t>Chat com adquirente</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Período multi-select</t>
+          <t>Score de conformidade próprio</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4846,9 +4846,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr"/>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Contratos globais visíveis</t>
+          <t>Período multi-select</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4887,9 +4887,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr"/>
@@ -4915,12 +4915,12 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Aviso de recolhimento assumido pelo adquirente</t>
+          <t>Contratos globais visíveis</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Convite e acesso por senha própria</t>
+          <t>Aviso de recolhimento assumido pelo adquirente</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4969,9 +4969,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr"/>
@@ -4997,12 +4997,12 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Papéis Responsável e Leitura</t>
+          <t>Convite e acesso por senha própria</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -5010,9 +5010,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G105" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr"/>
@@ -5038,22 +5038,22 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Painel inicial do fornecedor</t>
+          <t>Papéis Responsável e Leitura</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr"/>
@@ -5079,12 +5079,12 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Comprovantes de pagamento disponíveis ao fornecedor</t>
+          <t>Painel inicial do fornecedor</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
@@ -5115,22 +5115,22 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Tela de login</t>
+          <t>Comprovantes de pagamento disponíveis ao fornecedor</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Perfis: Cliente e Fornecedor</t>
+          <t>Tela de login</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Troca de perfil in-session</t>
+          <t>Perfis: Cliente e Fornecedor</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Tokens CSS globais + PALETTE JS</t>
+          <t>Troca de perfil in-session</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Sidebar teal colapsável + localStorage</t>
+          <t>Tokens CSS globais + PALETTE JS</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Tema claro/escuro automático</t>
+          <t>Sidebar teal colapsável + localStorage</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>shBuildFilterPanel — filtros padronizados</t>
+          <t>Tema claro/escuro automático</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>RF Core — 10 colunas uniformes</t>
+          <t>shBuildFilterPanel — filtros padronizados</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>ESC fecha qualquer modal</t>
+          <t>RF Core — 10 colunas uniformes</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Tooltip de coluna como padrão de projeto</t>
+          <t>ESC fecha qualquer modal</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -5502,9 +5502,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G117" s="11" t="inlineStr">
-        <is>
-          <t>Fora</t>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Documentação de produto dentro da aplicação</t>
+          <t>Tooltip de coluna como padrão de projeto</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Selo de modo demonstração</t>
+          <t>Documentação de produto dentro da aplicação</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -5584,9 +5584,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>Fora</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr"/>
@@ -5612,17 +5612,17 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Login via SSO corporativo</t>
+          <t>Selo de modo demonstração</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>Nova</t>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -5643,27 +5643,27 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Políticas de execução sem limite de quantidade</t>
+          <t>Login via SSO corporativo</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por CNPJ</t>
+          <t>Políticas de execução sem limite de quantidade</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -5712,16 +5712,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="H122" s="9" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr"/>
       <c r="J122" s="3" t="inlineStr"/>
       <c r="K122" s="6" t="inlineStr"/>
       <c r="L122" s="6" t="inlineStr"/>
@@ -5743,7 +5735,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por contrato</t>
+          <t>Orquestração por CNPJ</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -5792,7 +5784,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por faixa de valor</t>
+          <t>Orquestração por contrato</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -5805,13 +5797,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G124" s="10" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr"/>
-      <c r="I124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J124" s="3" t="inlineStr"/>
       <c r="K124" s="6" t="inlineStr"/>
       <c r="L124" s="6" t="inlineStr"/>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Quatro bases de comparação da faixa</t>
+          <t>Orquestração por faixa de valor</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Três modos de operação</t>
+          <t>Quatro bases de comparação da faixa</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Janela de execução configurável</t>
+          <t>Três modos de operação</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -5928,9 +5928,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Critérios de inclusão por valor e flag</t>
+          <t>Janela de execução configurável</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Simulação da próxima execução</t>
+          <t>Critérios de inclusão por valor e flag</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -6010,9 +6010,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G129" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr"/>
@@ -6038,12 +6038,12 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Detecção de cobertura repetida</t>
+          <t>Simulação da próxima execução</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Alerta de sobreposição entre modelos</t>
+          <t>Detecção de cobertura repetida</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Listagem de políticas com lote ao vivo</t>
+          <t>Alerta de sobreposição entre modelos</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -6133,9 +6133,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr"/>
@@ -6161,12 +6161,12 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Ativação e pausa em massa</t>
+          <t>Listagem de políticas com lote ao vivo</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -6174,9 +6174,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G133" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr"/>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Auditoria com diff campo a campo</t>
+          <t>Ativação e pausa em massa</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -6215,21 +6215,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H134" s="9" t="inlineStr">
+      <c r="G134" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H134" s="3" t="inlineStr"/>
+      <c r="I134" s="3" t="inlineStr"/>
       <c r="J134" s="3" t="inlineStr"/>
       <c r="K134" s="6" t="inlineStr"/>
       <c r="L134" s="6" t="inlineStr"/>
@@ -6251,12 +6243,12 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Vínculo com a conexão de destino</t>
+          <t>Auditoria com diff campo a campo</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6264,13 +6256,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G135" s="10" t="inlineStr">
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr"/>
-      <c r="I135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J135" s="3" t="inlineStr"/>
       <c r="K135" s="6" t="inlineStr"/>
       <c r="L135" s="6" t="inlineStr"/>
@@ -6287,12 +6287,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Catálogo dos seis contextos da API</t>
+          <t>Vínculo com a conexão de destino</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -6305,21 +6305,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H136" s="9" t="inlineStr">
+      <c r="G136" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr"/>
       <c r="J136" s="3" t="inlineStr"/>
       <c r="K136" s="6" t="inlineStr"/>
       <c r="L136" s="6" t="inlineStr"/>
@@ -6341,7 +6333,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Conexões nas duas direções</t>
+          <t>Catálogo dos seis contextos da API</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
@@ -6354,13 +6346,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G137" s="10" t="inlineStr">
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="6" t="inlineStr"/>
       <c r="L137" s="6" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Assistente de nova conexão em três passos</t>
+          <t>Conexões nas duas direções</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Emissão de credencial de API</t>
+          <t>Assistente de nova conexão em três passos</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Exibição única do segredo</t>
+          <t>Emissão de credencial de API</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Escopos por contexto</t>
+          <t>Exibição única do segredo</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Rotação com janela de sobreposição</t>
+          <t>Escopos por contexto</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Exemplo da primeira chamada</t>
+          <t>Rotação com janela de sobreposição</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Alcance por CNPJ</t>
+          <t>Exemplo da primeira chamada</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Health check por conexão</t>
+          <t>Alcance por CNPJ</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Sonda ativa e observação passiva</t>
+          <t>Health check por conexão</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Histórico de incidentes</t>
+          <t>Sonda ativa e observação passiva</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Log de entregas com inspeção de payload</t>
+          <t>Histórico de incidentes</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Reenvio de entrega</t>
+          <t>Log de entregas com inspeção de payload</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Comprovantes recebidos do ERP</t>
+          <t>Reenvio de entrega</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6887,21 +6887,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="H150" s="9" t="inlineStr">
+      <c r="G150" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H150" s="3" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr"/>
       <c r="J150" s="3" t="inlineStr"/>
       <c r="K150" s="6" t="inlineStr"/>
       <c r="L150" s="6" t="inlineStr"/>
@@ -6923,12 +6915,12 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Teste de conexão</t>
+          <t>Comprovantes recebidos do ERP</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6936,13 +6928,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G151" s="10" t="inlineStr">
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr"/>
-      <c r="I151" s="3" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J151" s="3" t="inlineStr"/>
       <c r="K151" s="6" t="inlineStr"/>
       <c r="L151" s="6" t="inlineStr"/>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Integração com a Receita Federal — CBS</t>
+          <t>Teste de conexão</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr"/>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Integração com o Comitê Gestor — IBS</t>
+          <t>Integração com a Receita Federal — CBS</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Integração RAD</t>
+          <t>Integração com o Comitê Gestor — IBS</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Integração Databricks para comprovantes</t>
+          <t>Integração RAD</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
@@ -7118,27 +7118,27 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Painel unificado da jornada do documento</t>
+          <t>Integração Databricks para comprovantes</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Confronto com a Apuração Assistida</t>
+          <t>Painel unificado da jornada do documento</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Conciliação financeira pelos comprovantes</t>
+          <t>Confronto com a Apuração Assistida</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Sequenciamento das duas conciliações</t>
+          <t>Conciliação financeira pelos comprovantes</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -7292,12 +7292,12 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Próxima ação sugerida por documento</t>
+          <t>Sequenciamento das duas conciliações</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7310,16 +7310,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="H160" s="9" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H160" s="3" t="inlineStr"/>
+      <c r="I160" s="3" t="inlineStr"/>
       <c r="J160" s="3" t="inlineStr"/>
       <c r="K160" s="6" t="inlineStr"/>
       <c r="L160" s="6" t="inlineStr"/>
@@ -7341,12 +7333,12 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Listagem de registros com oito filtros</t>
+          <t>Próxima ação sugerida por documento</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7359,8 +7351,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr"/>
-      <c r="I161" s="3" t="inlineStr"/>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J161" s="3" t="inlineStr"/>
       <c r="K161" s="6" t="inlineStr"/>
       <c r="L161" s="6" t="inlineStr"/>
@@ -7382,12 +7382,12 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Propagação do resultado para documento e registros</t>
+          <t>Listagem de registros com oito filtros</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Recorte por múltiplos períodos</t>
+          <t>Propagação do resultado para documento e registros</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7441,16 +7441,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="H163" s="9" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H163" s="3" t="inlineStr"/>
+      <c r="I163" s="3" t="inlineStr"/>
       <c r="J163" s="3" t="inlineStr"/>
       <c r="K163" s="6" t="inlineStr"/>
       <c r="L163" s="6" t="inlineStr"/>
@@ -7467,17 +7459,17 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Resumo por tributo na competência</t>
+          <t>Recorte por múltiplos períodos</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -7490,8 +7482,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr"/>
-      <c r="I164" s="3" t="inlineStr"/>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J164" s="3" t="inlineStr"/>
       <c r="K164" s="6" t="inlineStr"/>
       <c r="L164" s="6" t="inlineStr"/>
@@ -7513,12 +7513,12 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Posição detalhada de créditos e débitos</t>
+          <t>Resumo por tributo na competência</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7526,9 +7526,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G165" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr"/>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Cálculo da competência</t>
+          <t>Posição detalhada de créditos e débitos</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7567,9 +7567,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G166" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G166" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Conclusão e reabertura da apuração</t>
+          <t>Cálculo da competência</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Abas Resumo, Créditos e Débitos</t>
+          <t>Conclusão e reabertura da apuração</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Navegação entre competências</t>
+          <t>Abas Resumo, Créditos e Débitos</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Exportação da apuração</t>
+          <t>Navegação entre competências</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7731,9 +7731,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G170" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr"/>
@@ -7749,17 +7749,17 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Assistente Tributário</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Chat livre sobre a legislação</t>
+          <t>Exportação da apuração</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -7772,9 +7772,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G171" s="8" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="G171" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr"/>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Diagnóstico guiado por árvore de decisão</t>
+          <t>Chat livre sobre a legislação</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Fontes indexadas com link para a norma</t>
+          <t>Diagnóstico guiado por árvore de decisão</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Histórico de conversas</t>
+          <t>Fontes indexadas com link para a norma</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -7913,22 +7913,22 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Assistente Tributário</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Relatórios agendados por módulo</t>
+          <t>Histórico de conversas</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7936,9 +7936,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G175" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr"/>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Ativação, edição e exclusão de agendamento</t>
+          <t>Relatórios agendados por módulo</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Integração ITSM por evento</t>
+          <t>Ativação, edição e exclusão de agendamento</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -8018,21 +8018,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G177" s="8" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="H177" s="9" t="inlineStr">
+      <c r="G177" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="H177" s="3" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr"/>
       <c r="J177" s="3" t="inlineStr"/>
       <c r="K177" s="6" t="inlineStr"/>
       <c r="L177" s="6" t="inlineStr"/>
@@ -8054,7 +8046,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Mapeamento dos campos do chamado</t>
+          <t>Integração ITSM por evento</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -8067,13 +8059,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G178" s="10" t="inlineStr">
+      <c r="G178" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="H178" s="3" t="inlineStr"/>
-      <c r="I178" s="3" t="inlineStr"/>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="J178" s="3" t="inlineStr"/>
       <c r="K178" s="6" t="inlineStr"/>
       <c r="L178" s="6" t="inlineStr"/>
@@ -8095,12 +8095,12 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Histórico de chamados abertos</t>
+          <t>Mapeamento dos campos do chamado</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Régua de cobrança pré-vencimento</t>
+          <t>Histórico de chamados abertos</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -8149,9 +8149,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G180" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G180" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Régua de cobrança pós-vencimento</t>
+          <t>Régua de cobrança pré-vencimento</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Etapas da régua com canal e condição</t>
+          <t>Régua de cobrança pós-vencimento</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Template de mensagem com variáveis</t>
+          <t>Etapas da régua com canal e condição</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Disparos por fornecedor e etapa</t>
+          <t>Template de mensagem com variáveis</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Auditoria da régua com motivo</t>
+          <t>Disparos por fornecedor e etapa</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8382,17 +8382,17 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Motor de execução das automações</t>
+          <t>Auditoria da régua com motivo</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>Nova</t>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Envio de e-mail transacional</t>
+          <t>Motor de execução das automações</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
@@ -8459,27 +8459,27 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Listagem de membros da organização</t>
+          <t>Envio de e-mail transacional</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
-        </is>
-      </c>
-      <c r="F188" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="G188" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="F188" s="9" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr"/>
@@ -8505,12 +8505,12 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Perfis de acesso</t>
+          <t>Listagem de membros da organização</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Convite de usuário</t>
+          <t>Perfis de acesso</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Revogação e reativação de acesso</t>
+          <t>Convite de usuário</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Abas por situação do acesso</t>
+          <t>Revogação e reativação de acesso</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Painel de acessos externos</t>
+          <t>Abas por situação do acesso</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
@@ -8682,29 +8682,70 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="G193" s="5" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="G193" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr"/>
-      <c r="I193" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I193" s="3" t="inlineStr"/>
       <c r="J193" s="3" t="inlineStr"/>
       <c r="K193" s="6" t="inlineStr"/>
       <c r="L193" s="6" t="inlineStr"/>
       <c r="M193" s="7" t="inlineStr"/>
     </row>
+    <row r="194">
+      <c r="A194" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Gestão</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Usuários e Acessos</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>Painel de acessos externos</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="inlineStr"/>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
+      <c r="J194" s="3" t="inlineStr"/>
+      <c r="K194" s="6" t="inlineStr"/>
+      <c r="L194" s="6" t="inlineStr"/>
+      <c r="M194" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M193"/>
+  <autoFilter ref="A1:M194"/>
   <dataValidations count="2">
-    <dataValidation sqref="K2:K193" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
+    <dataValidation sqref="K2:K194" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
       <formula1>"M0,M1,M2,Fora"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L193" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
+    <dataValidation sqref="L2:L194" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8881,7 +8922,7 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>5</v>
@@ -8893,11 +8934,11 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Entra a guia, o comprovante e o rastro dos três status. A entrega ao ERP passa ao M0 junto com a API. Na revisão de 15/09 a aba Execução Programada entrou e a gestão de colunas saiu: o piloto precisa ver o que está agendado, não configurar a própria grade.</t>
+          <t>Entra a guia, o comprovante e o rastro dos três status. A entrega ao ERP passa ao M0 junto com a API. Na revisão de 15/09 a aba Execução Programada entrou e a gestão de colunas saiu: o piloto precisa ver o que está agendado, não configurar a própria grade. Entra também o aviso ao fornecedor do recolhimento — sem ele o fornecedor paga o mesmo tributo de novo.</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9461,7 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D23" s="13" t="n">
         <v>55</v>
@@ -9432,7 +9473,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -10694,7 +10735,7 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>v2.1</t>
+          <t>v2.2</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10771,7 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>192 funcionalidades · 20 módulos · 183 do mapa + 9 novas</t>
+          <t>193 funcionalidades · 20 módulos · 184 do mapa + 9 novas</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10783,7 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>113 · 55 · 22 · 2</t>
+          <t>114 · 55 · 22 · 2</t>
         </is>
       </c>
     </row>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -2757,9 +2757,9 @@
           <t>Toda inconsistência tem vínculo obrigatório ao DF de origem. O campo rfId é opcional: nulo para inconsistências geradas antes da criação dos RFs (falhas de ingestão); preenchido quando a inconsistência é específica de um RF já criado (pós-apuração ou pós-conciliação financeira).</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2808,9 +2808,9 @@
           <t>Um mesmo DF pode acumular inconsistências geradas em etapas distintas do ciclo de vida (ex: divergência de valor IBS na apuração E comprovante CBS ausente na conciliação). Todas exibidas simultaneamente como pills nas listagens.</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2859,9 +2859,9 @@
           <t>Inconsistências de apuração identificadas individualmente por imposto: capur_ibs_valor (valor divergente), capur_ibs_aliquota (alíquota divergente), capur_cbs_valor, capur_cbs_aliquota. IBS e CBS apurados de forma independente.</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2910,9 +2910,9 @@
           <t>Inconsistências financeiras identificadas por imposto: cfin_ibs_split (split não executado), cfin_ibs_comprovante (comprovante divergente), cfin_cbs_split, cfin_cbs_comprovante. Inclui "Sem Comprovante" para contratos RAD sem anexo.</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2961,9 +2961,9 @@
           <t>Quadro kanban com colunas: Aberta, Em Análise, Aguardando Emitente, Resolvida e Glosada. Cards movidos entre colunas registram data e usuário da transição.</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3012,9 +3012,9 @@
           <t>Card de inconsistência pode ser atribuído a um operador específico, com campo de responsável e registro de data de atribuição.</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3071,9 +3071,9 @@
           <t>Modal expandido em dois painéis: dados da inconsistência e ações sugeridas à esquerda; histórico cronológico completo de transições, atribuições e comentários à direita.</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3122,9 +3122,9 @@
           <t>Assistente de diagnóstico com perguntas sequenciais para identificar o tipo de inconsistência: fluxo de entrada ou saída? Etapa de apuração (CAPUR) ou financeira (CFIN)? Qual imposto (IBS ou CBS)?</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3173,9 +3173,9 @@
           <t>Filtros combinados por tipo de inconsistência (taxonomia CAPUR/CFIN) e DF de origem, com suporte a seleção múltipla.</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>PRD do módulo, publicado à parte</t>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -10743,125 +10743,116 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Como revisar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revisões'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O194"/>
+  <dimension ref="A1:O209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10692,13 +10692,778 @@
       <c r="N194" s="7" t="inlineStr"/>
       <c r="O194" s="8" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>Saldo credor por período e tributo</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I195" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J195" s="3" t="inlineStr"/>
+      <c r="K195" s="3" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr"/>
+      <c r="M195" s="7" t="inlineStr"/>
+      <c r="N195" s="7" t="inlineStr"/>
+      <c r="O195" s="8" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>Comparar compensar e ressarcir</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I196" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J196" s="3" t="inlineStr"/>
+      <c r="K196" s="3" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr"/>
+      <c r="M196" s="7" t="inlineStr"/>
+      <c r="N196" s="7" t="inlineStr"/>
+      <c r="O196" s="8" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Declarar e cancelar a intenção</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I197" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J197" s="3" t="inlineStr"/>
+      <c r="K197" s="3" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr"/>
+      <c r="M197" s="7" t="inlineStr"/>
+      <c r="N197" s="7" t="inlineStr"/>
+      <c r="O197" s="8" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>Montar o pedido de CBS por documento</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I198" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J198" s="3" t="inlineStr"/>
+      <c r="K198" s="3" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr"/>
+      <c r="M198" s="7" t="inlineStr"/>
+      <c r="N198" s="7" t="inlineStr"/>
+      <c r="O198" s="8" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I199" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J199" s="3" t="inlineStr"/>
+      <c r="K199" s="3" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr"/>
+      <c r="M199" s="7" t="inlineStr"/>
+      <c r="N199" s="7" t="inlineStr"/>
+      <c r="O199" s="8" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>Listagem de pedidos do tributo</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I200" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J200" s="3" t="inlineStr"/>
+      <c r="K200" s="3" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr"/>
+      <c r="M200" s="7" t="inlineStr"/>
+      <c r="N200" s="7" t="inlineStr"/>
+      <c r="O200" s="8" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>Acompanhar análise e fiscalização</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I201" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J201" s="3" t="inlineStr"/>
+      <c r="K201" s="3" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr"/>
+      <c r="M201" s="7" t="inlineStr"/>
+      <c r="N201" s="7" t="inlineStr"/>
+      <c r="O201" s="8" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t>Registrar decisão e cancelamento</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I202" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="3" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr"/>
+      <c r="M202" s="7" t="inlineStr"/>
+      <c r="N202" s="7" t="inlineStr"/>
+      <c r="O202" s="8" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>Conciliar o recebimento com Selic</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I203" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J203" s="3" t="inlineStr"/>
+      <c r="K203" s="3" t="inlineStr"/>
+      <c r="L203" s="3" t="inlineStr"/>
+      <c r="M203" s="7" t="inlineStr"/>
+      <c r="N203" s="7" t="inlineStr"/>
+      <c r="O203" s="8" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>Previsão de entrada de caixa por tributo</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I204" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J204" s="3" t="inlineStr"/>
+      <c r="K204" s="3" t="inlineStr"/>
+      <c r="L204" s="3" t="inlineStr"/>
+      <c r="M204" s="7" t="inlineStr"/>
+      <c r="N204" s="7" t="inlineStr"/>
+      <c r="O204" s="8" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>Alertas de prazo do ressarcimento</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I205" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J205" s="3" t="inlineStr"/>
+      <c r="K205" s="3" t="inlineStr"/>
+      <c r="L205" s="3" t="inlineStr"/>
+      <c r="M205" s="7" t="inlineStr"/>
+      <c r="N205" s="7" t="inlineStr"/>
+      <c r="O205" s="8" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>Conferência do saldo com a Receita (CBS)</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I206" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J206" s="3" t="inlineStr"/>
+      <c r="K206" s="3" t="inlineStr"/>
+      <c r="L206" s="3" t="inlineStr"/>
+      <c r="M206" s="7" t="inlineStr"/>
+      <c r="N206" s="7" t="inlineStr"/>
+      <c r="O206" s="8" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>Trilha de auditoria do pedido</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-13 Auditar</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I207" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J207" s="3" t="inlineStr"/>
+      <c r="K207" s="3" t="inlineStr"/>
+      <c r="L207" s="3" t="inlineStr"/>
+      <c r="M207" s="7" t="inlineStr"/>
+      <c r="N207" s="7" t="inlineStr"/>
+      <c r="O207" s="8" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>Impedimentos do IBS</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I208" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J208" s="3" t="inlineStr"/>
+      <c r="K208" s="3" t="inlineStr"/>
+      <c r="L208" s="3" t="inlineStr"/>
+      <c r="M208" s="7" t="inlineStr"/>
+      <c r="N208" s="7" t="inlineStr"/>
+      <c r="O208" s="8" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>Registrar o pedido de IBS (protocolo)</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I209" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J209" s="3" t="inlineStr"/>
+      <c r="K209" s="3" t="inlineStr"/>
+      <c r="L209" s="3" t="inlineStr"/>
+      <c r="M209" s="7" t="inlineStr"/>
+      <c r="N209" s="7" t="inlineStr"/>
+      <c r="O209" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O194"/>
+  <autoFilter ref="A1:O209"/>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M194" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
+    <dataValidation sqref="M2:M209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
       <formula1>"M0,M1,M2,Fora"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N194" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
+    <dataValidation sqref="N2:N209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10853,6 +11618,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId165"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10864,7 +11644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11559,26 +12339,58 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Fora do M0 por decisão de 18/09/2026. A cadeia do crédito fecha na apropriação; o ressarcimento é o passo seguinte — transformar o saldo que sobrou em dinheiro. E o primeiro pedido real só existe em 2027: saldos de 2026 não são ressarcíveis. Treze funcionalidades em M1, o ciclo que tira o analista da planilha — saldo, intenção, pedido, decisão, recebimento, prazos, conferência e impedimentos. Duas em M2: o comparativo compensar × ressarcir e a previsão de caixa, que explicam a decisão em vez de executá-la. Implementado no protótipo em simulação 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C24" s="15" t="n">
         <v>114</v>
       </c>
-      <c r="D23" s="15" t="n">
-        <v>55</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="F23" s="15" t="n">
+      <c r="D24" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="15" t="n">
-        <v>193</v>
+      <c r="G24" s="15" t="n">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -12864,7 +13676,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>v2.3</t>
+          <t>v2.4</t>
         </is>
       </c>
     </row>
@@ -12876,7 +13688,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
     </row>
@@ -12888,7 +13700,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Mapa de Funcionalidades v2.1</t>
+          <t>Mapa de Funcionalidades v2.3</t>
         </is>
       </c>
     </row>
@@ -12900,7 +13712,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>193 funcionalidades · 20 módulos · 184 do mapa + 9 novas</t>
+          <t>208 funcionalidades · 21 módulos · 199 do mapa + 9 novas</t>
         </is>
       </c>
     </row>
@@ -12912,7 +13724,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>114 · 55 · 22 · 2</t>
+          <t>114 · 68 · 24 · 2</t>
         </is>
       </c>
     </row>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Como revisar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$215</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revisões'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56,12 +56,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00B97A10"/>
+      <color rgb="001D5FCC"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001D5FCC"/>
+      <color rgb="00B97A10"/>
       <sz val="10"/>
     </font>
     <font>
@@ -173,13 +173,13 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,7 +189,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O209"/>
+  <dimension ref="A1:O215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -986,27 +986,27 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Créditos IBS/CBS</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Listagem DFs de entrada — RF Core 10 colunas</t>
+          <t>Card de saldo credor e ressarcimento</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Tabela padronizada com ID RF, Tipo Fiscal (IBS/CBS), DF Vinculado, Entidade, Data, Valor do Tributo, Status do Crédito, Status de Registro, Método de Pagamento e Extinção. Mesma estrutura em todas as listagens de RF do sistema.</t>
+          <t>No Início, CBS e IBS lado a lado — disponível, reservado, em pedido, recebido no ano e próximo prazo —, sem somar os tributos. Leva ao módulo de Ressarcimento.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · F-02 Aba Registros Fiscais — listagem por tributo</t>
+          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1014,9 +1014,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr"/>
@@ -1042,17 +1042,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Filtros avançados em todas as colunas</t>
+          <t>Listagem DFs de entrada — RF Core 10 colunas</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Painel colapsável com filtros de busca textual, status (single/multi-select), tipo fiscal, contrato, entidade, range de data e range de valor em todas as colunas exibidas.</t>
+          <t>Tabela padronizada com ID RF, Tipo Fiscal (IBS/CBS), DF Vinculado, Entidade, Data, Valor do Tributo, Status do Crédito, Status de Registro, Método de Pagamento e Extinção. Mesma estrutura em todas as listagens de RF do sistema.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · F-03 Painel de filtros de Registros Fiscais — 22 campos</t>
+          <t>PRD de Crédito IBS/CBS · F-02 Aba Registros Fiscais — listagem por tributo</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1093,22 +1093,22 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Coluna Inconsistências por DF</t>
+          <t>Filtros avançados em todas as colunas</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Pills vermelhos com o tipo de cada inconsistência vinculada ao DF (ex: "Valor IBS divergente · Split CBS não executado"). Exibe todas as inconsistências ativas simultaneamente.</t>
+          <t>Painel colapsável com filtros de busca textual, status (single/multi-select), tipo fiscal, contrato, entidade, range de data e range de valor em todas as colunas exibidas.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · F-04 Aba Documentos Fiscais — visão consolidada por DF</t>
+          <t>PRD de Crédito IBS/CBS · F-03 Painel de filtros de Registros Fiscais — 22 campos</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Classificação CP / LP / Vencidos</t>
+          <t>Coluna Inconsistências por DF</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Créditos a apropriar classificados por prazo até o vencimento: Curto Prazo (≤30 dias do último dia do mês seguinte à emissão), Longo Prazo (&gt;30 dias) e Vencidos (prazo expirado). DFs vencidos excluídos das categorias CP/LP.</t>
+          <t>Pills vermelhos com o tipo de cada inconsistência vinculada ao DF (ex: "Valor IBS divergente · Split CBS não executado"). Exibe todas as inconsistências ativas simultaneamente.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · Seção 05 Arquitetura da tela</t>
+          <t>PRD de Crédito IBS/CBS · F-04 Aba Documentos Fiscais — visão consolidada por DF</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1195,22 +1195,22 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Calendário heatmap de vencimentos</t>
+          <t>Classificação CP / LP / Vencidos</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Visualização mensal navegável com intensidade de cor (tons teal) proporcional ao volume de créditos vencendo em cada dia. Clique em qualquer dia abre modal com a listagem dos DFs cujo vencimento cai naquela data.</t>
+          <t>Créditos a apropriar classificados por prazo até o vencimento: Curto Prazo (≤30 dias do último dia do mês seguinte à emissão), Longo Prazo (&gt;30 dias) e Vencidos (prazo expirado). DFs vencidos excluídos das categorias CP/LP.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · Seção 08 Gráficos e visualizações</t>
+          <t>PRD de Crédito IBS/CBS · Seção 05 Arquitetura da tela</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1218,9 +1218,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Badge de método de extinção (4 métodos)</t>
+          <t>Calendário heatmap de vencimentos</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Ícone colorido por método nas colunas Extinção de DFs e RFs: Split Payment (azul), Compensação (verde), Ressarcimento (âmbar) e Transferência (roxo). Visível também no modal de detalhe NF e na timeline do RF.</t>
+          <t>Visualização mensal navegável com intensidade de cor (tons teal) proporcional ao volume de créditos vencendo em cada dia. Clique em qualquer dia abre modal com a listagem dos DFs cujo vencimento cai naquela data.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · F-02 Aba Registros Fiscais — listagem por tributo</t>
+          <t>PRD de Crédito IBS/CBS · Seção 08 Gráficos e visualizações</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1269,9 +1269,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Gráficos extintos / vencidos / ageing</t>
+          <t>Badge de método de extinção (4 métodos)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Três gráficos analíticos no painel de créditos a apropriar: distribuição por status de extinção, volume de vencidos por mês e curva de ageing (dias desde a emissão).</t>
+          <t>Ícone colorido por método nas colunas Extinção de DFs e RFs: Split Payment, Compensação, Ressarcimento e Transferência. Ressarcimento só aparece com o pagamento de um pedido de ressarcimento. Visível também no modal do DF e no histórico do RF.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · Seção 08 Gráficos e visualizações</t>
+          <t>PRD de Crédito IBS/CBS · F-02 Aba Registros Fiscais — listagem por tributo</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1320,9 +1320,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Top 5 e Top 10 fornecedores</t>
+          <t>Gráficos extintos / vencidos / ageing</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Rankings de fornecedores por volume de crédito IBS+CBS no período selecionado, exibidos em grid lado a lado para comparação imediata.</t>
+          <t>Três gráficos analíticos no painel de créditos a apropriar: distribuição por status de extinção, volume de vencidos por mês e curva de ageing (dias desde a emissão).</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1371,21 +1371,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr"/>
@@ -1407,12 +1399,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Composição e método de extinção</t>
+          <t>Top 5 e Top 10 fornecedores</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Gráfico de distribuição percentual dos créditos por método de extinção utilizado (Split Payment, Compensação, Ressarcimento, Transferência).</t>
+          <t>Rankings de fornecedores por volume de crédito IBS+CBS no período selecionado, exibidos em grid lado a lado para comparação imediata.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1430,13 +1422,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr"/>
@@ -1458,22 +1458,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Ciclo do crédito: apropriação, extinção e prazo</t>
+          <t>Composição e método de extinção</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Três datas em cada RF e DF: o recolhimento que fez o crédito nascer, o consumo do crédito, e o limite de 5 anos do art. 54. Cada modalidade de recolhimento tem seu próprio marco.</t>
+          <t>Composição mensal dos créditos de entrada por situação: apropriado, utilizado por compensação, utilizado por ressarcimento, não apropriado, vencido, inconsistência e glosado.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · Seção 04 Máquinas de estado</t>
+          <t>PRD de Crédito IBS/CBS · Seção 08 Gráficos e visualizações</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1481,9 +1481,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -1509,22 +1509,22 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Assumir recolhimento via RAD</t>
+          <t>Ciclo do crédito: apropriação, extinção e prazo</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Numa DF com método Fornecedor e os dois tributos ainda não apropriados, o operador assume o pagamento do IBS e da CBS: o método vira RAD, a ação fica no histórico da DF e dos RFs, e o documento entra em Pagamentos RAD. Existe para garantir o crédito quando o fornecedor não recolhe (LC 214/2025, art. 36).</t>
+          <t>Três datas em cada RF e DF: o recolhimento que fez o crédito nascer, o consumo do crédito, e o limite de 5 anos do art. 54. Cada modalidade de recolhimento tem seu próprio marco.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · F-08 Assumir recolhimento via RAD</t>
+          <t>PRD de Crédito IBS/CBS · Seção 04 Máquinas de estado</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1560,22 +1560,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Visão por documento fiscal na aba DFs</t>
+          <t>Assumir recolhimento via RAD</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Aba que lista os documentos fiscais de entrada em vez dos registros, com IBS, CBS, crédito do documento, método de pagamento e as ações disponíveis. A decisão de assumir o recolhimento é por documento, não por registro.</t>
+          <t>Numa DF com método Fornecedor e os dois tributos ainda não apropriados, o operador assume o pagamento do IBS e da CBS: o método vira RAD, a ação fica no histórico da DF e dos RFs, e o documento entra em Pagamentos RAD. Existe para garantir o crédito quando o fornecedor não recolhe (LC 214/2025, art. 36).</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · F-04 Aba Documentos Fiscais — visão consolidada por DF</t>
+          <t>PRD de Crédito IBS/CBS · F-08 Assumir recolhimento via RAD</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1611,22 +1611,22 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Reverter o recolhimento assumido</t>
+          <t>Visão por documento fiscal na aba DFs</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Enquanto nenhuma guia tiver sido gerada, o operador desfaz a conversão e o documento volta ao método do contrato. A reversão fica no histórico do documento e dos registros, com motivo obrigatório.</t>
+          <t>Aba que lista os documentos fiscais de entrada em vez dos registros, com IBS, CBS, crédito do documento, método de pagamento e as ações disponíveis. A decisão de assumir o recolhimento é por documento, não por registro.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>PRD de Crédito IBS/CBS · F-08 Assumir recolhimento via RAD</t>
+          <t>PRD de Crédito IBS/CBS · F-04 Aba Documentos Fiscais — visão consolidada por DF</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Filtro por origem do método de pagamento</t>
+          <t>Reverter o recolhimento assumido</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Separa os documentos cujo método veio do contrato daqueles em que o adquirente assumiu o recolhimento. Sem esse recorte, a conversão manual desaparece dentro do total de RAD.</t>
+          <t>Enquanto nenhuma guia tiver sido gerada, o operador desfaz a conversão e o documento volta ao método do contrato. A reversão fica no histórico do documento e dos registros, com motivo obrigatório.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Débitos IBS/CBS</t>
+          <t>Créditos IBS/CBS</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Listagem DFs de saída</t>
+          <t>Filtro por origem do método de pagamento</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Documentos fiscais de saída com IBS e CBS apresentados em colunas separadas de valor, permitindo análise individual por imposto.</t>
+          <t>Separa os documentos cujo método veio do contrato daqueles em que o adquirente assumiu o recolhimento. Sem esse recorte, a conversão manual desaparece dentro do total de RAD.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>PRD de Débitos IBS/CBS · F-01 Listar documentos fiscais de saída</t>
+          <t>PRD de Crédito IBS/CBS · F-08 Assumir recolhimento via RAD</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Débitos IBS/CBS</t>
+          <t>Créditos IBS/CBS</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>IBS e CBS separados por coluna</t>
+          <t>Ressarcimento no ciclo do crédito</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Cada documento de saída mostra IBS e CBS em colunas próprias, e não um total somado. Os dois têm competência e destinação diferentes.</t>
+          <t>Painel por tributo com o crédito apropriado livre, reservado pela intenção, em pedido, compensado e ressarcido, e marcas e filtro nos RFs. Mostra que o crédito também vira dinheiro, não só abate débito.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>PRD de Débitos IBS/CBS · F-02 Separar IBS e CBS em colunas próprias</t>
+          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1787,9 +1787,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
@@ -1815,22 +1815,22 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Status extinção por prioridade entre RFs</t>
+          <t>Listagem DFs de saída</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Status do DF derivado dos dois RFs (IBS e CBS) com regra de prioridade explícita: inconsistência &gt; vencido &gt; extinto &gt; pendente. Um DF só é considerado extinto quando ambos os RFs estão extintos.</t>
+          <t>Documentos fiscais de saída com IBS e CBS apresentados em colunas separadas de valor, permitindo análise individual por imposto.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>PRD de Débitos IBS/CBS · F-03 Derivar o status do documento pelo pior registro</t>
+          <t>PRD de Débitos IBS/CBS · F-01 Listar documentos fiscais de saída</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1838,9 +1838,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -1866,17 +1866,17 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3 abas: Visão Geral · RFs · DFs</t>
+          <t>IBS e CBS separados por coluna</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Visão Geral (gráficos e KPIs de débito), Registros Fiscais (granularidade por RF/imposto) e Documentos Fiscais (visão agregada por DF). Filtros independentes em cada aba.</t>
+          <t>Cada documento de saída mostra IBS e CBS em colunas próprias, e não um total somado. Os dois têm competência e destinação diferentes.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>PRD de Débitos IBS/CBS · Seção 05 Arquitetura da tela</t>
+          <t>PRD de Débitos IBS/CBS · F-02 Separar IBS e CBS em colunas próprias</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1889,9 +1889,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -1917,17 +1917,17 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Coluna Inconsistências por DF</t>
+          <t>Status extinção por prioridade entre RFs</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Pills com tipo de inconsistência vinculada ao DF de saída. Mesma lógica da listagem de créditos — todas as inconsistências ativas exibidas em conjunto.</t>
+          <t>Status do DF derivado dos dois RFs (IBS e CBS) com regra de prioridade explícita: inconsistência &gt; vencido &gt; extinto &gt; pendente. Um DF só é considerado extinto quando ambos os RFs estão extintos.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>PRD de Débitos IBS/CBS · F-01 Listar documentos fiscais de saída</t>
+          <t>PRD de Débitos IBS/CBS · F-03 Derivar o status do documento pelo pior registro</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1940,9 +1940,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Filtros multi-seleção</t>
+          <t>3 abas: Visão Geral · RFs · DFs</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Filtros de status, tipo de DF, entidade, data e valor com suporte a seleção múltipla de opções por campo.</t>
+          <t>Visão Geral (gráficos e KPIs de débito), Registros Fiscais (granularidade por RF/imposto) e Documentos Fiscais (visão agregada por DF). Filtros independentes em cada aba.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>PRD de Débitos IBS/CBS · F-05 Filtrar por qualquer coluna relevante</t>
+          <t>PRD de Débitos IBS/CBS · Seção 05 Arquitetura da tela</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1991,7 +1991,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -2014,27 +2014,27 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Pagamentos RAD</t>
+          <t>Débitos IBS/CBS</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Listagem de guias RAD</t>
+          <t>Coluna Inconsistências por DF</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Tabela de guias de recolhimento geradas pelo adquirente (modelo RAD) com status individual: pago, pendente ou vencido — com data de vencimento e valor de cada guia.</t>
+          <t>Pills com tipo de inconsistência vinculada ao DF de saída. Mesma lógica da listagem de créditos — todas as inconsistências ativas exibidas em conjunto.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-04 Tabela de guias RAD — 22 colunas</t>
+          <t>PRD de Débitos IBS/CBS · F-01 Listar documentos fiscais de saída</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -2065,22 +2065,22 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Pagamentos RAD</t>
+          <t>Débitos IBS/CBS</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>St. Crédito · St. Registro · St. Pagamento independentes</t>
+          <t>Filtros multi-seleção</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Três colunas de estado separadas: Status do Crédito (ciclo de vida: não apropriado/apropriado/utilizado/glosado), Status de Registro (flags de risco: vencido/em risco/inconsistência) e Status do Pagamento (guia RAD: pago/pendente/vencido). Permite identificar créditos pagos via RAD que ainda têm inconsistência pendente.</t>
+          <t>Filtros de status, tipo de DF, entidade, data e valor com suporte a seleção múltipla de opções por campo.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · Seção 04 Máquinas de estado</t>
+          <t>PRD de Débitos IBS/CBS · F-05 Filtrar por qualquer coluna relevante</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2093,9 +2093,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -2116,27 +2116,27 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Pagamentos RAD</t>
+          <t>Débitos IBS/CBS</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Upload de comprovante PIX/RAD</t>
+          <t>Aviso da trava da intenção de ressarcimento</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Envio de comprovante de pagamento por RF — vinculado ao contrato RAD. O upload desbloqueia a marcação do RF como "Apropriado" e elimina a inconsistência "Sem Comprovante" quando presente.</t>
+          <t>Com intenção declarada, os créditos reservados não compensam débitos do mês seguinte do mesmo tributo, e os débitos não extintos seguem para recolhimento. O aviso explica por que a guia apareceu.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-09 Comprovante de pagamento PIX</t>
+          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -2144,9 +2144,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
@@ -2172,17 +2172,17 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Filtros em Pagamentos Executados</t>
+          <t>Listagem de guias RAD</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Busca por entidade, status de pagamento, data de vencimento e valor nas guias já processadas.</t>
+          <t>Tabela de guias de recolhimento geradas pelo adquirente (modelo RAD) com status individual: pago, pendente ou vencido — com data de vencimento e valor de cada guia.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-03 Painel de filtros avançados</t>
+          <t>PRD de Pagamentos RAD · F-04 Tabela de guias RAD — 22 colunas</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2223,17 +2223,17 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Aba Execução Programada</t>
+          <t>St. Crédito · St. Registro · St. Pagamento independentes</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>A face operacional das políticas: o que o motor produzirá, o que aguarda decisão e o que já saiu. Três seções — próxima execução, fila de decisão, histórico e falhas.</t>
+          <t>Três colunas de estado separadas: Status do Crédito (ciclo de vida: não apropriado/apropriado/utilizado/glosado), Status de Registro (flags de risco: vencido/em risco/inconsistência) e Status do Pagamento (guia RAD: pago/pendente/vencido). Permite identificar créditos pagos via RAD que ainda têm inconsistência pendente.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-11 Aba Execução Programada</t>
+          <t>PRD de Pagamentos RAD · Seção 04 Máquinas de estado</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2251,16 +2251,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="7" t="inlineStr"/>
@@ -2282,22 +2274,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Barra de cobertura das políticas</t>
+          <t>Upload de comprovante PIX/RAD</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Percentual das guias RAD pendentes sob alguma política ativa, quantas ficam de fora e em quais estabelecimentos. Recupera a leitura que a listagem por CNPJ dava de graça.</t>
+          <t>Envio de comprovante de pagamento por RF — vinculado ao contrato RAD. O upload desbloqueia a marcação do RF como "Apropriado" e elimina a inconsistência "Sem Comprovante" quando presente.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-11 Aba Execução Programada</t>
+          <t>PRD de Pagamentos RAD · F-09 Comprovante de pagamento PIX</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -2305,9 +2297,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -2333,17 +2325,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Listagem das guias represadas</t>
+          <t>Filtros em Pagamentos Executados</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Cada lote em espera abre a tabela das guias retidas, ordenada por valor, com o peso de cada uma no total e a concentração por CNPJ e contrato. Aberta por padrão.</t>
+          <t>Busca por entidade, status de pagamento, data de vencimento e valor nas guias já processadas.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-11 Aba Execução Programada</t>
+          <t>PRD de Pagamentos RAD · F-03 Painel de filtros avançados</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2356,9 +2348,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
@@ -2384,17 +2376,17 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Coluna Origem — automática ou manual</t>
+          <t>Aba Execução Programada</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Indica se a guia veio de uma política ativa ou de seleção manual, com faixa na linha. A determinação vem de um índice registro-para-política invalidado a cada mudança.</t>
+          <t>A face operacional das políticas: o que o motor produzirá, o que aguarda decisão e o que já saiu. Três seções — próxima execução, fila de decisão, histórico e falhas.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-04 Tabela de guias RAD — 22 colunas</t>
+          <t>PRD de Pagamentos RAD · F-11 Aba Execução Programada</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2412,8 +2404,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="7" t="inlineStr"/>
@@ -2435,22 +2435,22 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Coluna Entrega ao ERP</t>
+          <t>Barra de cobertura das políticas</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Estado do webhook que leva a guia ao ERP: entregue, pendente ou falha. Guia gerada e não entregue é crédito que se perde sem que nenhuma outra tela mostre problema.</t>
+          <t>Percentual das guias RAD pendentes sob alguma política ativa, quantas ficam de fora e em quais estabelecimentos. Recupera a leitura que a listagem por CNPJ dava de graça.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-04 Tabela de guias RAD — 22 colunas</t>
+          <t>PRD de Pagamentos RAD · F-11 Aba Execução Programada</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2458,9 +2458,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Antecipação de execução</t>
+          <t>Listagem das guias represadas</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Roda a janela agora, fora do calendário, para fechamento antecipado ou recuperação de janela perdida. Registra evento na política.</t>
+          <t>Cada lote em espera abre a tabela das guias retidas, ordenada por valor, com o peso de cada uma no total e a concentração por CNPJ e contrato. Aberta por padrão.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2509,7 +2509,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -2537,22 +2537,22 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Fila de erro de geração</t>
+          <t>Coluna Origem — automática ou manual</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Guias que voltaram com código de erro da API, agrupadas por causa. Dois dos três códigos de retorno possíveis são erro.</t>
+          <t>Indica se a guia veio de uma política ativa ou de seleção manual, com faixa na linha. A determinação vem de um índice registro-para-política invalidado a cada mudança.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-11 Aba Execução Programada</t>
+          <t>PRD de Pagamentos RAD · F-04 Tabela de guias RAD — 22 colunas</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -2560,9 +2560,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
@@ -2588,22 +2588,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Gestão de colunas e exportação CSV</t>
+          <t>Coluna Entrega ao ERP</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Escolha, reordenação e ordenação das dezenove colunas da listagem, com exportação em CSV da página ou do conjunto inteiro. A preferência fica salva no navegador.</t>
+          <t>Estado do webhook que leva a guia ao ERP: entregue, pendente ou falha. Guia gerada e não entregue é crédito que se perde sem que nenhuma outra tela mostre problema.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-12 Gestão de colunas e exportação da listagem</t>
+          <t>PRD de Pagamentos RAD · F-04 Tabela de guias RAD — 22 colunas</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2611,21 +2611,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="7" t="inlineStr"/>
@@ -2647,22 +2639,22 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Guias de recolhimento assumido</t>
+          <t>Antecipação de execução</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Documentos convertidos manualmente para RAD entram na fila de pagamento marcados como tal, com a data da conversão e o método que o contrato previa. Permite separar o que o contrato determinou do que o operador decidiu.</t>
+          <t>Roda a janela agora, fora do calendário, para fechamento antecipado ou recuperação de janela perdida. Registra evento na política.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-04 Tabela de guias RAD — 22 colunas</t>
+          <t>PRD de Pagamentos RAD · F-11 Aba Execução Programada</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2670,9 +2662,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
@@ -2698,22 +2690,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Aviso ao fornecedor do recolhimento</t>
+          <t>Fila de erro de geração</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Paga a guia RAD, o fornecedor recebe por e-mail o comprovante e o aviso de que o adquirente já recolheu aquele tributo — sem isso ele recolhe de novo. Roda em segundo plano: o que aparece é o evento no histórico do documento e a marca na linha do pagamento.</t>
+          <t>Guias que voltaram com código de erro da API, agrupadas por causa. Dois dos três códigos de retorno possíveis são erro.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>PRD de Pagamentos RAD · F-13 Aviso ao fornecedor do recolhimento pelo adquirente</t>
+          <t>PRD de Pagamentos RAD · F-11 Aba Execução Programada</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2721,9 +2713,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
@@ -2744,27 +2736,27 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Inconsistências</t>
+          <t>Pagamentos RAD</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Cards DF-cêntricos (rfId opcional)</t>
+          <t>Gestão de colunas e exportação CSV</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Toda inconsistência tem vínculo obrigatório ao DF de origem. O campo rfId é opcional: nulo para inconsistências geradas antes da criação dos RFs (falhas de ingestão); preenchido quando a inconsistência é específica de um RF já criado (pós-apuração ou pós-conciliação financeira).</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Escolha, reordenação e ordenação das dezenove colunas da listagem, com exportação em CSV da página ou do conjunto inteiro. A preferência fica salva no navegador.</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Pagamentos RAD · F-12 Gestão de colunas e exportação da listagem</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -2772,13 +2764,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
-      <c r="K42" s="3" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L42" s="3" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr"/>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Inconsistências</t>
+          <t>Pagamentos RAD</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Múltiplas inconsistências por DF</t>
+          <t>Guias de recolhimento assumido</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Um mesmo DF pode acumular inconsistências geradas em etapas distintas do ciclo de vida (ex: divergência de valor IBS na apuração E comprovante CBS ausente na conciliação). Todas exibidas simultaneamente como pills nas listagens.</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Documentos convertidos manualmente para RAD entram na fila de pagamento marcados como tal, com a data da conversão e o método que o contrato previa. Permite separar o que o contrato determinou do que o operador decidiu.</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Pagamentos RAD · F-04 Tabela de guias RAD — 22 colunas</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2846,27 +2846,27 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Inconsistências</t>
+          <t>Pagamentos RAD</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Taxonomia CAPUR IBS/CBS por imposto</t>
+          <t>Aviso ao fornecedor do recolhimento</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Inconsistências de apuração identificadas individualmente por imposto: capur_ibs_valor (valor divergente), capur_ibs_aliquota (alíquota divergente), capur_cbs_valor, capur_cbs_aliquota. IBS e CBS apurados de forma independente.</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Paga a guia RAD, o fornecedor recebe por e-mail o comprovante e o aviso de que o adquirente já recolheu aquele tributo — sem isso ele recolhe de novo. Roda em segundo plano: o que aparece é o evento no histórico do documento e a marca na linha do pagamento.</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Pagamentos RAD · F-13 Aviso ao fornecedor do recolhimento pelo adquirente</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Taxonomia CFIN IBS/CBS por imposto</t>
+          <t>Cards DF-cêntricos (rfId opcional)</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Inconsistências financeiras identificadas por imposto: cfin_ibs_split (split não executado), cfin_ibs_comprovante (comprovante divergente), cfin_cbs_split, cfin_cbs_comprovante. Inclui "Sem Comprovante" para contratos RAD sem anexo.</t>
+          <t>Toda inconsistência tem vínculo obrigatório ao DF de origem. O campo rfId é opcional: nulo para inconsistências geradas antes da criação dos RFs (falhas de ingestão); preenchido quando a inconsistência é específica de um RF já criado (pós-apuração ou pós-conciliação financeira).</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Kanban: Aberta → Resolvida / Glosada</t>
+          <t>Múltiplas inconsistências por DF</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Quadro kanban com colunas: Aberta, Em Análise, Aguardando Emitente, Resolvida e Glosada. Cards movidos entre colunas registram data e usuário da transição.</t>
+          <t>Um mesmo DF pode acumular inconsistências geradas em etapas distintas do ciclo de vida (ex: divergência de valor IBS na apuração E comprovante CBS ausente na conciliação). Todas exibidas simultaneamente como pills nas listagens.</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Atribuição de responsável</t>
+          <t>Taxonomia CAPUR IBS/CBS por imposto</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Card de inconsistência pode ser atribuído a um operador específico, com campo de responsável e registro de data de atribuição.</t>
+          <t>Inconsistências de apuração identificadas individualmente por imposto: capur_ibs_valor (valor divergente), capur_ibs_aliquota (alíquota divergente), capur_cbs_valor, capur_cbs_aliquota. IBS e CBS apurados de forma independente.</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -3032,16 +3032,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr"/>
@@ -3063,12 +3055,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Histórico de alterações</t>
+          <t>Taxonomia CFIN IBS/CBS por imposto</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Modal expandido em dois painéis: dados da inconsistência e ações sugeridas à esquerda; histórico cronológico completo de transições, atribuições e comentários à direita.</t>
+          <t>Inconsistências financeiras identificadas por imposto: cfin_ibs_split (split não executado), cfin_ibs_comprovante (comprovante divergente), cfin_cbs_split, cfin_cbs_comprovante. Inclui "Sem Comprovante" para contratos RAD sem anexo.</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -3078,7 +3070,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -3114,12 +3106,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Diagnóstico guiado — árvore de decisão</t>
+          <t>Kanban: Aberta → Resolvida / Glosada</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Assistente de diagnóstico com perguntas sequenciais para identificar o tipo de inconsistência: fluxo de entrada ou saída? Etapa de apuração (CAPUR) ou financeira (CFIN)? Qual imposto (IBS ou CBS)?</t>
+          <t>Quadro kanban com colunas: Aberta, Em Análise, Aguardando Emitente, Resolvida e Glosada. Cards movidos entre colunas registram data e usuário da transição.</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -3137,9 +3129,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
@@ -3165,12 +3157,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Filtros multiselect por tipo e DF</t>
+          <t>Atribuição de responsável</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Filtros combinados por tipo de inconsistência (taxonomia CAPUR/CFIN) e DF de origem, com suporte a seleção múltipla.</t>
+          <t>Card de inconsistência pode ser atribuído a um operador específico, com campo de responsável e registro de data de atribuição.</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -3180,7 +3172,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -3188,14 +3180,14 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>M1</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>M0</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -3219,22 +3211,22 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Ingestão de DFs</t>
+          <t>Inconsistências</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Upload CSV posicional (NF-e · CT-e · NFS-e)</t>
+          <t>Histórico de alterações</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Importação de arquivo CSV com layout de colunas posicionais fixo. Suporte aos tipos NF-e (Nota Fiscal Eletrônica), CT-e (Conhecimento de Transporte) e NFS-e (Nota Fiscal de Serviços).</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
+          <t>Modal expandido em dois painéis: dados da inconsistência e ações sugeridas à esquerda; histórico cronológico completo de transições, atribuições e comentários à direita.</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3270,22 +3262,22 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Ingestão de DFs</t>
+          <t>Inconsistências</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Suporte a Entrada e Saída</t>
+          <t>Diagnóstico guiado — árvore de decisão</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>O mesmo pipeline processa DFs de entrada (créditos IBS/CBS) e de saída (débitos IBS/CBS), detectando o fluxo pelo campo "tipo" do CSV.</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ingestão de DFs · Seção 04 Modelo de dados</t>
+          <t>Assistente de diagnóstico com perguntas sequenciais para identificar o tipo de inconsistência: fluxo de entrada ou saída? Etapa de apuração (CAPUR) ou financeira (CFIN)? Qual imposto (IBS ou CBS)?</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -3298,9 +3290,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr"/>
@@ -3321,27 +3313,27 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Ingestão de DFs</t>
+          <t>Inconsistências</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Pré-visualização antes de confirmar</t>
+          <t>Filtros multiselect por tipo e DF</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Após seleção do arquivo, uma tabela de prévia é gerada a partir do CSV antes de qualquer importação ser executada. O operador valida os dados e confirma ou cancela.</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
+          <t>Filtros combinados por tipo de inconsistência (taxonomia CAPUR/CFIN) e DF de origem, com suporte a seleção múltipla.</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -3349,13 +3341,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr"/>
-      <c r="K53" s="3" t="inlineStr"/>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L53" s="3" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
@@ -3372,22 +3372,22 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Ingestão de DFs</t>
+          <t>Inconsistências</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Validação binária: Importado / Inconsistência</t>
+          <t>Família Ressarcimento de inconsistências</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Cada linha do CSV resulta em um de dois status: Importado (aprovado — DF entra no sistema com RFs criados) ou Inconsistência (falha — DF não importado, card de inconsistência gerado automaticamente).</t>
+          <t>Saldo divergente da Receita, impedimento do IBS, deferimento parcial e pagamento divergente viram chamados no kanban e na listagem, com o pedido ou o RF de origem.</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
+          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3400,9 +3400,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr"/>
@@ -3428,22 +3428,22 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Stub DF para documentos rejeitados</t>
+          <t>Upload CSV posicional (NF-e · CT-e · NFS-e)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>DFs com falha de ingestão são injetados em nfListaFiltradaGlobal como registros stub com statusImportacao:"falha", tornando-os visíveis nas listagens de Créditos com todos os dados disponíveis (entidade, CNPJ, valor, data).</t>
+          <t>Importação de arquivo CSV com layout de colunas posicionais fixo. Suporte aos tipos NF-e (Nota Fiscal Eletrônica), CT-e (Conhecimento de Transporte) e NFS-e (Nota Fiscal de Serviços).</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Ingestão de DFs</t>
+          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Card de inconsistência automático</t>
+          <t>Suporte a Entrada e Saída</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Para cada DF rejeitado, um card de inconsistência é criado e vinculado ao stub DF via nf._inconsistencias[]. Tipos: falha de layout (CSV malformado), CNPJ inválido (não encontrado na RFB) ou documento duplicado.</t>
+          <t>O mesmo pipeline processa DFs de entrada (créditos IBS/CBS) e de saída (débitos IBS/CBS), detectando o fluxo pelo campo "tipo" do CSV.</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs · Seção 05 Pipeline e máquinas de estado</t>
+          <t>PRD de Ingestão de DFs · Seção 04 Modelo de dados</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -3530,22 +3530,22 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Ingestão por API com credencial própria</t>
+          <t>Pré-visualização antes de confirmar</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>A conexão de ingestão passa a ter credencial emitida dentro do produto, com escopos de escrita e leitura. É o canal que torna o upload manual uma exceção.</t>
+          <t>Após seleção do arquivo, uma tabela de prévia é gerada a partir do CSV antes de qualquer importação ser executada. O operador valida os dados e confirma ou cancela.</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs · Seção 13 Integrações e dependências</t>
+          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
@@ -3571,32 +3571,32 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>FCT — Fluxo de Caixa Tributário</t>
+          <t>Ingestão de DFs</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Forecast de Fluxo Fiscal</t>
+          <t>Validação binária: Importado / Inconsistência</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Projeção de entradas tributárias (créditos IBS+CBS) e saídas (débitos e pagamentos) com média móvel progressiva calculada sobre os dados históricos disponíveis.</t>
+          <t>Cada linha do CSV resulta em um de dois status: Importado (aprovado — DF entra no sistema com RFs criados) ou Inconsistência (falha — DF não importado, card de inconsistência gerado automaticamente).</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-08 Projetar o fluxo fiscal</t>
+          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -3604,9 +3604,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr"/>
@@ -3622,32 +3622,32 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>FCT — Fluxo de Caixa Tributário</t>
+          <t>Ingestão de DFs</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Média móvel progressiva</t>
+          <t>Stub DF para documentos rejeitados</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>A média é calculada sobre os N meses históricos disponíveis, crescendo progressivamente à medida que mais dados são acumulados — sem período mínimo fixo.</t>
+          <t>DFs com falha de ingestão são injetados em nfListaFiltradaGlobal como registros stub com statusImportacao:"falha", tornando-os visíveis nas listagens de Créditos com todos os dados disponíveis (entidade, CNPJ, valor, data).</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · Seção 07 Indicadores e projeções</t>
+          <t>Não descrita no PRD de Ingestão de DFs</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -3655,9 +3655,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
@@ -3673,32 +3673,32 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>FCT — Fluxo de Caixa Tributário</t>
+          <t>Ingestão de DFs</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Corte realizado / projeção na data atual</t>
+          <t>Card de inconsistência automático</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Linha vertical posicionada na data atual separa visualmente os dados históricos realizados (traço sólido) das projeções futuras (traço pontilhado), em ambos os forecasts.</t>
+          <t>Para cada DF rejeitado, um card de inconsistência é criado e vinculado ao stub DF via nf._inconsistencias[]. Tipos: falha de layout (CSV malformado), CNPJ inválido (não encontrado na RFB) ou documento duplicado.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-09 Separar realizado de projetado na data de corte</t>
+          <t>PRD de Ingestão de DFs · Seção 05 Pipeline e máquinas de estado</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -3706,9 +3706,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr"/>
@@ -3724,32 +3724,32 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>FCT — Fluxo de Caixa Tributário</t>
+          <t>Ingestão de DFs</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Forecast de Aproveitamento de Crédito</t>
+          <t>Ingestão por API com credencial própria</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Projeção de quando os créditos a apropriar serão efetivamente utilizados para extinção de débitos, com base no ritmo histórico de aproveitamento do adquirente.</t>
+          <t>A conexão de ingestão passa a ter credencial emitida dentro do produto, com escopos de escrita e leitura. É o canal que torna o upload manual uma exceção.</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-10 Projetar o aproveitamento do crédito</t>
+          <t>PRD de Ingestão de DFs · Seção 13 Integrações e dependências</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -3757,9 +3757,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
@@ -3785,17 +3785,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Insights: melhor mês · tendência · perda projetada</t>
+          <t>Forecast de Fluxo Fiscal</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Três insights calculados automaticamente: melhor mês histórico (maior volume de créditos), tendência (crescente/estável/queda com percentual) e perda projetada por não-aproveitamento de créditos disponíveis.</t>
+          <t>Projeção de entradas tributárias (créditos IBS+CBS) e saídas (débitos e pagamentos) com média móvel progressiva calculada sobre os dados históricos disponíveis.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-11 Apresentar os insights do forecast</t>
+          <t>PRD de Analytics · F-08 Projetar o fluxo fiscal</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Tabela mensal de aproveitamento</t>
+          <t>Média móvel progressiva</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Tabela com colunas: Período, Créditos Gerados (IBS+CBS), Créditos Aproveitados e Percentual de Utilização — para cada mês do histórico disponível.</t>
+          <t>A média é calculada sobre os N meses históricos disponíveis, crescendo progressivamente à medida que mais dados são acumulados — sem período mínimo fixo.</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-14 Detalhar o fluxo mensal em tabela</t>
+          <t>PRD de Analytics · Seção 07 Indicadores e projeções</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -3887,22 +3887,22 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Retry automático de renderização</t>
+          <t>Corte realizado / projeção na data atual</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Quando os dados assíncronos de nfListaFiltradaGlobal ainda não estão disponíveis no momento da renderização, o módulo FCT tenta novamente automaticamente.</t>
+          <t>Linha vertical posicionada na data atual separa visualmente os dados históricos realizados (traço sólido) das projeções futuras (traço pontilhado), em ambos os forecasts.</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Analytics</t>
+          <t>PRD de Analytics · F-09 Separar realizado de projetado na data de corte</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -3933,22 +3933,22 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Inteligência</t>
+          <t>FCT — Fluxo de Caixa Tributário</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Score de risco por fornecedor (0–100)</t>
+          <t>Forecast de Aproveitamento de Crédito</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Pontuação de conformidade fiscal calculada por fornecedor com base no critério: volume de créditos em risco (flags vencido/em_risco/inconsistência) dividido pelo total de créditos gerados. Resultado convertido em escala 0–100.</t>
+          <t>Projeção de quando os créditos a apropriar serão efetivamente utilizados para extinção de débitos, com base no ritmo histórico de aproveitamento do adquirente.</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
+          <t>PRD de Analytics · F-10 Projetar o aproveitamento do crédito</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3961,21 +3961,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J65" s="10" t="inlineStr">
+      <c r="I65" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
       <c r="N65" s="7" t="inlineStr"/>
@@ -3992,22 +3984,22 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Inteligência</t>
+          <t>FCT — Fluxo de Caixa Tributário</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Critério: créditos em risco ÷ total</t>
+          <t>Insights: melhor mês · tendência · perda projetada</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>O score sai da razão entre o crédito em risco e o crédito total originado pelo fornecedor — proporção, não valor absoluto, para não punir volume.</t>
+          <t>Três insights calculados automaticamente: melhor mês histórico (maior volume de créditos), tendência (crescente/estável/queda com percentual) e perda projetada por não-aproveitamento de créditos disponíveis.</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
+          <t>PRD de Analytics · F-11 Apresentar os insights do forecast</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -4020,21 +4012,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr">
+      <c r="I66" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr"/>
       <c r="L66" s="3" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
       <c r="N66" s="7" t="inlineStr"/>
@@ -4051,22 +4035,22 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Inteligência</t>
+          <t>FCT — Fluxo de Caixa Tributário</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Score ≥ 70 → badge verde (baixo risco)</t>
+          <t>Tabela mensal de aproveitamento</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Fornecedores com score ≥ 70 recebem badge verde indicando baixo risco fiscal. Entre 40 e 69: âmbar (risco médio). Abaixo de 40: vermelho (alto risco).</t>
+          <t>Tabela com colunas: Período, Créditos Gerados (IBS+CBS), Créditos Aproveitados e Percentual de Utilização — para cada mês do histórico disponível.</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
+          <t>PRD de Analytics · F-14 Detalhar o fluxo mensal em tabela</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -4079,21 +4063,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J67" s="10" t="inlineStr">
+      <c r="I67" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="7" t="inlineStr"/>
@@ -4110,27 +4086,27 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Inteligência</t>
+          <t>FCT — Fluxo de Caixa Tributário</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Ranking Top 5 Melhores e Top 5 Piores</t>
+          <t>Retry automático de renderização</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Dois rankings lado a lado: os 5 fornecedores com maior score (baixo risco, priorizados para relacionamento) e os 5 com menor score (alto risco, candidatos a ação imediata).</t>
+          <t>Quando os dados assíncronos de nfListaFiltradaGlobal ainda não estão disponíveis no momento da renderização, o módulo FCT tenta novamente automaticamente.</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-04 Ranquear os melhores e os piores fornecedores</t>
+          <t>Não descrita no PRD de Analytics</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -4138,21 +4114,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
+      <c r="I68" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="7" t="inlineStr"/>
@@ -4174,17 +4142,17 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Mapa de bolhas risco × volume</t>
+          <t>Score de risco por fornecedor (0–100)</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Gráfico de dispersão com todos os fornecedores posicionados por dois eixos: eixo X = volume de créditos gerados; eixo Y = score de risco. Bolhas com anti-sobreposição para legibilidade mesmo com muitos fornecedores.</t>
+          <t>Pontuação de conformidade fiscal calculada por fornecedor com base no critério: volume de créditos em risco (flags vencido/em_risco/inconsistência) dividido pelo total de créditos gerados. Resultado convertido em escala 0–100.</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Analytics</t>
+          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -4202,7 +4170,7 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr">
+      <c r="J69" s="11" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
@@ -4233,17 +4201,17 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Tabela mensal de crédito por fornecedor</t>
+          <t>Critério: créditos em risco ÷ total</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Histórico mensal por fornecedor com colunas de créditos gerados (IBS+CBS) e aproveitados, permitindo identificar variações de volume ao longo do tempo.</t>
+          <t>O score sai da razão entre o crédito em risco e o crédito total originado pelo fornecedor — proporção, não valor absoluto, para não punir volume.</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-07 Abrir a tabela mensal de crédito</t>
+          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -4256,13 +4224,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I70" s="9" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr"/>
-      <c r="K70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L70" s="3" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="7" t="inlineStr"/>
@@ -4274,32 +4250,32 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Contratos</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Modelo RAD — adquirente recolhe o tributo</t>
+          <t>Score ≥ 70 → badge verde (baixo risco)</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Contratos no modelo RAD (Recolhimento pelo Adquirente Destinatário) definem que o adquirente é responsável por gerar e pagar as guias de IBS/CBS. Exige comprovante de pagamento para apropriação do crédito.</t>
+          <t>Fornecedores com score ≥ 70 recebem badge verde indicando baixo risco fiscal. Entre 40 e 69: âmbar (risco médio). Abaixo de 40: vermelho (alto risco).</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
+          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
@@ -4312,8 +4288,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr"/>
-      <c r="K71" s="3" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L71" s="3" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr"/>
@@ -4325,32 +4309,32 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Contratos</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Modelo Fornecedor — fornecedor recolhe</t>
+          <t>Ranking Top 5 Melhores e Top 5 Piores</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Contratos no modelo Fornecedor definem que o próprio fornecedor recolhe o tributo. O adquirente não precisa gerar guias nem anexar comprovante — a apropriação do crédito ocorre automaticamente após confirmação de pagamento pelo fornecedor.</t>
+          <t>Dois rankings lado a lado: os 5 fornecedores com maior score (baixo risco, priorizados para relacionamento) e os 5 com menor score (alto risco, candidatos a ação imediata).</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
+          <t>PRD de Analytics · F-04 Ranquear os melhores e os piores fornecedores</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -4363,8 +4347,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr"/>
-      <c r="K72" s="3" t="inlineStr"/>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L72" s="3" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="7" t="inlineStr"/>
@@ -4376,32 +4368,32 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Contratos</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Multi-contratos por fornecedor</t>
+          <t>Mapa de bolhas risco × volume</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Um fornecedor pode ter mais de um contrato vigente simultaneamente (ex: RAD para produtos da linha A, Fornecedor para produtos da linha B, com vigências e condições distintas).</t>
+          <t>Gráfico de dispersão com todos os fornecedores posicionados por dois eixos: eixo X = volume de créditos gerados; eixo Y = score de risco. Bolhas com anti-sobreposição para legibilidade mesmo com muitos fornecedores.</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · Seção 05 Resolução de contrato vigente</t>
+          <t>Não descrita no PRD de Analytics</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -4414,8 +4406,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr"/>
-      <c r="K73" s="3" t="inlineStr"/>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L73" s="3" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="7" t="inlineStr"/>
@@ -4427,32 +4427,32 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Contratos</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Vínculo contrato → obrigações de comprovante</t>
+          <t>Tabela mensal de crédito por fornecedor</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>O modelo do contrato determina automaticamente quais validações de comprovante são aplicadas nos RFs daquele fornecedor — elimina necessidade de configuração manual por RF.</t>
+          <t>Histórico mensal por fornecedor com colunas de créditos gerados (IBS+CBS) e aproveitados, permitindo identificar variações de volume ao longo do tempo.</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Contratos</t>
+          <t>PRD de Analytics · F-07 Abrir a tabela mensal de crédito</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -4460,9 +4460,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr"/>
@@ -4488,22 +4488,22 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Listagem com filtros padronizados</t>
+          <t>Modelo RAD — adquirente recolhe o tributo</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Tabela de contratos com filtros shBuildFilterPanel por modelo (RAD/Fornecedor), status de vigência e fornecedor vinculado.</t>
+          <t>Contratos no modelo RAD (Recolhimento pelo Adquirente Destinatário) definem que o adquirente é responsável por gerar e pagar as guias de IBS/CBS. Exige comprovante de pagamento para apropriação do crédito.</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · F-01 Listagem de contratos</t>
+          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -4539,17 +4539,17 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Contrato como recorte de política RAD</t>
+          <t>Modelo Fornecedor — fornecedor recolhe</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Contratos de método RAD podem ser o critério de cobertura de uma política de execução, na orquestração por contrato.</t>
+          <t>Contratos no modelo Fornecedor definem que o próprio fornecedor recolhe o tributo. O adquirente não precisa gerar guias nem anexar comprovante — a apropriação do crédito ocorre automaticamente após confirmação de pagamento pelo fornecedor.</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -4562,9 +4562,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr"/>
@@ -4590,17 +4590,17 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Modelo Split Payment — retenção na liquidação</t>
+          <t>Multi-contratos por fornecedor</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Terceiro método de pagamento do contrato: o IBS e a CBS são segregados no próprio instrumento de pagamento e recolhidos na liquidação. Documentos em Split Payment não admitem recolhimento assumido, porque o instrumento já separa o tributo (art. 36, caput).</t>
+          <t>Um fornecedor pode ter mais de um contrato vigente simultaneamente (ex: RAD para produtos da linha A, Fornecedor para produtos da linha B, com vigências e condições distintas).</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
+          <t>PRD de Contratos · Seção 05 Resolução de contrato vigente</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4613,21 +4613,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
       <c r="L77" s="3" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
       <c r="N77" s="7" t="inlineStr"/>
@@ -4644,22 +4636,22 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Cadastro com razão social anonimizada</t>
+          <t>Vínculo contrato → obrigações de comprovante</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Razões sociais geradas deterministicamente por índice (seed fixo), garantindo que o mesmo fornecedor receba sempre o mesmo nome fictício entre sessões. Ex: "Induspar Componentes Ltda", "Metalúrgica Sulamérica S.A.".</t>
+          <t>O modelo do contrato determina automaticamente quais validações de comprovante são aplicadas nos RFs daquele fornecedor — elimina necessidade de configuração manual por RF.</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-04 Cadastrar fornecedor</t>
+          <t>Não descrita no PRD de Contratos</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -4695,27 +4687,27 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>CNPJ formatado XX.XXX.XXX/XXXX-XX</t>
+          <t>Listagem com filtros padronizados</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>CNPJs exibidos no padrão visual brasileiro em todos os módulos. Consistência garantida por função de formatação centralizada.</t>
+          <t>Tabela de contratos com filtros shBuildFilterPanel por modelo (RAD/Fornecedor), status de vigência e fornecedor vinculado.</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-04 Cadastrar fornecedor</t>
+          <t>PRD de Contratos · F-01 Listagem de contratos</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -4746,27 +4738,27 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Edição com trilha de auditoria</t>
+          <t>Contrato como recorte de política RAD</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Cada alteração de campo no cadastro registra: campo editado, valor anterior, novo valor, usuário que editou e data/hora. Histórico append-only — não pode ser apagado.</t>
+          <t>Contratos de método RAD podem ser o critério de cobertura de uma política de execução, na orquestração por contrato.</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-06 Registrar auditoria do cadastro</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -4774,7 +4766,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -4797,22 +4789,22 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Multi-contratos no cadastro</t>
+          <t>Modelo Split Payment — retenção na liquidação</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Campo que vincula mais de um contrato vigente ao mesmo fornecedor. Visível no cadastro com status de cada contrato (ativo/encerrado/suspenso).</t>
+          <t>Terceiro método de pagamento do contrato: o IBS e a CBS são segregados no próprio instrumento de pagamento e recolhidos na liquidação. Documentos em Split Payment não admitem recolhimento assumido, porque o instrumento já separa o tributo (art. 36, caput).</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-05 Editar fornecedor</t>
+          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4825,13 +4817,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr"/>
-      <c r="K81" s="3" t="inlineStr"/>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L81" s="3" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
       <c r="N81" s="7" t="inlineStr"/>
@@ -4853,22 +4853,22 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Score de conformidade no cadastro</t>
+          <t>Cadastro com razão social anonimizada</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Score calculado pelo módulo Inteligência exibido diretamente na ficha do fornecedor, com badge de cor por faixa de risco.</t>
+          <t>Razões sociais geradas deterministicamente por índice (seed fixo), garantindo que o mesmo fornecedor receba sempre o mesmo nome fictício entre sessões. Ex: "Induspar Componentes Ltda", "Metalúrgica Sulamérica S.A.".</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-07 Apresentar score e classificação</t>
+          <t>PRD de Fornecedor · F-04 Cadastrar fornecedor</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -4876,9 +4876,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr"/>
@@ -4904,22 +4904,22 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Aba Acessos no cadastro</t>
+          <t>CNPJ formatado XX.XXX.XXX/XXXX-XX</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Quem do fornecedor acessa o portal, com papel, alcance, último acesso e situação, mais os convites pendentes com prazo de expiração.</t>
+          <t>CNPJs exibidos no padrão visual brasileiro em todos os módulos. Consistência garantida por função de formatação centralizada.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-09 Listar quem acessa o portal</t>
+          <t>PRD de Fornecedor · F-04 Cadastrar fornecedor</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
@@ -4955,17 +4955,17 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Convite, reenvio e cancelamento</t>
+          <t>Edição com trilha de auditoria</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>O operador convida por e-mail escolhendo papel e CNPJs do grupo, e nunca define senha. Reenviar invalida o link anterior.</t>
+          <t>Cada alteração de campo no cadastro registra: campo editado, valor anterior, novo valor, usuário que editou e data/hora. Histórico append-only — não pode ser apagado.</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-10 Convidar uma pessoa</t>
+          <t>PRD de Fornecedor · F-06 Registrar auditoria do cadastro</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -4978,9 +4978,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr"/>
@@ -5006,22 +5006,22 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Revogação com motivo e trilha</t>
+          <t>Multi-contratos no cadastro</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Corta o acesso na hora e encerra as sessões abertas. O acesso revogado continua na lista — apagá-lo apagaria a autoria dos comprovantes já enviados.</t>
+          <t>Campo que vincula mais de um contrato vigente ao mesmo fornecedor. Visível no cadastro com status de cada contrato (ativo/encerrado/suspenso).</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-12 Revogar acesso com motivo</t>
+          <t>PRD de Fornecedor · F-05 Editar fornecedor</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -5029,21 +5029,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J85" s="10" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr"/>
       <c r="L85" s="3" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
       <c r="N85" s="7" t="inlineStr"/>
@@ -5065,22 +5057,22 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Importação de fornecedores e grupos por CSV</t>
+          <t>Score de conformidade no cadastro</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Um arquivo cria, atualiza e monta o grupo econômico pela coluna de matriz, resolvido em segunda passada — a filial pode vir antes da matriz.</t>
+          <t>Score calculado pelo módulo Inteligência exibido diretamente na ficha do fornecedor, com badge de cor por faixa de risco.</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-13 Cadastrar e atualizar por CSV</t>
+          <t>PRD de Fornecedor · F-07 Apresentar score e classificação</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -5088,9 +5080,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr"/>
@@ -5116,22 +5108,22 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Importação de status e de convites em massa</t>
+          <t>Aba Acessos no cadastro</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Ativar, inativar ou bloquear em lote, com motivo; e convidar muita gente de uma vez, ignorando quem já tem acesso ativo.</t>
+          <t>Quem do fornecedor acessa o portal, com papel, alcance, último acesso e situação, mais os convites pendentes com prazo de expiração.</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-15 Atualizar status e convidar em massa</t>
+          <t>PRD de Fornecedor · F-09 Listar quem acessa o portal</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -5167,22 +5159,22 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Pré-visualização e relatório da importação</t>
+          <t>Convite, reenvio e cancelamento</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Antes de gravar, mostra o que será criado, atualizado, ignorado e recusado, e quantos acessos mudam de alcance. Depois, o relatório traz linha a linha o que falhou e o que fazer.</t>
+          <t>O operador convida por e-mail escolhendo papel e CNPJs do grupo, e nunca define senha. Reenviar invalida o link anterior.</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-16 Conferir antes de gravar e receber o relatório</t>
+          <t>PRD de Fornecedor · F-10 Convidar uma pessoa</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -5190,21 +5182,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J88" s="10" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr"/>
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
       <c r="N88" s="7" t="inlineStr"/>
@@ -5226,22 +5210,22 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Histórico de lotes de importação</t>
+          <t>Revogação com motivo e trilha</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Cada importação vira um lote com autor, data, contagens e o arquivo original — a resposta para “quem inativou estes fornecedores?”.</t>
+          <t>Corta o acesso na hora e encerra as sessões abertas. O acesso revogado continua na lista — apagá-lo apagaria a autoria dos comprovantes já enviados.</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-17 Guardar o histórico de lotes</t>
+          <t>PRD de Fornecedor · F-12 Revogar acesso com motivo</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -5249,13 +5233,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr"/>
-      <c r="K89" s="3" t="inlineStr"/>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
       <c r="N89" s="7" t="inlineStr"/>
@@ -5272,27 +5264,27 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Organização</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Hierarquia CNPJ: Matriz + Filiais</t>
+          <t>Importação de fornecedores e grupos por CSV</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Visualização da estrutura do grupo econômico com CNPJ da matriz e todos os CNPJs de filiais vinculados. Status de conformidade fiscal exibido por entidade.</t>
+          <t>Um arquivo cria, atualiza e monta o grupo econômico pela coluna de matriz, resolvido em segunda passada — a filial pode vir antes da matriz.</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>PRD de Organização · F-01 Listar CNPJs agrupados por grupo econômico</t>
+          <t>PRD de Fornecedor · F-13 Cadastrar e atualizar por CSV</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -5323,27 +5315,27 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Organização</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Status de conformidade por entidade</t>
+          <t>Importação de status e de convites em massa</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Indicador de conformidade fiscal (créditos em risco, inconsistências abertas, vencimentos próximos) calculado individualmente para cada CNPJ da hierarquia.</t>
+          <t>Ativar, inativar ou bloquear em lote, com motivo; e convidar muita gente de uma vez, ignorando quem já tem acesso ativo.</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Organização</t>
+          <t>PRD de Fornecedor · F-15 Atualizar status e convidar em massa</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
@@ -5351,9 +5343,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr"/>
@@ -5374,27 +5366,27 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Organização</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Apuração Assistida na sidebar</t>
+          <t>Pré-visualização e relatório da importação</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Dados da Apuração Assistida do Governo (CG-IBS/RFB) exibidos na sidebar da aplicação, permitindo consulta rápida sem sair do contexto de trabalho atual.</t>
+          <t>Antes de gravar, mostra o que será criado, atualizado, ignorado e recusado, e quantos acessos mudam de alcance. Depois, o relatório traz linha a linha o que falhou e o que fazer.</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Organização</t>
+          <t>PRD de Fornecedor · F-16 Conferir antes de gravar e receber o relatório</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -5402,13 +5394,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr"/>
-      <c r="K92" s="3" t="inlineStr"/>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L92" s="3" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
       <c r="N92" s="7" t="inlineStr"/>
@@ -5425,27 +5425,27 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Organização</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Filtro Grupo Econômico — sincroniza tudo</t>
+          <t>Histórico de lotes de importação</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Seletor de CNPJ no header da aplicação que ao ser alterado recalcula nfListaFiltradaGlobal e dispara sincronizarTudo(), propagando o filtro para todos os módulos simultaneamente.</t>
+          <t>Cada importação vira um lote com autor, data, contagens e o arquivo original — a resposta para “quem inativou estes fornecedores?”.</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>PRD de Organização · F-01 Listar CNPJs agrupados por grupo econômico</t>
+          <t>PRD de Fornecedor · F-17 Guardar o histórico de lotes</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Auditoria de alterações cadastrais</t>
+          <t>Hierarquia CNPJ: Matriz + Filiais</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Histórico de mudanças na organização (razão social, CNPJs, responsáveis) com registro de usuário, data e campo alterado.</t>
+          <t>Visualização da estrutura do grupo econômico com CNPJ da matriz e todos os CNPJs de filiais vinculados. Status de conformidade fiscal exibido por entidade.</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>PRD de Organização · F-05 Registrar auditoria do cadastro</t>
+          <t>PRD de Organização · F-01 Listar CNPJs agrupados por grupo econômico</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
@@ -5504,9 +5504,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr"/>
@@ -5522,32 +5522,32 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>DFs filtrados pelo CNPJ próprio</t>
+          <t>Status de conformidade por entidade</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Fornecedor autenticado visualiza exclusivamente os documentos fiscais emitidos para o seu CNPJ — sem acesso a dados de outros fornecedores ou do adquirente.</t>
+          <t>Indicador de conformidade fiscal (créditos em risco, inconsistências abertas, vencimentos próximos) calculado individualmente para cada CNPJ da hierarquia.</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-01 Listar os documentos do próprio CNPJ</t>
+          <t>Não descrita no PRD de Organização</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -5555,9 +5555,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr"/>
@@ -5573,27 +5573,27 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>IBS e CBS separados por RF</t>
+          <t>Apuração Assistida na sidebar</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Status de cada imposto (IBS e CBS) exibido individualmente por RF, sem agrupamento. Permite ao fornecedor identificar qual imposto tem pendência.</t>
+          <t>Dados da Apuração Assistida do Governo (CG-IBS/RFB) exibidos na sidebar da aplicação, permitindo consulta rápida sem sair do contexto de trabalho atual.</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-02 Separar IBS e CBS por registro</t>
+          <t>Não descrita no PRD de Organização</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -5624,32 +5624,32 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Grupo econômico: Matriz + Filiais</t>
+          <t>Filtro Grupo Econômico — sincroniza tudo</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Fornecedor com grupo econômico pode visualizar DFs de todos os CNPJs do grupo (Matriz + Filiais) em painel consolidado.</t>
+          <t>Seletor de CNPJ no header da aplicação que ao ser alterado recalcula nfListaFiltradaGlobal e dispara sincronizarTudo(), propagando o filtro para todos os módulos simultaneamente.</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-03 Enxergar o grupo econômico</t>
+          <t>PRD de Organização · F-01 Listar CNPJs agrupados por grupo econômico</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -5657,9 +5657,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr"/>
@@ -5675,27 +5675,27 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Envio de comprovante RAD/PIX</t>
+          <t>Auditoria de alterações cadastrais</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Formulário de upload de comprovante de pagamento (PIX ou guia RAD) anexado ao RF específico. Notifica o adquirente e desbloqueia o processo de apropriação do crédito.</t>
+          <t>Histórico de mudanças na organização (razão social, CNPJs, responsáveis) com registro de usuário, data e campo alterado.</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-04 Enviar comprovante de recolhimento</t>
+          <t>PRD de Organização · F-05 Registrar auditoria do cadastro</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -5708,21 +5708,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J98" s="10" t="inlineStr">
+      <c r="I98" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr"/>
       <c r="L98" s="3" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
       <c r="N98" s="7" t="inlineStr"/>
@@ -5734,32 +5726,32 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Contestação de DFs vencidos</t>
+          <t>Enquadramento por órgão para o ressarcimento</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Fluxo formal de contestação para DFs com prazo vencido: texto justificado, evidências em anexo e envio ao adquirente para análise.</t>
+          <t>Programa de conformidade e prazo de análise na Receita e no Comitê Gestor, pedido centralizado na matriz e impedimentos do IBS registrados. Define o prazo de cada pedido.</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-05 Contestar documento vencido</t>
+          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
@@ -5767,7 +5759,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="I99" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -5795,22 +5787,22 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Chat com adquirente</t>
+          <t>DFs filtrados pelo CNPJ próprio</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Canal de comunicação direto dentro do portal para dúvidas ou negociações sobre DFs específicos, sem necessidade de contato por e-mail externo.</t>
+          <t>Fornecedor autenticado visualiza exclusivamente os documentos fiscais emitidos para o seu CNPJ — sem acesso a dados de outros fornecedores ou do adquirente.</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-06 Conversar com o adquirente</t>
+          <t>PRD de Portal do Fornecedor · F-01 Listar os documentos do próprio CNPJ</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -5818,9 +5810,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr"/>
@@ -5846,22 +5838,22 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Score de conformidade próprio</t>
+          <t>IBS e CBS separados por RF</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Fornecedor visualiza seu próprio score de conformidade fiscal calculado pelo adquirente, com detalhamento dos critérios que impactam negativamente a pontuação.</t>
+          <t>Status de cada imposto (IBS e CBS) exibido individualmente por RF, sem agrupamento. Permite ao fornecedor identificar qual imposto tem pendência.</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-07 Ver o próprio score de conformidade</t>
+          <t>PRD de Portal do Fornecedor · F-02 Separar IBS e CBS por registro</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
@@ -5869,9 +5861,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I101" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr"/>
@@ -5897,22 +5889,22 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Período multi-select</t>
+          <t>Grupo econômico: Matriz + Filiais</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Mesmo componente de seleção de meses individuais do portal cliente. Propaga o filtro de período por todos os módulos do portal do fornecedor.</t>
+          <t>Fornecedor com grupo econômico pode visualizar DFs de todos os CNPJs do grupo (Matriz + Filiais) em painel consolidado.</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-08 Recortar por período</t>
+          <t>PRD de Portal do Fornecedor · F-03 Enxergar o grupo econômico</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
@@ -5920,9 +5912,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr"/>
@@ -5948,22 +5940,22 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Contratos globais visíveis</t>
+          <t>Envio de comprovante RAD/PIX</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Lista dos contratos vigentes entre o fornecedor e o adquirente, com modelo (RAD/Fornecedor), vigência e condições relevantes para o ciclo de crédito.</t>
+          <t>Formulário de upload de comprovante de pagamento (PIX ou guia RAD) anexado ao RF específico. Notifica o adquirente e desbloqueia o processo de apropriação do crédito.</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-09 Consultar os contratos vigentes</t>
+          <t>PRD de Portal do Fornecedor · F-04 Enviar comprovante de recolhimento</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
@@ -5971,13 +5963,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I103" s="11" t="inlineStr">
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J103" s="3" t="inlineStr"/>
-      <c r="K103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
       <c r="N103" s="7" t="inlineStr"/>
@@ -5999,22 +5999,22 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Aviso de recolhimento assumido pelo adquirente</t>
+          <t>Contestação de DFs vencidos</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Quando o adquirente assume o recolhimento de um documento, o fornecedor vê o aviso de não recolher. Se recolher assim mesmo, o excedente volta a ele em até três dias úteis, mas o caixa já saiu duas vezes.</t>
+          <t>Fluxo formal de contestação para DFs com prazo vencido: texto justificado, evidências em anexo e envio ao adquirente para análise.</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-10 Ver o aviso de recolhimento assumido</t>
+          <t>PRD de Portal do Fornecedor · F-05 Contestar documento vencido</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
@@ -6022,7 +6022,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I104" s="11" t="inlineStr">
+      <c r="I104" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -6050,17 +6050,17 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Convite e acesso por senha própria</t>
+          <t>Chat com adquirente</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>O fornecedor entra pelo portal com credencial dele, criada ao aceitar um convite de uso único com validade de 7 dias. Antes disso, o portal só era alcançado por troca de perfil na sessão do operador.</t>
+          <t>Canal de comunicação direto dentro do portal para dúvidas ou negociações sobre DFs específicos, sem necessidade de contato por e-mail externo.</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-11 Entrar com credencial própria</t>
+          <t>PRD de Portal do Fornecedor · F-06 Conversar com o adquirente</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -6073,9 +6073,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr"/>
@@ -6101,22 +6101,22 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Papéis Responsável e Leitura</t>
+          <t>Score de conformidade próprio</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Responsável envia comprovante, contesta e conversa pelo chat; Leitura vê o mesmo e não age. É a única distinção que muda o risco do acesso externo.</t>
+          <t>Fornecedor visualiza seu próprio score de conformidade fiscal calculado pelo adquirente, com detalhamento dos critérios que impactam negativamente a pontuação.</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-12 Agir conforme o papel</t>
+          <t>PRD de Portal do Fornecedor · F-07 Ver o próprio score de conformidade</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
@@ -6124,7 +6124,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I106" s="11" t="inlineStr">
+      <c r="I106" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -6152,27 +6152,27 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Painel inicial do fornecedor</t>
+          <t>Período multi-select</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>O que ele deve, o que já foi recolhido e o que vence a seguir, em quatro números. É a tela que responde “preciso fazer alguma coisa hoje?” antes de qualquer listagem.</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Mesmo componente de seleção de meses individuais do portal cliente. Propaga o filtro de período por todos os módulos do portal do fornecedor.</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Portal do Fornecedor · F-08 Recortar por período</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
-        </is>
-      </c>
-      <c r="H107" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
@@ -6203,17 +6203,17 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Comprovantes de pagamento disponíveis ao fornecedor</t>
+          <t>Contratos globais visíveis</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Quando o adquirente recolhe — por RAD ou por recolhimento assumido —, o comprovante fica disponível ao fornecedor no próprio documento. Hoje o fluxo existe só na direção contrária: o fornecedor envia o dele.</t>
-        </is>
-      </c>
-      <c r="F108" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Lista dos contratos vigentes entre o fornecedor e o adquirente, com modelo (RAD/Fornecedor), vigência e condições relevantes para o ciclo de crédito.</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Portal do Fornecedor · F-09 Consultar os contratos vigentes</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -6221,14 +6221,14 @@
           <t>Listagem</t>
         </is>
       </c>
-      <c r="H108" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I108" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr"/>
@@ -6249,27 +6249,27 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Tela de login</t>
+          <t>Aviso de recolhimento assumido pelo adquirente</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Autenticação client-side com credenciais (Admin/Positivo123@). Sessão persistida em sessionStorage — não requer backend. Tela de login bloqueia acesso a qualquer módulo antes da autenticação.</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Quando o adquirente assume o recolhimento de um documento, o fornecedor vê o aviso de não recolher. Se recolher assim mesmo, o excedente volta a ele em até três dias úteis, mas o caixa já saiu duas vezes.</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Portal do Fornecedor · F-10 Ver o aviso de recolhimento assumido</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
@@ -6277,9 +6277,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr"/>
@@ -6300,27 +6300,27 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Perfis: Cliente e Fornecedor</t>
+          <t>Convite e acesso por senha própria</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Após login, o usuário seleciona o perfil: Cliente (adquirente — acesso completo a todos os módulos) ou Fornecedor (acesso restrito ao portal com dados filtrados pelo CNPJ do fornecedor).</t>
-        </is>
-      </c>
-      <c r="F110" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>O fornecedor entra pelo portal com credencial dele, criada ao aceitar um convite de uso único com validade de 7 dias. Antes disso, o portal só era alcançado por troca de perfil na sessão do operador.</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Portal do Fornecedor · F-11 Entrar com credencial própria</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
@@ -6351,27 +6351,27 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Troca de perfil in-session</t>
+          <t>Papéis Responsável e Leitura</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Card do usuário no header e modal de configurações permitem alternar de perfil durante a sessão sem necessidade de novo login.</t>
-        </is>
-      </c>
-      <c r="F111" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Responsável envia comprovante, contesta e conversa pelo chat; Leitura vê o mesmo e não age. É a única distinção que muda o risco do acesso externo.</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Portal do Fornecedor · F-12 Agir conforme o papel</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
@@ -6379,9 +6379,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr"/>
@@ -6402,17 +6402,17 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Tokens CSS globais + PALETTE JS</t>
+          <t>Painel inicial do fornecedor</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Todas as cores da interface definidas como variáveis CSS (--teal, --blue, --red etc.) e objeto PALETTE no JS. Nenhum valor hexadecimal inline no código — consistência visual garantida centralmente.</t>
+          <t>O que ele deve, o que já foi recolhido e o que vence a seguir, em quatro números. É a tela que responde “preciso fazer alguma coisa hoje?” antes de qualquer listagem.</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I112" s="6" t="inlineStr">
@@ -6453,17 +6453,17 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Sidebar teal colapsável + localStorage</t>
+          <t>Comprovantes de pagamento disponíveis ao fornecedor</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Toggle de 56px com transição CSS suave entre expandida (labels visíveis) e colapsada (ícones com tooltips). Estado persistido em localStorage — mantido entre sessões e recarregamentos.</t>
+          <t>Quando o adquirente recolhe — por RAD ou por recolhimento assumido —, o comprovante fica disponível ao fornecedor no próprio documento. Hoje o fluxo existe só na direção contrária: o fornecedor envia o dele.</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Tema claro/escuro automático</t>
+          <t>Tela de login</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>prefers-color-scheme detecta o tema do sistema operacional e aplica automaticamente. Override manual disponível via atributo data-theme. Tokens redefinidos para cada tema sem hardcode de cores.</t>
+          <t>Autenticação client-side com credenciais (Admin/Positivo123@). Sessão persistida em sessionStorage — não requer backend. Tela de login bloqueia acesso a qualquer módulo antes da autenticação.</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>shBuildFilterPanel — filtros padronizados</t>
+          <t>Perfis: Cliente e Fornecedor</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Função geradora de painéis de filtro colapsáveis com design unificado (classe sh-fp). Aplicada em Créditos, Débitos, Pagamentos, Inconsistências, Contratos, Fornecedores, Organização e Portal Fornecedor.</t>
+          <t>Após login, o usuário seleciona o perfil: Cliente (adquirente — acesso completo a todos os módulos) ou Fornecedor (acesso restrito ao portal com dados filtrados pelo CNPJ do fornecedor).</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>RF Core — 10 colunas uniformes</t>
+          <t>Troca de perfil in-session</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Conjunto padronizado de colunas presente em todas as listagens de RF do sistema: ID RF, Tipo Fiscal, DF Vinculado, Entidade, Data, Valor, Status do Crédito, Status de Registro, Método de Pagamento e Extinção. Filtros obrigatórios em todas as colunas.</t>
+          <t>Card do usuário no header e modal de configurações permitem alternar de perfil durante a sessão sem necessidade de novo login.</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>ESC fecha qualquer modal</t>
+          <t>Tokens CSS globais + PALETTE JS</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Atalho de teclado global — qualquer overlay aberto no sistema (modais de detalhe NF, RF, inconsistência, fornecedor, contrato) responde ao ESC e fecha sem ação adicional do usuário.</t>
+          <t>Todas as cores da interface definidas como variáveis CSS (--teal, --blue, --red etc.) e objeto PALETTE no JS. Nenhum valor hexadecimal inline no código — consistência visual garantida centralmente.</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Tooltip de coluna como padrão de projeto</t>
+          <t>Sidebar teal colapsável + localStorage</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Toda coluna declarada no catálogo de tabelas ganha explicação no cabeçalho, aplicada sempre do mesmo jeito. 104 colunas documentadas nas nove listagens; coluna nova só é publicada se souber se explicar.</t>
+          <t>Toggle de 56px com transição CSS suave entre expandida (labels visíveis) e colapsada (ícones com tooltips). Estado persistido em localStorage — mantido entre sessões e recarregamentos.</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
@@ -6736,9 +6736,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>Fora</t>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr"/>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Documentação de produto dentro da aplicação</t>
+          <t>Tema claro/escuro automático</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Hub de PRDs, mapa de funcionalidades e changelog acessíveis pela própria aplicação, sem depender de link externo. Quem opera e quem especifica leem a mesma versão.</t>
+          <t>prefers-color-scheme detecta o tema do sistema operacional e aplica automaticamente. Override manual disponível via atributo data-theme. Tokens redefinidos para cada tema sem hardcode de cores.</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
@@ -6787,9 +6787,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>Fora</t>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr"/>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Selo de modo demonstração</t>
+          <t>shBuildFilterPanel — filtros padronizados</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>A troca de perfil é marcada na interface como recurso de demonstração, e não parte do produto final: num ambiente real o fornecedor entra por convite e senha própria.</t>
+          <t>Função geradora de painéis de filtro colapsáveis com design unificado (classe sh-fp). Aplicada em Créditos, Débitos, Pagamentos, Inconsistências, Contratos, Fornecedores, Organização e Portal Fornecedor.</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Login via SSO corporativo</t>
+          <t>RF Core — 10 colunas uniformes</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Entrada pelo provedor de identidade da empresa (SAML 2.0 ou OIDC), com provisionamento e revogação vindos de lá. Não existe no produto: hoje o acesso é uma senha no código.</t>
+          <t>Conjunto padronizado de colunas presente em todas as listagens de RF do sistema: ID RF, Tipo Fiscal, DF Vinculado, Entidade, Data, Valor, Status do Crédito, Status de Registro, Método de Pagamento e Extinção. Filtros obrigatórios em todas as colunas.</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="H121" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
@@ -6907,32 +6907,32 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Políticas de execução sem limite de quantidade</t>
+          <t>ESC fecha qualquer modal</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>A organização cria quantas políticas precisar. Cada uma declara o que cobre, quando roda e quanta decisão humana existe — substituindo a relação um-para-um com o CNPJ comprador.</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Execução RAD · F-03 Criar e editar política</t>
+          <t>Atalho de teclado global — qualquer overlay aberto no sistema (modais de detalhe NF, RF, inconsistência, fornecedor, contrato) responde ao ESC e fecha sem ação adicional do usuário.</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
@@ -6958,32 +6958,32 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por CNPJ</t>
+          <t>Tooltip de coluna como padrão de projeto</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>A política cobre um ou mais CNPJs compradores. Todo registro fiscal de método RAD desses estabelecimentos entra na janela. Use quando a régua é do estabelecimento.</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>Toda coluna declarada no catálogo de tabelas ganha explicação no cabeçalho, aplicada sempre do mesmo jeito. 104 colunas documentadas nas nove listagens; coluna nova só é publicada se souber se explicar.</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
@@ -6991,21 +6991,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J123" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K123" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>Fora</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr"/>
+      <c r="K123" s="3" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
       <c r="N123" s="7" t="inlineStr"/>
@@ -7017,32 +7009,32 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por contrato</t>
+          <t>Documentação de produto dentro da aplicação</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>A política cobre um ou mais contratos de método RAD, em qualquer CNPJ comprador. Use quando a régua é do acordo — um contrato de insumo com prazo próprio.</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>Hub de PRDs, mapa de funcionalidades e changelog acessíveis pela própria aplicação, sem depender de link externo. Quem opera e quem especifica leem a mesma versão.</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
@@ -7050,21 +7042,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J124" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>Fora</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr"/>
       <c r="L124" s="3" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
       <c r="N124" s="7" t="inlineStr"/>
@@ -7076,32 +7060,32 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por faixa de valor</t>
+          <t>Selo de modo demonstração</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>A política cobre as guias cujo valor cai numa faixa. Separa grão fino de alto valor sem respeitar fronteira de estabelecimento.</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>A troca de perfil é marcada na interface como recurso de demonstração, e não parte do produto final: num ambiente real o fornecedor entra por convite e senha própria.</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
@@ -7109,9 +7093,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I125" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr"/>
@@ -7127,42 +7111,42 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Quatro bases de comparação da faixa</t>
+          <t>Login via SSO corporativo</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>A faixa incide sobre o valor da guia CBS/IBS, o imposto total do documento, o valor da nota ou o valor líquido. R$ 400 mil de nota e R$ 400 mil de guia descrevem conjuntos diferentes.</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>Entrada pelo provedor de identidade da empresa (SAML 2.0 ou OIDC), com provisionamento e revogação vindos de lá. Não existe no produto: hoje o acesso é uma senha no código.</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="I126" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr"/>
@@ -7188,12 +7172,12 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Três modos de operação</t>
+          <t>Políticas de execução sem limite de quantidade</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Automático gera e entrega sem intervenção — é o estado pretendido. Assistido aguarda aprovação a cada janela, como passo transitório. Manual não age.</t>
+          <t>A organização cria quantas políticas precisar. Cada uma declara o que cobre, quando roda e quanta decisão humana existe — substituindo a relação um-para-um com o CNPJ comprador.</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -7211,9 +7195,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I127" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr"/>
@@ -7239,17 +7223,17 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Janela de execução configurável</t>
+          <t>Orquestração por CNPJ</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Dias do mês em seleção múltipla, hora e antecedência em dias sobre o vencimento da guia.</t>
+          <t>A política cobre um ou mais CNPJs compradores. Todo registro fiscal de método RAD desses estabelecimentos entra na janela. Use quando a régua é do estabelecimento.</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-05 Definir a janela de execução</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -7267,8 +7251,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J128" s="3" t="inlineStr"/>
-      <c r="K128" s="3" t="inlineStr"/>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
       <c r="N128" s="7" t="inlineStr"/>
@@ -7290,17 +7282,17 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Critérios de inclusão por valor e flag</t>
+          <t>Orquestração por contrato</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Valor mínimo por guia e as flags que retêm a nota fora do lote — glosado, vencido, inconsistência. A nota retida não é descartada: aparece na fila com o motivo.</t>
+          <t>A política cobre um ou mais contratos de método RAD, em qualquer CNPJ comprador. Use quando a régua é do acordo — um contrato de insumo com prazo próprio.</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-06 Definir critérios de inclusão</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -7318,8 +7310,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J129" s="3" t="inlineStr"/>
-      <c r="K129" s="3" t="inlineStr"/>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
       <c r="N129" s="7" t="inlineStr"/>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Simulação da próxima execução</t>
+          <t>Orquestração por faixa de valor</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Antes de salvar, calcula quantas guias e que valor a política produziria hoje, e para onde elas iriam. Converte a política de promessa em número conferível.</t>
+          <t>A política cobre as guias cujo valor cai numa faixa. Separa grão fino de alto valor sem respeitar fronteira de estabelecimento.</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-12 Mostrar o lote antes de acontecer</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
@@ -7364,7 +7364,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I130" s="11" t="inlineStr">
+      <c r="I130" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -7392,22 +7392,22 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Detecção de cobertura repetida</t>
+          <t>Quatro bases de comparação da faixa</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Mesmo CNPJ ou mesmo contrato em duas políticas, ou faixas que se cruzam sobre a mesma base, barram o salvamento nomeando a política dona.</t>
+          <t>A faixa incide sobre o valor da guia CBS/IBS, o imposto total do documento, o valor da nota ou o valor líquido. R$ 400 mil de nota e R$ 400 mil de guia descrevem conjuntos diferentes.</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-08 Validar antes de salvar</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
@@ -7415,7 +7415,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I131" s="11" t="inlineStr">
+      <c r="I131" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -7443,22 +7443,22 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Alerta de sobreposição entre modelos</t>
+          <t>Três modos de operação</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Entre modelos diferentes a colisão só existe sobre notas concretas. A listagem mede quais registros são reivindicados por mais de uma política ativa e nomeia o par.</t>
+          <t>Automático gera e entrega sem intervenção — é o estado pretendido. Assistido aguarda aprovação a cada janela, como passo transitório. Manual não age.</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-02 Alertar sobreposição entre políticas ativas</t>
+          <t>PRD de Execução RAD · F-03 Criar e editar política</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -7466,7 +7466,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I132" s="11" t="inlineStr">
+      <c r="I132" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -7494,22 +7494,22 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Listagem de políticas com lote ao vivo</t>
+          <t>Janela de execução configurável</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Uma linha por política, com orquestração, cobertura em texto, modo, janela e quantas guias produziria na próxima janela — calculado no render.</t>
+          <t>Dias do mês em seleção múltipla, hora e antecedência em dias sobre o vencimento da guia.</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-01 Listar as políticas com sua cobertura</t>
+          <t>PRD de Execução RAD · F-05 Definir a janela de execução</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
@@ -7545,22 +7545,22 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Ativação e pausa em massa</t>
+          <t>Critérios de inclusão por valor e flag</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Seleção múltipla de políticas, útil em fechamento contábil ou incidente de integração. Cada mudança entra no histórico da política.</t>
+          <t>Valor mínimo por guia e as flags que retêm a nota fora do lote — glosado, vencido, inconsistência. A nota retida não é descartada: aparece na fila com o motivo.</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-10 Ativar e pausar em massa</t>
+          <t>PRD de Execução RAD · F-06 Definir critérios de inclusão</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -7568,9 +7568,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I134" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr"/>
@@ -7596,22 +7596,22 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Auditoria com diff campo a campo</t>
+          <t>Simulação da próxima execução</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Criação, edição, ativação, pausa e execução antecipada, com autor, momento e o de/para de cada campo alterado. O editor trabalha sobre cópia: cancelar desfaz.</t>
+          <t>Antes de salvar, calcula quantas guias e que valor a política produziria hoje, e para onde elas iriam. Converte a política de promessa em número conferível.</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-09 Registrar o histórico de alterações</t>
+          <t>PRD de Execução RAD · F-12 Mostrar o lote antes de acontecer</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
@@ -7619,21 +7619,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J135" s="10" t="inlineStr">
+      <c r="I135" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="K135" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
       <c r="N135" s="7" t="inlineStr"/>
@@ -7655,22 +7647,22 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Vínculo com a conexão de destino</t>
+          <t>Detecção de cobertura repetida</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Só conexões do tipo RAD ↔ ERP aparecem no seletor, com a saúde da conexão à vista. Sem conexão, a guia é gerada e fica na plataforma.</t>
+          <t>Mesmo CNPJ ou mesmo contrato em duas políticas, ou faixas que se cruzam sobre a mesma base, barram o salvamento nomeando a política dona.</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-07 Vincular a conexão de destino</t>
+          <t>PRD de Execução RAD · F-08 Validar antes de salvar</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -7678,7 +7670,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I136" s="11" t="inlineStr">
+      <c r="I136" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -7701,27 +7693,27 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Catálogo dos seis contextos da API</t>
+          <t>Alerta de sobreposição entre modelos</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Ingestão de DFs, fornecedores, contratos, RAD ↔ ERP, garantia de crédito e automações — cada um com endpoints, eventos, escopos e limites derivados da documentação publicada.</t>
+          <t>Entre modelos diferentes a colisão só existe sobre notas concretas. A listagem mede quais registros são reivindicados por mais de uma política ativa e nomeia o par.</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-02 Escolher o tipo no catálogo</t>
+          <t>PRD de Execução RAD · F-02 Alertar sobreposição entre políticas ativas</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
@@ -7729,21 +7721,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J137" s="10" t="inlineStr">
+      <c r="I137" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="3" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
       <c r="N137" s="7" t="inlineStr"/>
@@ -7760,27 +7744,27 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Conexões nas duas direções</t>
+          <t>Listagem de políticas com lote ao vivo</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Entrada, quando o ERP chama a API do SplitHub; saída, quando o SplitHub chama o endpoint do ERP; e bidirecional, no caso do RAD.</t>
+          <t>Uma linha por política, com orquestração, cobertura em texto, modo, janela e quantas guias produziria na próxima janela — calculado no render.</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-01 Listar conexões agrupadas por direção</t>
+          <t>PRD de Execução RAD · F-01 Listar as políticas com sua cobertura</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -7788,9 +7772,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I138" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr"/>
@@ -7811,22 +7795,22 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Assistente de nova conexão em três passos</t>
+          <t>Ativação e pausa em massa</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Tipo, configuração e credenciais. O tipo escolhido determina o que a plataforma pede e o que emite ao final.</t>
+          <t>Seleção múltipla de políticas, útil em fechamento contábil ou incidente de integração. Cada mudança entra no histórico da política.</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-02 Escolher o tipo no catálogo</t>
+          <t>PRD de Execução RAD · F-10 Ativar e pausar em massa</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -7839,7 +7823,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I139" s="11" t="inlineStr">
+      <c r="I139" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -7862,27 +7846,27 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Emissão de credencial de API</t>
+          <t>Auditoria com diff campo a campo</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>client_id e client_secret, trocados por um JWT. Fecha o vão que a documentação de autenticação declarava não especificar — antes, cada cliente era integrado fora do produto.</t>
+          <t>Criação, edição, ativação, pausa e execução antecipada, com autor, momento e o de/para de cada campo alterado. O editor trabalha sobre cópia: cancelar desfaz.</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-05 Emitir credenciais com exibição única</t>
+          <t>PRD de Execução RAD · F-09 Registrar o histórico de alterações</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -7890,13 +7874,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I140" s="11" t="inlineStr">
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J140" s="3" t="inlineStr"/>
-      <c r="K140" s="3" t="inlineStr"/>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L140" s="3" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
       <c r="N140" s="7" t="inlineStr"/>
@@ -7913,27 +7905,27 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Exibição única do segredo</t>
+          <t>Vínculo com a conexão de destino</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>O valor aparece em claro uma só vez; a plataforma guarda apenas o hash. Fechada a tela, o painel mostra os quatro últimos caracteres.</t>
+          <t>Só conexões do tipo RAD ↔ ERP aparecem no seletor, com a saúde da conexão à vista. Sem conexão, a guia é gerada e fica na plataforma.</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-05 Emitir credenciais com exibição única</t>
+          <t>PRD de Execução RAD · F-07 Vincular a conexão de destino</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
@@ -7941,7 +7933,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I141" s="11" t="inlineStr">
+      <c r="I141" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -7969,17 +7961,17 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Escopos por contexto</t>
+          <t>Catálogo dos seis contextos da API</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Cada escopo declara o que o JWT poderá fazer. Os destrutivos não vêm marcados por padrão; chamada fora do escopo retorna 403.</t>
+          <t>Ingestão de DFs, fornecedores, contratos, RAD ↔ ERP, garantia de crédito e automações — cada um com endpoints, eventos, escopos e limites derivados da documentação publicada.</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-04 Configurar escopos, destino e alcance</t>
+          <t>PRD de Integrações · F-02 Escolher o tipo no catálogo</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -7992,13 +7984,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I142" s="11" t="inlineStr">
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J142" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J142" s="3" t="inlineStr"/>
-      <c r="K142" s="3" t="inlineStr"/>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L142" s="3" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
       <c r="N142" s="7" t="inlineStr"/>
@@ -8020,22 +8020,22 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Rotação com janela de sobreposição</t>
+          <t>Conexões nas duas direções</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>O segredo anterior segue válido por 24 horas, para dar janela de troca sem derrubar a integração. Na conexão bidirecional, as duas rotações são independentes.</t>
+          <t>Entrada, quando o ERP chama a API do SplitHub; saída, quando o SplitHub chama o endpoint do ERP; e bidirecional, no caso do RAD.</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-07 Rotacionar o segredo com janela de sobreposição</t>
+          <t>PRD de Integrações · F-01 Listar conexões agrupadas por direção</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
@@ -8043,7 +8043,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I143" s="11" t="inlineStr">
+      <c r="I143" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8071,22 +8071,22 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Exemplo da primeira chamada</t>
+          <t>Assistente de nova conexão em três passos</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>O curl do login e da chamada autenticada, montado com os valores reais — ou o cálculo do HMAC do header de assinatura, no caso das conexões de saída.</t>
+          <t>Tipo, configuração e credenciais. O tipo escolhido determina o que a plataforma pede e o que emite ao final.</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-06 Montar o exemplo da primeira chamada</t>
+          <t>PRD de Integrações · F-02 Escolher o tipo no catálogo</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I144" s="11" t="inlineStr">
+      <c r="I144" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8122,22 +8122,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Alcance por CNPJ</t>
+          <t>Emissão de credencial de API</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>A conexão pode ser restringida a um subconjunto de estabelecimentos. Uma credencial de filial não deveria enviar documento de outra.</t>
+          <t>client_id e client_secret, trocados por um JWT. Fecha o vão que a documentação de autenticação declarava não especificar — antes, cada cliente era integrado fora do produto.</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-04 Configurar escopos, destino e alcance</t>
+          <t>PRD de Integrações · F-05 Emitir credenciais com exibição única</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
@@ -8145,7 +8145,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I145" s="11" t="inlineStr">
+      <c r="I145" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8173,22 +8173,22 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Health check por conexão</t>
+          <t>Exibição única do segredo</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Estado operacional, degradado, fora do ar ou sem tráfego, com disponibilidade em 24h, 7 e 30 dias e latência p50/p95.</t>
+          <t>O valor aparece em claro uma só vez; a plataforma guarda apenas o hash. Fechada a tela, o painel mostra os quatro últimos caracteres.</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-10 Classificar a saúde de cada conexão</t>
+          <t>PRD de Integrações · F-05 Emitir credenciais com exibição única</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -8196,7 +8196,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I146" s="11" t="inlineStr">
+      <c r="I146" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8224,22 +8224,22 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Sonda ativa e observação passiva</t>
+          <t>Escopos por contexto</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Conexão de saída é sondada com evento de teste. Conexão de entrada não tem o que sondar — quem chama é o ERP —, e ali a leitura vem do tráfego recebido.</t>
+          <t>Cada escopo declara o que o JWT poderá fazer. Os destrutivos não vêm marcados por padrão; chamada fora do escopo retorna 403.</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-11 Executar health check sob demanda</t>
+          <t>PRD de Integrações · F-04 Configurar escopos, destino e alcance</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
@@ -8247,7 +8247,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I147" s="11" t="inlineStr">
+      <c r="I147" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8275,22 +8275,22 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Histórico de incidentes</t>
+          <t>Rotação com janela de sobreposição</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Severidade, causa classificada, duração, impacto quantificado e linha do tempo com detecção, alerta, diagnóstico e resolução.</t>
+          <t>O segredo anterior segue válido por 24 horas, para dar janela de troca sem derrubar a integração. Na conexão bidirecional, as duas rotações são independentes.</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-12 Registrar o histórico de incidentes</t>
+          <t>PRD de Integrações · F-07 Rotacionar o segredo com janela de sobreposição</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -8298,7 +8298,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I148" s="11" t="inlineStr">
+      <c r="I148" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8326,22 +8326,22 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Log de entregas com inspeção de payload</t>
+          <t>Exemplo da primeira chamada</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Evento, chave do documento, tentativas e status HTTP, com o JSON exato transmitido. Sem isso, depurar divergência com o ERP vira troca de e-mails.</t>
+          <t>O curl do login e da chamada autenticada, montado com os valores reais — ou o cálculo do HMAC do header de assinatura, no caso das conexões de saída.</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-14 Listar e inspecionar entregas</t>
+          <t>PRD de Integrações · F-06 Montar o exemplo da primeira chamada</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
@@ -8349,7 +8349,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I149" s="11" t="inlineStr">
+      <c r="I149" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8377,22 +8377,22 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Reenvio de entrega</t>
+          <t>Alcance por CNPJ</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Individual ou em lote. A especificação diz que o SplitHub reenvia até receber 200 OK, mas não define o teto — o reenvio manual cobre o caso em que a automática desiste.</t>
+          <t>A conexão pode ser restringida a um subconjunto de estabelecimentos. Uma credencial de filial não deveria enviar documento de outra.</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-15 Reenviar entrega</t>
+          <t>PRD de Integrações · F-04 Configurar escopos, destino e alcance</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
@@ -8400,7 +8400,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I150" s="11" t="inlineStr">
+      <c r="I150" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8428,22 +8428,22 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Comprovantes recebidos do ERP</t>
+          <t>Health check por conexão</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Chamadas ao endpoint de comprovante, com identificador da guia, meio, valor e resultado. As rejeitadas aparecem isoladas, com o motivo.</t>
+          <t>Estado operacional, degradado, fora do ar ou sem tráfego, com disponibilidade em 24h, 7 e 30 dias e latência p50/p95.</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-16 Listar comprovantes recebidos e isolar rejeitados</t>
+          <t>PRD de Integrações · F-10 Classificar a saúde de cada conexão</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
@@ -8451,21 +8451,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J151" s="10" t="inlineStr">
+      <c r="I151" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
       <c r="N151" s="7" t="inlineStr"/>
@@ -8487,22 +8479,22 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Teste de conexão</t>
+          <t>Sonda ativa e observação passiva</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Dispara um evento de teste com payload fictício e mostra a resposta HTTP. Valida a URL antes de a política de execução depender dela.</t>
+          <t>Conexão de saída é sondada com evento de teste. Conexão de entrada não tem o que sondar — quem chama é o ERP —, e ali a leitura vem do tráfego recebido.</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-08 Testar conexão</t>
+          <t>PRD de Integrações · F-11 Executar health check sob demanda</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
@@ -8510,7 +8502,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I152" s="11" t="inlineStr">
+      <c r="I152" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -8538,32 +8530,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Integração com a Receita Federal — CBS</t>
+          <t>Histórico de incidentes</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Apuração assistida da CBS na Plataforma da RFB: autenticação, solicitação e retirada do resultado apurado por período. É a metade federal do confronto que hoje a conciliação simula.</t>
-        </is>
-      </c>
-      <c r="F153" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Severidade, causa classificada, duração, impacto quantificado e linha do tempo com detecção, alerta, diagnóstico e resolução.</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Integrações · F-12 Registrar o histórico de incidentes</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H153" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I153" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr"/>
@@ -8589,32 +8581,32 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Integração com o Comitê Gestor — IBS</t>
+          <t>Log de entregas com inspeção de payload</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Apuração assistida do IBS no CG-IBS: credencial própria, recebimento por webhook e arquivo diferencial, com a conta corrente fiscal por operação. É a outra metade do confronto.</t>
-        </is>
-      </c>
-      <c r="F154" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Evento, chave do documento, tentativas e status HTTP, com o JSON exato transmitido. Sem isso, depurar divergência com o ERP vira troca de e-mails.</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Integrações · F-14 Listar e inspecionar entregas</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H154" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr"/>
@@ -8640,17 +8632,17 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Integração RAD</t>
+          <t>Reenvio de entrega</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Geração e liquidação da guia de recolhimento pelo adquirente junto ao órgão arrecadador, com retorno do pagamento. Hoje a guia é produzida dentro do produto e o comprovante volta à mão.</t>
-        </is>
-      </c>
-      <c r="F155" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Individual ou em lote. A especificação diz que o SplitHub reenvia até receber 200 OK, mas não define o teto — o reenvio manual cobre o caso em que a automática desiste.</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Integrações · F-15 Reenviar entrega</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -8658,14 +8650,14 @@
           <t>Ação</t>
         </is>
       </c>
-      <c r="H155" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J155" s="3" t="inlineStr"/>
@@ -8691,27 +8683,27 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Integração Databricks para comprovantes</t>
+          <t>Comprovantes recebidos do ERP</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Ingestão de comprovantes de recolhimento a partir do lakehouse do cliente, em vez de upload arquivo a arquivo. É o que alimenta a conciliação financeira em volume.</t>
-        </is>
-      </c>
-      <c r="F156" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Chamadas ao endpoint de comprovante, com identificador da guia, meio, valor e resultado. As rejeitadas aparecem isoladas, com o motivo.</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Integrações · F-16 Listar comprovantes recebidos e isolar rejeitados</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H156" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I156" s="6" t="inlineStr">
@@ -8719,8 +8711,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J156" s="3" t="inlineStr"/>
-      <c r="K156" s="3" t="inlineStr"/>
+      <c r="J156" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L156" s="3" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
       <c r="N156" s="7" t="inlineStr"/>
@@ -8732,32 +8732,32 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Painel unificado da jornada do documento</t>
+          <t>Teste de conexão</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Cinco marcos por documento — ingestão, confirmação do governo, IBS pago, CBS pago e crédito apropriado — com o volume parado em cada um. Mostra onde a jornada trava antes de o crédito estar garantido.</t>
+          <t>Dispara um evento de teste com payload fictício e mostra a resposta HTTP. Valida a URL antes de a política de execução depender dela.</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-05 Apresentar o painel unificado</t>
+          <t>PRD de Integrações · F-08 Testar conexão</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
@@ -8765,9 +8765,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I157" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I157" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J157" s="3" t="inlineStr"/>
@@ -8783,37 +8783,37 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Confronto com a Apuração Assistida</t>
+          <t>Integração com a Receita Federal — CBS</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Compara o que o SplitHub apurou com o que a Apuração Assistida devolveu, documento a documento. Divergência vira inconsistência CAPUR, por tributo.</t>
-        </is>
-      </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Conciliação IBS/CBS · F-01 Confrontar valores com a Apuração Assistida</t>
+          <t>Apuração assistida da CBS na Plataforma da RFB: autenticação, solicitação e retirada do resultado apurado por período. É a metade federal do confronto que hoje a conciliação simula.</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H158" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I158" s="6" t="inlineStr">
@@ -8834,37 +8834,37 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Conciliação financeira pelos comprovantes</t>
+          <t>Integração com o Comitê Gestor — IBS</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Confere o valor recolhido contra o valor devido usando os comprovantes recebidos. Divergência vira inconsistência CFIN, por tributo.</t>
-        </is>
-      </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Conciliação IBS/CBS · F-02 Derivar a conciliação financeira dos comprovantes</t>
+          <t>Apuração assistida do IBS no CG-IBS: credencial própria, recebimento por webhook e arquivo diferencial, com a conta corrente fiscal por operação. É a outra metade do confronto.</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
-        </is>
-      </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H159" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I159" s="6" t="inlineStr">
@@ -8885,37 +8885,37 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Sequenciamento das duas conciliações</t>
+          <t>Integração RAD</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>A conciliação financeira só é avaliada depois de a apuração fechar. Conciliar pagamento contra um valor que o governo ainda não confirmou produz divergência falsa.</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Conciliação IBS/CBS · F-03 Sequenciar os dois processos</t>
+          <t>Geração e liquidação da guia de recolhimento pelo adquirente junto ao órgão arrecadador, com retorno do pagamento. Hoje a guia é produzida dentro do produto e o comprovante volta à mão.</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H160" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I160" s="6" t="inlineStr">
@@ -8936,37 +8936,37 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Próxima ação sugerida por documento</t>
+          <t>Integração Databricks para comprovantes</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Cada documento carrega a ação que destrava a jornada: cobrar comprovante, abrir inconsistência, reprocessar a apuração ou apropriar o crédito.</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Conciliação IBS/CBS · F-04 Sugerir a próxima ação por documento</t>
+          <t>Ingestão de comprovantes de recolhimento a partir do lakehouse do cliente, em vez de upload arquivo a arquivo. É o que alimenta a conciliação financeira em volume.</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H161" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I161" s="6" t="inlineStr">
@@ -8974,16 +8974,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J161" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K161" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J161" s="3" t="inlineStr"/>
+      <c r="K161" s="3" t="inlineStr"/>
       <c r="L161" s="3" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
       <c r="N161" s="7" t="inlineStr"/>
@@ -9005,22 +8997,22 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Listagem de registros com oito filtros</t>
+          <t>Painel unificado da jornada do documento</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Registros fiscais filtrados por tipo de documento, estado CAPUR, estado CFIN, tributo, entidade, período, valor e fornecedor.</t>
+          <t>Cinco marcos por documento — ingestão, confirmação do governo, IBS pago, CBS pago e crédito apropriado — com o volume parado em cada um. Mostra onde a jornada trava antes de o crédito estar garantido.</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-06 Listar registros fiscais com oito filtros</t>
+          <t>PRD de Conciliação IBS/CBS · F-05 Apresentar o painel unificado</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -9056,17 +9048,17 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Propagação do resultado para documento e registros</t>
+          <t>Confronto com a Apuração Assistida</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>O resultado da conciliação de cada registro sobe para o documento pela regra de pior estado, e o documento só fica conciliado quando IBS e CBS fecham.</t>
+          <t>Compara o que o SplitHub apurou com o que a Apuração Assistida devolveu, documento a documento. Divergência vira inconsistência CAPUR, por tributo.</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-07 Propagar o resultado para documento e registros</t>
+          <t>PRD de Conciliação IBS/CBS · F-01 Confrontar valores com a Apuração Assistida</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -9107,22 +9099,22 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Recorte por múltiplos períodos</t>
+          <t>Conciliação financeira pelos comprovantes</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Seleção de várias competências ao mesmo tempo, porque divergência de apuração costuma aparecer na virada do mês.</t>
+          <t>Confere o valor recolhido contra o valor devido usando os comprovantes recebidos. Divergência vira inconsistência CFIN, por tributo.</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-08 Recortar por múltiplos períodos</t>
+          <t>PRD de Conciliação IBS/CBS · F-02 Derivar a conciliação financeira dos comprovantes</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
@@ -9135,16 +9127,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J164" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J164" s="3" t="inlineStr"/>
+      <c r="K164" s="3" t="inlineStr"/>
       <c r="L164" s="3" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
       <c r="N164" s="7" t="inlineStr"/>
@@ -9161,27 +9145,27 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Resumo por tributo na competência</t>
+          <t>Sequenciamento das duas conciliações</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Saldo inicial, créditos apropriados, créditos utilizados, débitos, débitos extintos e tributo a pagar, com IBS e CBS em linhas próprias.</t>
-        </is>
-      </c>
-      <c r="F165" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>A conciliação financeira só é avaliada depois de a apuração fechar. Conciliar pagamento contra um valor que o governo ainda não confirmou produz divergência falsa.</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Conciliação IBS/CBS · F-03 Sequenciar os dois processos</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
@@ -9212,27 +9196,27 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Posição detalhada de créditos e débitos</t>
+          <t>Próxima ação sugerida por documento</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Abre o resumo em créditos a apropriar, apropriados e utilizados, e em débitos extintos e em aberto, com o percentual de cada faixa.</t>
-        </is>
-      </c>
-      <c r="F166" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Cada documento carrega a ação que destrava a jornada: cobrar comprovante, abrir inconsistência, reprocessar a apuração ou apropriar o crédito.</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Conciliação IBS/CBS · F-04 Sugerir a próxima ação por documento</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
@@ -9240,13 +9224,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I166" s="11" t="inlineStr">
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J166" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J166" s="3" t="inlineStr"/>
-      <c r="K166" s="3" t="inlineStr"/>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L166" s="3" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
       <c r="N166" s="7" t="inlineStr"/>
@@ -9263,27 +9255,27 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Cálculo da competência</t>
+          <t>Listagem de registros com oito filtros</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Recalcula a apuração a partir dos documentos e registros do período, registrando data e hora da última execução.</t>
-        </is>
-      </c>
-      <c r="F167" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Registros fiscais filtrados por tipo de documento, estado CAPUR, estado CFIN, tributo, entidade, período, valor e fornecedor.</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Conciliação IBS/CBS · F-06 Listar registros fiscais com oito filtros</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
@@ -9314,27 +9306,27 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Conclusão e reabertura da apuração</t>
+          <t>Propagação do resultado para documento e registros</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Fecha a competência para congelar a posição, e permite reabrir quando um documento retardatário ou uma conciliação muda o resultado.</t>
-        </is>
-      </c>
-      <c r="F168" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>O resultado da conciliação de cada registro sobe para o documento pela regra de pior estado, e o documento só fica conciliado quando IBS e CBS fecham.</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Conciliação IBS/CBS · F-07 Propagar o resultado para documento e registros</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
@@ -9365,27 +9357,27 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Abas Resumo, Créditos e Débitos</t>
+          <t>Recorte por múltiplos períodos</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Três recortes da mesma competência: o consolidado por tributo, a composição do crédito e a composição do débito.</t>
-        </is>
-      </c>
-      <c r="F169" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Seleção de várias competências ao mesmo tempo, porque divergência de apuração costuma aparecer na virada do mês.</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Conciliação IBS/CBS · F-08 Recortar por múltiplos períodos</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
@@ -9398,8 +9390,16 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J169" s="3" t="inlineStr"/>
-      <c r="K169" s="3" t="inlineStr"/>
+      <c r="J169" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L169" s="3" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
       <c r="N169" s="7" t="inlineStr"/>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Navegação entre competências</t>
+          <t>Resumo por tributo na competência</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Troca de período com o estado da apuração visível — calculada, concluída ou reaberta.</t>
+          <t>Saldo inicial, créditos apropriados, créditos utilizados em compensação, débitos, débitos extintos e tributo a pagar, com IBS e CBS em linhas próprias. Crédito ressarcido não conta como utilizado.</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Exportação da apuração</t>
+          <t>Posição detalhada de créditos e débitos</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Gera o arquivo da posição apurada para conferência fora do sistema e para anexar ao fechamento contábil.</t>
+          <t>Abre o resumo em créditos a apropriar, apropriados e utilizados, e em débitos extintos e em aberto, com o percentual de cada faixa.</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
@@ -9495,7 +9495,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I171" s="11" t="inlineStr">
+      <c r="I171" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -9513,27 +9513,27 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Assistente Tributário</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Chat livre sobre a legislação</t>
+          <t>Cálculo da competência</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Pergunta aberta sobre IBS, CBS e split payment respondida a partir das fontes indexadas, com a referência do dispositivo.</t>
-        </is>
-      </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Analytics · F-15 Responder perguntas sobre a legislação</t>
+          <t>Recalcula a apuração a partir dos documentos e registros do período, registrando data e hora da última execução.</t>
+        </is>
+      </c>
+      <c r="F172" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -9546,9 +9546,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I172" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J172" s="3" t="inlineStr"/>
@@ -9564,27 +9564,27 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Assistente Tributário</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Diagnóstico guiado por árvore de decisão</t>
+          <t>Conclusão e reabertura da apuração</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Fluxo de perguntas fechadas que leva o operador até o enquadramento do caso, sem depender de ele saber formular a pergunta certa.</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Analytics · F-16 Conduzir um diagnóstico guiado</t>
+          <t>Fecha a competência para congelar a posição, e permite reabrir quando um documento retardatário ou uma conciliação muda o resultado.</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -9597,9 +9597,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I173" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J173" s="3" t="inlineStr"/>
@@ -9615,27 +9615,27 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Assistente Tributário</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Fontes indexadas com link para a norma</t>
+          <t>Abas Resumo, Créditos e Débitos</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>LC 214/2025 e Decreto 12.955/2026 indexados e acessíveis, com as notas técnicas da RFB em indexação.</t>
-        </is>
-      </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Analytics · F-17 Listar e abrir as fontes indexadas</t>
+          <t>Três recortes da mesma competência: o consolidado por tributo, a composição do crédito e a composição do débito.</t>
+        </is>
+      </c>
+      <c r="F174" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -9648,9 +9648,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I174" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J174" s="3" t="inlineStr"/>
@@ -9666,27 +9666,27 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Assistente Tributário</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Histórico de conversas</t>
+          <t>Navegação entre competências</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Conversas anteriores preservadas na lateral, para retomar um diagnóstico sem refazer o caminho.</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Analytics · F-18 Preservar o histórico de conversas</t>
+          <t>Troca de período com o estado da apuração visível — calculada, concluída ou reaberta.</t>
+        </is>
+      </c>
+      <c r="F175" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -9699,9 +9699,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I175" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J175" s="3" t="inlineStr"/>
@@ -9717,32 +9717,32 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Relatórios agendados por módulo</t>
+          <t>Exportação da apuração</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Envio recorrente de crédito, débito, inconsistências, pagamentos ou consolidado, com destinatários, recorrência, dia e hora e formato.</t>
-        </is>
-      </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Automações · F-01 Agendar relatório por módulo</t>
+          <t>Gera o arquivo da posição apurada para conferência fora do sistema e para anexar ao fechamento contábil.</t>
+        </is>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
@@ -9750,7 +9750,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I176" s="11" t="inlineStr">
+      <c r="I176" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -9768,27 +9768,27 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Ativação, edição e exclusão de agendamento</t>
+          <t>Saída para ressarcimento no transporte do saldo</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Liga e desliga um relatório sem perder a configuração, e mostra último e próximo envio.</t>
+          <t>O saldo que vai para intenção ou pedido não é transportado para compensação, e o crédito ressarcido fica fora dos utilizados — não abate tributo a pagar.</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-02 Ligar, desligar e excluir agendamento</t>
+          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -9801,7 +9801,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I177" s="11" t="inlineStr">
+      <c r="I177" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -9819,32 +9819,32 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Assistente Tributário</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Integração ITSM por evento</t>
+          <t>Chat livre sobre a legislação</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Quatro eventos do produto — nova inconsistência, status alterado, registro próximo do vencimento e conciliação parada — abrem chamado no sistema de ITSM, cada um ligável em separado.</t>
+          <t>Pergunta aberta sobre IBS, CBS e split payment respondida a partir das fontes indexadas, com a referência do dispositivo.</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-04 Escolher quais eventos abrem chamado</t>
+          <t>PRD de Analytics · F-15 Responder perguntas sobre a legislação</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
@@ -9857,16 +9857,8 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="J178" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J178" s="3" t="inlineStr"/>
+      <c r="K178" s="3" t="inlineStr"/>
       <c r="L178" s="3" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
       <c r="N178" s="7" t="inlineStr"/>
@@ -9878,32 +9870,32 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Assistente Tributário</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Mapeamento dos campos do chamado</t>
+          <t>Diagnóstico guiado por árvore de decisão</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Título, prioridade e categoria montados por template com variáveis do registro, para o chamado chegar tratável do outro lado.</t>
+          <t>Fluxo de perguntas fechadas que leva o operador até o enquadramento do caso, sem depender de ele saber formular a pergunta certa.</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-05 Montar o chamado por template</t>
+          <t>PRD de Analytics · F-16 Conduzir um diagnóstico guiado</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">
@@ -9911,9 +9903,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I179" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I179" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J179" s="3" t="inlineStr"/>
@@ -9929,27 +9921,27 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Assistente Tributário</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Histórico de chamados abertos</t>
+          <t>Fontes indexadas com link para a norma</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Evento, registro, status HTTP e número do chamado de cada envio, inclusive os que falharam.</t>
+          <t>LC 214/2025 e Decreto 12.955/2026 indexados e acessíveis, com as notas técnicas da RFB em indexação.</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-06 Acompanhar o histórico de envios ao ITSM</t>
+          <t>PRD de Analytics · F-17 Listar e abrir as fontes indexadas</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -9962,9 +9954,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I180" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I180" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J180" s="3" t="inlineStr"/>
@@ -9980,32 +9972,32 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Assistente Tributário</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Régua de cobrança pré-vencimento</t>
+          <t>Histórico de conversas</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Sequência de avisos antes do vencimento, com gatilho em dias, número máximo de envios e intervalo entre eles.</t>
+          <t>Conversas anteriores preservadas na lateral, para retomar um diagnóstico sem refazer o caminho.</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-07 Criar régua de cobrança pelo assistente</t>
+          <t>PRD de Analytics · F-18 Preservar o histórico de conversas</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
@@ -10013,9 +10005,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I181" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J181" s="3" t="inlineStr"/>
@@ -10041,17 +10033,17 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Régua de cobrança pós-vencimento</t>
+          <t>Relatórios agendados por módulo</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Sequência de cobranças depois do vencimento, com escalada gerencial e abertura de chamado quando a mora persiste.</t>
+          <t>Envio recorrente de crédito, débito, inconsistências, pagamentos ou consolidado, com destinatários, recorrência, dia e hora e formato.</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-07 Criar régua de cobrança pelo assistente</t>
+          <t>PRD de Automações · F-01 Agendar relatório por módulo</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -10064,9 +10056,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I182" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J182" s="3" t="inlineStr"/>
@@ -10092,22 +10084,22 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Etapas da régua com canal e condição</t>
+          <t>Ativação, edição e exclusão de agendamento</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Cada etapa define o dia relativo ao vencimento, o canal e a condição de disparo, e pode escalar para a régua seguinte.</t>
+          <t>Liga e desliga um relatório sem perder a configuração, e mostra último e próximo envio.</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-08 Desenhar as etapas da régua</t>
+          <t>PRD de Automações · F-02 Ligar, desligar e excluir agendamento</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
@@ -10115,9 +10107,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I183" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I183" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J183" s="3" t="inlineStr"/>
@@ -10143,17 +10135,17 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Template de mensagem com variáveis</t>
+          <t>Integração ITSM por evento</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Assunto e corpo com fornecedor, registro, tributo, valor, vencimento e dias de atraso preenchidos no envio.</t>
+          <t>Quatro eventos do produto — nova inconsistência, status alterado, registro próximo do vencimento e conciliação parada — abrem chamado no sistema de ITSM, cada um ligável em separado.</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-09 Escrever a mensagem com variáveis</t>
+          <t>PRD de Automações · F-04 Escolher quais eventos abrem chamado</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -10166,13 +10158,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I184" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J184" s="3" t="inlineStr"/>
-      <c r="K184" s="3" t="inlineStr"/>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J184" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L184" s="3" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
       <c r="N184" s="7" t="inlineStr"/>
@@ -10194,22 +10194,22 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Disparos por fornecedor e etapa</t>
+          <t>Mapeamento dos campos do chamado</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Histórico do que foi enviado, para quem, em que etapa e com que resultado — entregue, aberto, devolvido ou convertido em chamado.</t>
+          <t>Título, prioridade e categoria montados por template com variáveis do registro, para o chamado chegar tratável do outro lado.</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-11 Acompanhar os disparos por fornecedor</t>
+          <t>PRD de Automações · F-05 Montar o chamado por template</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr">
@@ -10217,9 +10217,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I185" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J185" s="3" t="inlineStr"/>
@@ -10245,22 +10245,22 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Auditoria da régua com motivo</t>
+          <t>Histórico de chamados abertos</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Criação, ativação e cada alteração de parâmetro ficam registradas com autor, data e justificativa.</t>
+          <t>Evento, registro, status HTTP e número do chamado de cada envio, inclusive os que falharam.</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-12 Auditar a régua</t>
+          <t>PRD de Automações · F-06 Acompanhar o histórico de envios ao ITSM</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
@@ -10268,9 +10268,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I186" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J186" s="3" t="inlineStr"/>
@@ -10296,17 +10296,17 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Motor de execução das automações</t>
+          <t>Régua de cobrança pré-vencimento</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>O que faz a régua disparar: avaliação diária dos registros contra as etapas, respeito ao teto de envios e ao intervalo, e registro do disparo. Não existe hoje — o módulo desenha automações e não executa nenhuma.</t>
-        </is>
-      </c>
-      <c r="F187" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Sequência de avisos antes do vencimento, com gatilho em dias, número máximo de envios e intervalo entre eles.</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações · F-07 Criar régua de cobrança pelo assistente</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -10314,9 +10314,9 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="H187" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I187" s="6" t="inlineStr">
@@ -10347,17 +10347,17 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Envio de e-mail transacional</t>
+          <t>Régua de cobrança pós-vencimento</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Provedor de envio, com registro de entrega e devolução. Serve à régua e também ao convite do fornecedor, que hoje é simulado na tela. Sem ele, régua ativa é régua que não cobra ninguém.</t>
-        </is>
-      </c>
-      <c r="F188" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Sequência de cobranças depois do vencimento, com escalada gerencial e abertura de chamado quando a mora persiste.</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações · F-07 Criar régua de cobrança pelo assistente</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -10365,9 +10365,9 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="H188" s="10" t="inlineStr">
-        <is>
-          <t>Nova</t>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I188" s="6" t="inlineStr">
@@ -10393,27 +10393,27 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Listagem de membros da organização</t>
+          <t>Etapas da régua com canal e condição</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Usuário, e-mail, perfil, último acesso e situação, com o total de ativos, administradores, convites pendentes e inativos.</t>
-        </is>
-      </c>
-      <c r="F189" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Cada etapa define o dia relativo ao vencimento, o canal e a condição de disparo, e pode escalar para a régua seguinte.</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações · F-08 Desenhar as etapas da régua</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
@@ -10421,9 +10421,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I189" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J189" s="3" t="inlineStr"/>
@@ -10444,22 +10444,22 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Perfis de acesso</t>
+          <t>Template de mensagem com variáveis</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>Administrador, Analista Fiscal, Controller e Auditor, cada um com o alcance declarado por módulo e a permissão de agir ou só ler.</t>
-        </is>
-      </c>
-      <c r="F190" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Assunto e corpo com fornecedor, registro, tributo, valor, vencimento e dias de atraso preenchidos no envio.</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações · F-09 Escrever a mensagem com variáveis</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -10472,9 +10472,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I190" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J190" s="3" t="inlineStr"/>
@@ -10495,27 +10495,27 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Convite de usuário</t>
+          <t>Disparos por fornecedor e etapa</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Convida por e-mail com o perfil já definido, e reenvia o convite que não foi aceito.</t>
-        </is>
-      </c>
-      <c r="F191" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Histórico do que foi enviado, para quem, em que etapa e com que resultado — entregue, aberto, devolvido ou convertido em chamado.</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações · F-11 Acompanhar os disparos por fornecedor</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr">
@@ -10523,9 +10523,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I191" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J191" s="3" t="inlineStr"/>
@@ -10546,27 +10546,27 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Revogação e reativação de acesso</t>
+          <t>Auditoria da régua com motivo</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Corta o acesso sem apagar o usuário, preservando a trilha do que ele fez, e devolve o acesso quando necessário.</t>
-        </is>
-      </c>
-      <c r="F192" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Criação, ativação e cada alteração de parâmetro ficam registradas com autor, data e justificativa.</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações · F-12 Auditar a régua</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr">
@@ -10574,9 +10574,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I192" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J192" s="3" t="inlineStr"/>
@@ -10597,17 +10597,17 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Abas por situação do acesso</t>
+          <t>Motor de execução das automações</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Todos, ativos, pendentes e inativos, para achar rápido quem está sem acesso ou com convite parado.</t>
+          <t>O que faz a régua disparar: avaliação diária dos registros contra as etapas, respeito ao teto de envios e ao intervalo, e registro do disparo. Não existe hoje — o módulo desenha automações e não executa nenhuma.</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
@@ -10617,17 +10617,17 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
-        </is>
-      </c>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="I193" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H193" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J193" s="3" t="inlineStr"/>
@@ -10648,17 +10648,17 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Painel de acessos externos</t>
+          <t>Envio de e-mail transacional</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Todos os acessos de fornecedores numa tela, com busca, filtro por situação e a trilha recente. Responde quem, de fora da organização, enxerga os dados hoje.</t>
+          <t>Provedor de envio, com registro de entrega e devolução. Serve à régua e também ao convite do fornecedor, que hoje é simulado na tela. Sem ele, régua ativa é régua que não cobra ninguém.</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
@@ -10668,12 +10668,12 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
-        </is>
-      </c>
-      <c r="H194" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H194" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I194" s="6" t="inlineStr">
@@ -10682,11 +10682,7 @@
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr"/>
-      <c r="K194" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="K194" s="3" t="inlineStr"/>
       <c r="L194" s="3" t="inlineStr"/>
       <c r="M194" s="7" t="inlineStr"/>
       <c r="N194" s="7" t="inlineStr"/>
@@ -10698,27 +10694,27 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Saldo credor por período e tributo</t>
+          <t>Listagem de membros da organização</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
+          <t>Usuário, e-mail, perfil, último acesso e situação, com o total de ativos, administradores, convites pendentes e inativos.</t>
+        </is>
+      </c>
+      <c r="F195" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -10731,7 +10727,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I195" s="11" t="inlineStr">
+      <c r="I195" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -10749,32 +10745,32 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Comparar compensar e ressarcir</t>
+          <t>Perfis de acesso</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
-        </is>
-      </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
+          <t>Administrador, Analista Fiscal, Controller e Auditor, cada um com o alcance declarado por módulo e a permissão de agir ou só ler.</t>
+        </is>
+      </c>
+      <c r="F196" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
@@ -10782,9 +10778,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I196" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I196" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J196" s="3" t="inlineStr"/>
@@ -10800,27 +10796,27 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Declarar e cancelar a intenção</t>
+          <t>Convite de usuário</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
+          <t>Convida por e-mail com o perfil já definido, e reenvia o convite que não foi aceito.</t>
+        </is>
+      </c>
+      <c r="F197" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -10833,7 +10829,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I197" s="11" t="inlineStr">
+      <c r="I197" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -10851,27 +10847,27 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Montar o pedido de CBS por documento</t>
+          <t>Revogação e reativação de acesso</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
-        </is>
-      </c>
-      <c r="F198" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
+          <t>Corta o acesso sem apagar o usuário, preservando a trilha do que ele fez, e devolve o acesso quando necessário.</t>
+        </is>
+      </c>
+      <c r="F198" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -10884,7 +10880,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I198" s="11" t="inlineStr">
+      <c r="I198" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -10902,32 +10898,32 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
+          <t>Abas por situação do acesso</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
-        </is>
-      </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
+          <t>Todos, ativos, pendentes e inativos, para achar rápido quem está sem acesso ou com convite parado.</t>
+        </is>
+      </c>
+      <c r="F199" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
@@ -10935,7 +10931,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I199" s="11" t="inlineStr">
+      <c r="I199" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -10953,27 +10949,27 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Listagem de pedidos do tributo</t>
+          <t>Painel de acessos externos</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
-        </is>
-      </c>
-      <c r="F200" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
+          <t>Todos os acessos de fornecedores numa tela, com busca, filtro por situação e a trilha recente. Responde quem, de fora da organização, enxerga os dados hoje.</t>
+        </is>
+      </c>
+      <c r="F200" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -10986,13 +10982,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I200" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J200" s="3" t="inlineStr"/>
-      <c r="K200" s="3" t="inlineStr"/>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L200" s="3" t="inlineStr"/>
       <c r="M200" s="7" t="inlineStr"/>
       <c r="N200" s="7" t="inlineStr"/>
@@ -11014,22 +11014,22 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Acompanhar análise e fiscalização</t>
+          <t>Saldo credor por período e tributo</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
+          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
+          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
@@ -11037,7 +11037,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I201" s="11" t="inlineStr">
+      <c r="I201" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -11065,22 +11065,22 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Registrar decisão e cancelamento</t>
+          <t>Comparar compensar e ressarcir</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
+          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
+          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
@@ -11088,9 +11088,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I202" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I202" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J202" s="3" t="inlineStr"/>
@@ -11116,17 +11116,17 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Conciliar o recebimento com Selic</t>
+          <t>Declarar e cancelar a intenção</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
+          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
+          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -11139,7 +11139,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I203" s="11" t="inlineStr">
+      <c r="I203" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -11167,22 +11167,22 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Previsão de entrada de caixa por tributo</t>
+          <t>Montar o pedido de CBS por documento</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
+          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
+          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
@@ -11190,9 +11190,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I204" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I204" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J204" s="3" t="inlineStr"/>
@@ -11218,22 +11218,22 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Alertas de prazo do ressarcimento</t>
+          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
+          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
+          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr">
@@ -11241,7 +11241,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I205" s="11" t="inlineStr">
+      <c r="I205" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -11269,22 +11269,22 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Conferência do saldo com a Receita (CBS)</t>
+          <t>Listagem de pedidos do tributo</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
+          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
+          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I206" s="11" t="inlineStr">
+      <c r="I206" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -11320,22 +11320,22 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Trilha de auditoria do pedido</t>
+          <t>Acompanhar análise e fiscalização</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
+          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-13 Auditar</t>
+          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
@@ -11343,7 +11343,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I207" s="11" t="inlineStr">
+      <c r="I207" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -11371,22 +11371,22 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Impedimentos do IBS</t>
+          <t>Registrar decisão e cancelamento</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
+          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
+          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H208" s="3" t="inlineStr">
@@ -11394,7 +11394,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I208" s="11" t="inlineStr">
+      <c r="I208" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -11422,17 +11422,17 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Registrar o pedido de IBS (protocolo)</t>
+          <t>Conciliar o recebimento com Selic</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -11445,7 +11445,7 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I209" s="11" t="inlineStr">
+      <c r="I209" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
@@ -11457,13 +11457,319 @@
       <c r="N209" s="7" t="inlineStr"/>
       <c r="O209" s="8" t="inlineStr"/>
     </row>
+    <row r="210">
+      <c r="A210" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>Previsão de entrada de caixa por tributo</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I210" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J210" s="3" t="inlineStr"/>
+      <c r="K210" s="3" t="inlineStr"/>
+      <c r="L210" s="3" t="inlineStr"/>
+      <c r="M210" s="7" t="inlineStr"/>
+      <c r="N210" s="7" t="inlineStr"/>
+      <c r="O210" s="8" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>Alertas de prazo do ressarcimento</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I211" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J211" s="3" t="inlineStr"/>
+      <c r="K211" s="3" t="inlineStr"/>
+      <c r="L211" s="3" t="inlineStr"/>
+      <c r="M211" s="7" t="inlineStr"/>
+      <c r="N211" s="7" t="inlineStr"/>
+      <c r="O211" s="8" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>Conferência do saldo com a Receita (CBS)</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I212" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J212" s="3" t="inlineStr"/>
+      <c r="K212" s="3" t="inlineStr"/>
+      <c r="L212" s="3" t="inlineStr"/>
+      <c r="M212" s="7" t="inlineStr"/>
+      <c r="N212" s="7" t="inlineStr"/>
+      <c r="O212" s="8" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>Trilha de auditoria do pedido</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-13 Auditar</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I213" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J213" s="3" t="inlineStr"/>
+      <c r="K213" s="3" t="inlineStr"/>
+      <c r="L213" s="3" t="inlineStr"/>
+      <c r="M213" s="7" t="inlineStr"/>
+      <c r="N213" s="7" t="inlineStr"/>
+      <c r="O213" s="8" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>Impedimentos do IBS</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I214" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J214" s="3" t="inlineStr"/>
+      <c r="K214" s="3" t="inlineStr"/>
+      <c r="L214" s="3" t="inlineStr"/>
+      <c r="M214" s="7" t="inlineStr"/>
+      <c r="N214" s="7" t="inlineStr"/>
+      <c r="O214" s="8" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>Registrar o pedido de IBS (protocolo)</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I215" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J215" s="3" t="inlineStr"/>
+      <c r="K215" s="3" t="inlineStr"/>
+      <c r="L215" s="3" t="inlineStr"/>
+      <c r="M215" s="7" t="inlineStr"/>
+      <c r="N215" s="7" t="inlineStr"/>
+      <c r="O215" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O209"/>
+  <autoFilter ref="A1:O215"/>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
+    <dataValidation sqref="M2:M215" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
       <formula1>"M0,M1,M2,Fora"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N209" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
+    <dataValidation sqref="N2:N215" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11508,9 +11814,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId46"/>
@@ -11564,11 +11870,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId104"/>
@@ -11595,19 +11901,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId143"/>
@@ -11618,12 +11924,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId159"/>
@@ -11633,6 +11939,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId171"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11714,7 +12026,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
@@ -11723,11 +12035,11 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Só o que responde “onde está meu crédito hoje”. Forecast e cockpit dependem de série histórica que o piloto ainda não tem.</t>
+          <t>Só o que responde “onde está meu crédito hoje”. Forecast e cockpit dependem de série histórica que o piloto ainda não tem. O card de saldo credor e ressarcimento entra em M1 (D17).</t>
         </is>
       </c>
     </row>
@@ -11746,7 +12058,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>3</v>
@@ -11755,11 +12067,11 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>O módulo que a tese defende entra quase inteiro: 11 de 14. Ficam fora três gráficos analíticos — eles explicam o crédito, não o garantem. O Top 5 e Top 10 de fornecedores subiu na revisão de 15/09: saber de quem cobrar primeiro é operação, não análise.</t>
+          <t>O módulo que a tese defende entra quase inteiro: 11 de 14. Ficam fora três gráficos analíticos — eles explicam o crédito, não o garantem. O Top 5 e Top 10 de fornecedores subiu na revisão de 15/09: saber de quem cobrar primeiro é operação, não análise. O painel Ressarcimento no ciclo do crédito entra em M1 (D17): o M0 do módulo não muda.</t>
         </is>
       </c>
     </row>
@@ -11778,7 +12090,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -11787,11 +12099,11 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Débito entra só para a apuração fechar. O produto se vende pelo crédito.</t>
+          <t>Débito entra só para a apuração fechar. O produto se vende pelo crédito. O aviso da trava da intenção de ressarcimento entra em M1 (D17).</t>
         </is>
       </c>
     </row>
@@ -11842,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -11851,11 +12163,11 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>A inconsistência é o que impede o crédito de morrer em silêncio. Na revisão de 15/09 a atribuição de responsável entrou — inconsistência sem dono não é tratada — e os filtros multiselect saíram.</t>
+          <t>A inconsistência é o que impede o crédito de morrer em silêncio. Na revisão de 15/09 a atribuição de responsável entrou — inconsistência sem dono não é tratada — e os filtros multiselect saíram. A família Ressarcimento de inconsistências entra em M1 (D17).</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12346,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>1</v>
@@ -12043,11 +12355,11 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Hierarquia e filtro de grupo econômico atravessam todas as telas — sem eles, nenhum número fecha.</t>
+          <t>Hierarquia e filtro de grupo econômico atravessam todas as telas — sem eles, nenhum número fecha. O enquadramento por órgão para o ressarcimento entra em M1 (D17).</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12538,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
@@ -12235,11 +12547,11 @@
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>A apuração é onde o crédito vira número exigível. Entra o ciclo calcular–concluir–reabrir.</t>
+          <t>A apuração é onde o crédito vira número exigível. Entra o ciclo calcular–concluir–reabrir. A saída para ressarcimento no transporte do saldo entra em M1 (D17); o ciclo do M0 não muda.</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12693,7 @@
         <v>114</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>24</v>
@@ -12390,7 +12702,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -13676,7 +13988,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>v2.4</t>
+          <t>v2.5</t>
         </is>
       </c>
     </row>
@@ -13700,7 +14012,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Mapa de Funcionalidades v2.3</t>
+          <t>Mapa de Funcionalidades v2.4</t>
         </is>
       </c>
     </row>
@@ -13712,7 +14024,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>208 funcionalidades · 21 módulos · 199 do mapa + 9 novas</t>
+          <t>214 funcionalidades · 21 módulos · 205 do mapa + 9 novas</t>
         </is>
       </c>
     </row>
@@ -13724,7 +14036,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>114 · 68 · 24 · 2</t>
+          <t>114 · 74 · 24 · 2</t>
         </is>
       </c>
     </row>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -17733,7 +17733,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>v2.7</t>
+          <t>v2.7.1</t>
         </is>
       </c>
     </row>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Como revisar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$290</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revisões'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O287"/>
+  <dimension ref="A1:O290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Catálogo tipificado em quatro famílias</t>
+          <t>Catálogo tipificado em seis famílias</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>PRD de Inconsistências · Seção 03 Cat&amp;aacute;logo de tipos</t>
+          <t>PRD de Inconsistências · Seção 03 Catálogo de tipos</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Ingestão de DFs</t>
+          <t>Inconsistências</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Upload CSV posicional (NF-e · CT-e · NFS-e)</t>
+          <t>Filtro por família de inconsistência</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Importação de arquivo CSV com layout de colunas posicionais fixo. Suporte aos tipos NF-e (Nota Fiscal Eletrônica), CT-e (Conhecimento de Transporte) e NFS-e (Nota Fiscal de Serviços).</t>
+          <t>Recorte pelas seis famílias do catálogo — documento, confronto com o Fisco, ciclo do crédito e do débito, recolhimento e comprovação, ressarcimento e integração. Escolher a família restringe o filtro de tipo às ocorrências daquela origem.</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
+          <t>PRD de Inconsistências · Seção 03 Catálogo de tipos</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -4522,9 +4522,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr"/>
@@ -4545,27 +4545,27 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Ingestão de DFs</t>
+          <t>Inconsistências</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Suporte a Entrada e Saída</t>
+          <t>Coluna Família na listagem de ocorrências</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>O mesmo pipeline processa DFs de entrada (créditos IBS/CBS) e de saída (débitos IBS/CBS), detectando o fluxo pelo campo "tipo" do CSV.</t>
+          <t>Chip com a letra e o nome da família na tabela de inconsistências, com a cor da própria família. Diz de onde a falha veio sem precisar interpretar o tipo.</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs · Seção 04 Modelo de dados</t>
+          <t>PRD de Inconsistências · Seção 03 Catálogo de tipos</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -4573,9 +4573,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr"/>
@@ -4596,27 +4596,27 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Ingestão de DFs</t>
+          <t>Inconsistências</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Pré-visualização antes de confirmar</t>
+          <t>Filtro de família e de tipo no kanban</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Após seleção do arquivo, uma tabela de prévia é gerada a partir do CSV antes de qualquer importação ser executada. O operador valida os dados e confirma ou cancela.</t>
+          <t>O quadro passa a filtrar por família, com a contagem de cada uma, e por tipo dentro da família escolhida — antes separava só por fluxo e prioridade.</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
+          <t>PRD de Inconsistências · Seção 03 Catálogo de tipos</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -4624,9 +4624,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr"/>
@@ -4652,12 +4652,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Validação binária: Importado / Inconsistência</t>
+          <t>Upload CSV posicional (NF-e · CT-e · NFS-e)</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Cada linha do CSV resulta em um de dois status: Importado (aprovado — DF entra no sistema com RFs criados) ou Inconsistência (falha — DF não importado, card de inconsistência gerado automaticamente).</t>
+          <t>Importação de arquivo CSV com layout de colunas posicionais fixo. Suporte aos tipos NF-e (Nota Fiscal Eletrônica), CT-e (Conhecimento de Transporte) e NFS-e (Nota Fiscal de Serviços).</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -4703,22 +4703,22 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Stub DF para documentos rejeitados</t>
+          <t>Suporte a Entrada e Saída</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>DFs com falha de ingestão são injetados em nfListaFiltradaGlobal como registros stub com statusImportacao:"falha", tornando-os visíveis nas listagens de Créditos com todos os dados disponíveis (entidade, CNPJ, valor, data).</t>
+          <t>O mesmo pipeline processa DFs de entrada (créditos IBS/CBS) e de saída (débitos IBS/CBS), detectando o fluxo pelo campo "tipo" do CSV.</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Ingestão de DFs</t>
+          <t>PRD de Ingestão de DFs · Seção 04 Modelo de dados</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Card de inconsistência automático</t>
+          <t>Pré-visualização antes de confirmar</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Para cada DF rejeitado, um card de inconsistência é criado e vinculado ao stub DF via nf._inconsistencias[]. Tipos: falha de layout (CSV malformado), CNPJ inválido (não encontrado na RFB) ou documento duplicado.</t>
+          <t>Após seleção do arquivo, uma tabela de prévia é gerada a partir do CSV antes de qualquer importação ser executada. O operador valida os dados e confirma ou cancela.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs · Seção 05 Pipeline e máquinas de estado</t>
+          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
@@ -4805,22 +4805,22 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Ingestão por API com credencial própria</t>
+          <t>Validação binária: Importado / Inconsistência</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>A conexão de ingestão passa a ter credencial emitida dentro do produto, com escopos de escrita e leitura. É o canal que torna o upload manual uma exceção.</t>
+          <t>Cada linha do CSV resulta em um de dois status: Importado (aprovado — DF entra no sistema com RFs criados) ou Inconsistência (falha — DF não importado, card de inconsistência gerado automaticamente).</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs · Seção 13 Integrações e dependências</t>
+          <t>PRD de Ingestão de DFs · F-03 Importar por upload de CSV</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -4856,22 +4856,22 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Ingestão em lote de até 500 documentos</t>
+          <t>Stub DF para documentos rejeitados</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Lote em JSON ou CSV, com identificador próprio para acompanhar o processamento do conjunto.</t>
+          <t>DFs com falha de ingestão são injetados em nfListaFiltradaGlobal como registros stub com statusImportacao:"falha", tornando-os visíveis nas listagens de Créditos com todos os dados disponíveis (entidade, CNPJ, valor, data).</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs</t>
+          <t>Não descrita no PRD de Ingestão de DFs</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
@@ -4879,9 +4879,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr"/>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Situação do documento na esteira</t>
+          <t>Card de inconsistência automático</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Recebido, em processamento, concluído ou com erro, com consulta por documento e por lote.</t>
+          <t>Para cada DF rejeitado, um card de inconsistência é criado e vinculado ao stub DF via nf._inconsistencias[]. Tipos: falha de layout (CSV malformado), CNPJ inválido (não encontrado na RFB) ou documento duplicado.</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs</t>
+          <t>PRD de Ingestão de DFs · Seção 05 Pipeline e máquinas de estado</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
@@ -4930,9 +4930,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr"/>
@@ -4958,22 +4958,22 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Imutabilidade do documento concluído</t>
+          <t>Ingestão por API com credencial própria</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Documento processado não é mais alterável; correção só em pendente ou com erro.</t>
+          <t>A conexão de ingestão passa a ter credencial emitida dentro do produto, com escopos de escrita e leitura. É o canal que torna o upload manual uma exceção.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ingestão de DFs</t>
+          <t>PRD de Ingestão de DFs · Seção 13 Integrações e dependências</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -4981,9 +4981,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr"/>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Vínculo ao contrato na entrada</t>
+          <t>Ingestão em lote de até 500 documentos</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>O documento chega amarrado ao contrato, com possibilidade de divergir dele no caso específico. É por aí que a elegibilidade ao RAD alcança o documento.</t>
+          <t>Lote em JSON ou CSV, com identificador próprio para acompanhar o processamento do conjunto.</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -5032,9 +5032,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr"/>
@@ -5050,32 +5050,32 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>FCT — Fluxo de Caixa Tributário</t>
+          <t>Ingestão de DFs</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Forecast de Fluxo Fiscal</t>
+          <t>Situação do documento na esteira</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Projeção de entradas tributárias (créditos IBS+CBS) e saídas (débitos e pagamentos) com média móvel progressiva calculada sobre os dados históricos disponíveis.</t>
+          <t>Recebido, em processamento, concluído ou com erro, com consulta por documento e por lote.</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-08 Projetar o fluxo fiscal</t>
+          <t>PRD de Ingestão de DFs</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -5083,9 +5083,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr"/>
@@ -5101,32 +5101,32 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>FCT — Fluxo de Caixa Tributário</t>
+          <t>Ingestão de DFs</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Média móvel progressiva</t>
+          <t>Imutabilidade do documento concluído</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>A média é calculada sobre os N meses históricos disponíveis, crescendo progressivamente à medida que mais dados são acumulados — sem período mínimo fixo.</t>
+          <t>Documento processado não é mais alterável; correção só em pendente ou com erro.</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · Seção 07 Indicadores e projeções</t>
+          <t>PRD de Ingestão de DFs</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -5134,9 +5134,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr"/>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>FCT — Fluxo de Caixa Tributário</t>
+          <t>Ingestão de DFs</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Corte realizado / projeção na data atual</t>
+          <t>Vínculo ao contrato na entrada</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Linha vertical posicionada na data atual separa visualmente os dados históricos realizados (traço sólido) das projeções futuras (traço pontilhado), em ambos os forecasts.</t>
+          <t>O documento chega amarrado ao contrato, com possibilidade de divergir dele no caso específico. É por aí que a elegibilidade ao RAD alcança o documento.</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-09 Separar realizado de projetado na data de corte</t>
+          <t>PRD de Ingestão de DFs</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Forecast de Aproveitamento de Crédito</t>
+          <t>Forecast de Fluxo Fiscal</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Projeção de quando os créditos a apropriar serão efetivamente utilizados para extinção de débitos, com base no ritmo histórico de aproveitamento do adquirente.</t>
+          <t>Projeção de entradas tributárias (créditos IBS+CBS) e saídas (débitos e pagamentos) com média móvel progressiva calculada sobre os dados históricos disponíveis.</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-10 Projetar o aproveitamento do crédito</t>
+          <t>PRD de Analytics · F-08 Projetar o fluxo fiscal</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -5264,17 +5264,17 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Insights: melhor mês · tendência · perda projetada</t>
+          <t>Média móvel progressiva</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Três insights calculados automaticamente: melhor mês histórico (maior volume de créditos), tendência (crescente/estável/queda com percentual) e perda projetada por não-aproveitamento de créditos disponíveis.</t>
+          <t>A média é calculada sobre os N meses históricos disponíveis, crescendo progressivamente à medida que mais dados são acumulados — sem período mínimo fixo.</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-11 Apresentar os insights do forecast</t>
+          <t>PRD de Analytics · Seção 07 Indicadores e projeções</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -5315,17 +5315,17 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Tabela mensal de aproveitamento</t>
+          <t>Corte realizado / projeção na data atual</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Tabela com colunas: Período, Créditos Gerados (IBS+CBS), Créditos Aproveitados e Percentual de Utilização — para cada mês do histórico disponível.</t>
+          <t>Linha vertical posicionada na data atual separa visualmente os dados históricos realizados (traço sólido) das projeções futuras (traço pontilhado), em ambos os forecasts.</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-14 Detalhar o fluxo mensal em tabela</t>
+          <t>PRD de Analytics · F-09 Separar realizado de projetado na data de corte</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -5366,22 +5366,22 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Retry automático de renderização</t>
+          <t>Forecast de Aproveitamento de Crédito</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Quando os dados assíncronos de nfListaFiltradaGlobal ainda não estão disponíveis no momento da renderização, o módulo FCT tenta novamente automaticamente.</t>
+          <t>Projeção de quando os créditos a apropriar serão efetivamente utilizados para extinção de débitos, com base no ritmo histórico de aproveitamento do adquirente.</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Analytics</t>
+          <t>PRD de Analytics · F-10 Projetar o aproveitamento do crédito</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Fluxo mensal com compensação, guia e saldo credor</t>
+          <t>Insights: melhor mês · tendência · perda projetada</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Cada mês mostra o débito e para onde ele foi: pago em dinheiro por split ou RAD, compensado com crédito, a recolher em guia e em aberto. A soma das quatro colunas fecha o débito do mês.</t>
+          <t>Três insights calculados automaticamente: melhor mês histórico (maior volume de créditos), tendência (crescente/estável/queda com percentual) e perda projetada por não-aproveitamento de créditos disponíveis.</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · Seção 01 Contexto e posicionamento</t>
+          <t>PRD de Analytics · F-11 Apresentar os insights do forecast</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -5440,9 +5440,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr"/>
@@ -5468,17 +5468,17 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Projeção pela ordem do art. 53</t>
+          <t>Tabela mensal de aproveitamento</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>A projeção compensa o saldo credor na ordem da lei e só sobre o débito que depende de crédito, porque o extinto por split ou RAD nunca disputou crédito.</t>
+          <t>Tabela com colunas: Período, Créditos Gerados (IBS+CBS), Créditos Aproveitados e Percentual de Utilização — para cada mês do histórico disponível.</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · Seção 01 Contexto e posicionamento</t>
+          <t>PRD de Analytics · F-14 Detalhar o fluxo mensal em tabela</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -5491,9 +5491,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr"/>
@@ -5519,22 +5519,22 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Alíquota efetiva mensal</t>
+          <t>Retry automático de renderização</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Percentual do faturamento que virou tributo não absorvido por crédito, mês a mês, contra a referência de 26,5%. Mede o aproveitamento real do crédito, não a alíquota nominal.</t>
+          <t>Quando os dados assíncronos de nfListaFiltradaGlobal ainda não estão disponíveis no momento da renderização, o módulo FCT tenta novamente automaticamente.</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · Seção 01 Contexto e posicionamento</t>
+          <t>Não descrita no PRD de Analytics</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -5542,9 +5542,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr"/>
@@ -5570,12 +5570,12 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Posição líquida — saldo credor mês a mês</t>
+          <t>Fluxo mensal com compensação, guia e saldo credor</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Linha do saldo credor apurado ao fim de cada período. Substitui o acumulado de crédito menos débito, que ignorava o débito extinto por split e RAD.</t>
+          <t>Cada mês mostra o débito e para onde ele foi: pago em dinheiro por split ou RAD, compensado com crédito, a recolher em guia e em aberto. A soma das quatro colunas fecha o débito do mês.</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Créditos a apropriar por mês de origem</t>
+          <t>Projeção pela ordem do art. 53</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Créditos ainda não apropriados distribuídos pelo mês do documento que os originou, separando condicionado, em risco e glosado.</t>
+          <t>A projeção compensa o saldo credor na ordem da lei e só sobre o débito que depende de crédito, porque o extinto por split ou RAD nunca disputou crédito.</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -5672,17 +5672,17 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Simulação por cenário de receita e de fornecedor</t>
+          <t>Alíquota efetiva mensal</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Horizonte, cenário de receita e comportamento do fornecedor — este último é o que mais move o resultado, porque é a dependência do pagamento em ação.</t>
+          <t>Percentual do faturamento que virou tributo não absorvido por crédito, mês a mês, contra a referência de 26,5%. Mede o aproveitamento real do crédito, não a alíquota nominal.</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics</t>
+          <t>PRD de Analytics · Seção 01 Contexto e posicionamento</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -5695,9 +5695,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr"/>
@@ -5718,22 +5718,22 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Inteligência</t>
+          <t>FCT — Fluxo de Caixa Tributário</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Score de risco por fornecedor (0–100)</t>
+          <t>Posição líquida — saldo credor mês a mês</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Pontuação de conformidade fiscal calculada por fornecedor com base no critério: volume de créditos em risco (flags vencido/em_risco/inconsistência) dividido pelo total de créditos gerados. Resultado convertido em escala 0–100.</t>
+          <t>Linha do saldo credor apurado ao fim de cada período. Substitui o acumulado de crédito menos débito, que ignorava o débito extinto por split e RAD.</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
+          <t>PRD de Analytics · Seção 01 Contexto e posicionamento</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -5746,21 +5746,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J100" s="11" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr"/>
       <c r="L100" s="3" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
       <c r="N100" s="7" t="inlineStr"/>
@@ -5777,22 +5769,22 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Inteligência</t>
+          <t>FCT — Fluxo de Caixa Tributário</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Critério: créditos em risco ÷ total</t>
+          <t>Créditos a apropriar por mês de origem</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>O score sai da razão entre o crédito em risco e o crédito total originado pelo fornecedor — proporção, não valor absoluto, para não punir volume.</t>
+          <t>Créditos ainda não apropriados distribuídos pelo mês do documento que os originou, separando condicionado, em risco e glosado.</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
+          <t>PRD de Analytics · Seção 01 Contexto e posicionamento</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -5805,21 +5797,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J101" s="11" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="3" t="inlineStr"/>
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
       <c r="N101" s="7" t="inlineStr"/>
@@ -5836,22 +5820,22 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Inteligência</t>
+          <t>FCT — Fluxo de Caixa Tributário</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Score ≥ 70 → badge verde (baixo risco)</t>
+          <t>Simulação por cenário de receita e de fornecedor</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Fornecedores com score ≥ 70 recebem badge verde indicando baixo risco fiscal. Entre 40 e 69: âmbar (risco médio). Abaixo de 40: vermelho (alto risco).</t>
+          <t>Horizonte, cenário de receita e comportamento do fornecedor — este último é o que mais move o resultado, porque é a dependência do pagamento em ação.</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
+          <t>PRD de Analytics</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -5864,21 +5848,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J102" s="11" t="inlineStr">
+      <c r="I102" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr"/>
       <c r="L102" s="3" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
       <c r="N102" s="7" t="inlineStr"/>
@@ -5900,17 +5876,17 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Ranking Top 5 Melhores e Top 5 Piores</t>
+          <t>Score de risco por fornecedor (0–100)</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Dois rankings lado a lado: os 5 fornecedores com maior score (baixo risco, priorizados para relacionamento) e os 5 com menor score (alto risco, candidatos a ação imediata).</t>
+          <t>Pontuação de conformidade fiscal calculada por fornecedor com base no critério: volume de créditos em risco (flags vencido/em_risco/inconsistência) dividido pelo total de créditos gerados. Resultado convertido em escala 0–100.</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-04 Ranquear os melhores e os piores fornecedores</t>
+          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -5959,17 +5935,17 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Mapa de bolhas risco × volume</t>
+          <t>Critério: créditos em risco ÷ total</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Gráfico de dispersão com todos os fornecedores posicionados por dois eixos: eixo X = volume de créditos gerados; eixo Y = score de risco. Bolhas com anti-sobreposição para legibilidade mesmo com muitos fornecedores.</t>
+          <t>O score sai da razão entre o crédito em risco e o crédito total originado pelo fornecedor — proporção, não valor absoluto, para não punir volume.</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Analytics</t>
+          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -6018,17 +5994,17 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Tabela mensal de crédito por fornecedor</t>
+          <t>Score ≥ 70 → badge verde (baixo risco)</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Histórico mensal por fornecedor com colunas de créditos gerados (IBS+CBS) e aproveitados, permitindo identificar variações de volume ao longo do tempo.</t>
+          <t>Fornecedores com score ≥ 70 recebem badge verde indicando baixo risco fiscal. Entre 40 e 69: âmbar (risco médio). Abaixo de 40: vermelho (alto risco).</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-07 Abrir a tabela mensal de crédito</t>
+          <t>PRD de Analytics · F-03 Pontuar o risco por fornecedor</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -6041,13 +6017,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I105" s="9" t="inlineStr">
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="J105" s="3" t="inlineStr"/>
-      <c r="K105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
       <c r="N105" s="7" t="inlineStr"/>
@@ -6069,17 +6053,17 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Volume financeiro de NFs sob RAD em 90 e 120 dias</t>
+          <t>Ranking Top 5 Melhores e Top 5 Piores</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Volume das notas cujo recolhimento pelo adquirente vence nas próximas janelas, para dimensionar o caixa necessário e antecipar decisão de política.</t>
+          <t>Dois rankings lado a lado: os 5 fornecedores com maior score (baixo risco, priorizados para relacionamento) e os 5 com menor score (alto risco, candidatos a ação imediata).</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · Seção 01 Contexto e posicionamento</t>
+          <t>PRD de Analytics · F-04 Ranquear os melhores e os piores fornecedores</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -6092,13 +6076,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I106" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J106" s="3" t="inlineStr"/>
-      <c r="K106" s="3" t="inlineStr"/>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
       <c r="N106" s="7" t="inlineStr"/>
@@ -6120,22 +6112,22 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Alertas de vencimento, concentração, desvio e divergência</t>
+          <t>Mapa de bolhas risco × volume</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Quatro famílias de sinal calculadas sobre a base real de registros fiscais, nunca sobre projeção.</t>
+          <t>Gráfico de dispersão com todos os fornecedores posicionados por dois eixos: eixo X = volume de créditos gerados; eixo Y = score de risco. Bolhas com anti-sobreposição para legibilidade mesmo com muitos fornecedores.</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics</t>
+          <t>Não descrita no PRD de Analytics</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
@@ -6143,13 +6135,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I107" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J107" s="3" t="inlineStr"/>
-      <c r="K107" s="3" t="inlineStr"/>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
       <c r="N107" s="7" t="inlineStr"/>
@@ -6171,22 +6171,22 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Separação entre alerta e ocorrência</t>
+          <t>Tabela mensal de crédito por fornecedor</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Alerta é observação estatística; ocorrência é fato apurado, com responsável e prazo. Confundi-los encheria a fila de suspeitas.</t>
+          <t>Histórico mensal por fornecedor com colunas de créditos gerados (IBS+CBS) e aproveitados, permitindo identificar variações de volume ao longo do tempo.</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics</t>
+          <t>PRD de Analytics · F-07 Abrir a tabela mensal de crédito</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
@@ -6194,9 +6194,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I108" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr"/>
@@ -6212,32 +6212,32 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Contratos</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Modelo RAD — adquirente recolhe o tributo</t>
+          <t>Volume financeiro de NFs sob RAD em 90 e 120 dias</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Contratos no modelo RAD (Recolhimento pelo Adquirente Destinatário) definem que o adquirente é responsável por gerar e pagar as guias de IBS/CBS. Exige comprovante de pagamento para apropriação do crédito.</t>
+          <t>Volume das notas cujo recolhimento pelo adquirente vence nas próximas janelas, para dimensionar o caixa necessário e antecipar decisão de política.</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
+          <t>PRD de Analytics · Seção 01 Contexto e posicionamento</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
@@ -6245,9 +6245,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr"/>
@@ -6263,32 +6263,32 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Contratos</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Modelo Fornecedor — fornecedor recolhe</t>
+          <t>Alertas de vencimento, concentração, desvio e divergência</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Contratos no modelo Fornecedor definem que o próprio fornecedor recolhe o tributo. O adquirente não precisa gerar guias nem anexar comprovante — a apropriação do crédito ocorre automaticamente após confirmação de pagamento pelo fornecedor.</t>
+          <t>Quatro famílias de sinal calculadas sobre a base real de registros fiscais, nunca sobre projeção.</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
+          <t>PRD de Analytics</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
@@ -6296,9 +6296,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr"/>
@@ -6314,32 +6314,32 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Contratos</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Multi-contratos por fornecedor</t>
+          <t>Separação entre alerta e ocorrência</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Um fornecedor pode ter mais de um contrato vigente simultaneamente (ex: RAD para produtos da linha A, Fornecedor para produtos da linha B, com vigências e condições distintas).</t>
+          <t>Alerta é observação estatística; ocorrência é fato apurado, com responsável e prazo. Confundi-los encheria a fila de suspeitas.</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · Seção 05 Resolução de contrato vigente</t>
+          <t>PRD de Analytics</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
@@ -6347,9 +6347,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr"/>
@@ -6375,17 +6375,17 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Vínculo contrato → obrigações de comprovante</t>
+          <t>Modelo RAD — adquirente recolhe o tributo</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>O modelo do contrato determina automaticamente quais validações de comprovante são aplicadas nos RFs daquele fornecedor — elimina necessidade de configuração manual por RF.</t>
+          <t>Contratos no modelo RAD (Recolhimento pelo Adquirente Destinatário) definem que o adquirente é responsável por gerar e pagar as guias de IBS/CBS. Exige comprovante de pagamento para apropriação do crédito.</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Contratos</t>
+          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Listagem com filtros padronizados</t>
+          <t>Modelo Fornecedor — fornecedor recolhe</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Tabela de contratos com filtros shBuildFilterPanel por modelo (RAD/Fornecedor), status de vigência e fornecedor vinculado.</t>
+          <t>Contratos no modelo Fornecedor definem que o próprio fornecedor recolhe o tributo. O adquirente não precisa gerar guias nem anexar comprovante — a apropriação do crédito ocorre automaticamente após confirmação de pagamento pelo fornecedor.</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · F-01 Listagem de contratos</t>
+          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
@@ -6477,17 +6477,17 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Contrato como recorte de política RAD</t>
+          <t>Multi-contratos por fornecedor</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Contratos de método RAD podem ser o critério de cobertura de uma política de execução, na orquestração por contrato.</t>
+          <t>Um fornecedor pode ter mais de um contrato vigente simultaneamente (ex: RAD para produtos da linha A, Fornecedor para produtos da linha B, com vigências e condições distintas).</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>PRD de Contratos · Seção 05 Resolução de contrato vigente</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -6500,9 +6500,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I114" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr"/>
@@ -6528,17 +6528,17 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Modelo Split Payment — retenção na liquidação</t>
+          <t>Vínculo contrato → obrigações de comprovante</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Terceiro método de pagamento do contrato: o IBS e a CBS são segregados no próprio instrumento de pagamento e recolhidos na liquidação. Documentos em Split Payment não admitem recolhimento assumido, porque o instrumento já separa o tributo (art. 36, caput).</t>
+          <t>O modelo do contrato determina automaticamente quais validações de comprovante são aplicadas nos RFs daquele fornecedor — elimina necessidade de configuração manual por RF.</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
+          <t>Não descrita no PRD de Contratos</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -6551,21 +6551,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="J115" s="11" t="inlineStr">
+      <c r="I115" s="6" t="inlineStr">
         <is>
           <t>M0</t>
         </is>
       </c>
-      <c r="K115" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J115" s="3" t="inlineStr"/>
+      <c r="K115" s="3" t="inlineStr"/>
       <c r="L115" s="3" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
       <c r="N115" s="7" t="inlineStr"/>
@@ -6587,22 +6579,22 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Elegibilidade do contrato ao RAD</t>
+          <t>Listagem com filtros padronizados</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Decide se aquele contrato entra no fluxo de recolhimento pelo adquirente. Torna a decisão uma propriedade negociada, e não uma escolha caso a caso na tela.</t>
+          <t>Tabela de contratos com filtros shBuildFilterPanel por modelo (RAD/Fornecedor), status de vigência e fornecedor vinculado.</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos</t>
+          <t>PRD de Contratos · F-01 Listagem de contratos</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
@@ -6610,9 +6602,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I116" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr"/>
@@ -6638,17 +6630,17 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Chave do contrato no ERP</t>
+          <t>Contrato como recorte de política RAD</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Identificador do contrato no sistema do cliente. Sustenta a idempotência: reenvio não cria contrato duplicado.</t>
+          <t>Contratos de método RAD podem ser o critério de cobertura de uma política de execução, na orquestração por contrato.</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -6689,17 +6681,17 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Renovação automática do contrato</t>
+          <t>Modelo Split Payment — retenção na liquidação</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>O contrato se renova no fim da vigência, sem depender de ação.</t>
+          <t>Terceiro método de pagamento do contrato: o IBS e a CBS são segregados no próprio instrumento de pagamento e recolhidos na liquidação. Documentos em Split Payment não admitem recolhimento assumido, porque o instrumento já separa o tributo (art. 36, caput).</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos</t>
+          <t>PRD de Contratos · Seção 02 Métodos de pagamento</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -6717,8 +6709,16 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="J118" s="3" t="inlineStr"/>
-      <c r="K118" s="3" t="inlineStr"/>
+      <c r="J118" s="11" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L118" s="3" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
       <c r="N118" s="7" t="inlineStr"/>
@@ -6735,22 +6735,22 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Cadastro com razão social anonimizada</t>
+          <t>Elegibilidade do contrato ao RAD</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Razões sociais geradas deterministicamente por índice (seed fixo), garantindo que o mesmo fornecedor receba sempre o mesmo nome fictício entre sessões. Ex: "Induspar Componentes Ltda", "Metalúrgica Sulamérica S.A.".</t>
+          <t>Decide se aquele contrato entra no fluxo de recolhimento pelo adquirente. Torna a decisão uma propriedade negociada, e não uma escolha caso a caso na tela.</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-04 Cadastrar fornecedor</t>
+          <t>PRD de Contratos</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -6763,9 +6763,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr"/>
@@ -6786,22 +6786,22 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>CNPJ formatado XX.XXX.XXX/XXXX-XX</t>
+          <t>Chave do contrato no ERP</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>CNPJs exibidos no padrão visual brasileiro em todos os módulos. Consistência garantida por função de formatação centralizada.</t>
+          <t>Identificador do contrato no sistema do cliente. Sustenta a idempotência: reenvio não cria contrato duplicado.</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-04 Cadastrar fornecedor</t>
+          <t>PRD de Contratos</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -6814,9 +6814,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr"/>
@@ -6837,27 +6837,27 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Edição com trilha de auditoria</t>
+          <t>Renovação automática do contrato</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Cada alteração de campo no cadastro registra: campo editado, valor anterior, novo valor, usuário que editou e data/hora. Histórico append-only — não pode ser apagado.</t>
+          <t>O contrato se renova no fim da vigência, sem depender de ação.</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-06 Registrar auditoria do cadastro</t>
+          <t>PRD de Contratos</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
@@ -6865,9 +6865,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I121" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr"/>
@@ -6893,17 +6893,17 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Multi-contratos no cadastro</t>
+          <t>Cadastro com razão social anonimizada</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Campo que vincula mais de um contrato vigente ao mesmo fornecedor. Visível no cadastro com status de cada contrato (ativo/encerrado/suspenso).</t>
+          <t>Razões sociais geradas deterministicamente por índice (seed fixo), garantindo que o mesmo fornecedor receba sempre o mesmo nome fictício entre sessões. Ex: "Induspar Componentes Ltda", "Metalúrgica Sulamérica S.A.".</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-05 Editar fornecedor</t>
+          <t>PRD de Fornecedor · F-04 Cadastrar fornecedor</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -6944,22 +6944,22 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Score de conformidade no cadastro</t>
+          <t>CNPJ formatado XX.XXX.XXX/XXXX-XX</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Score calculado pelo módulo Inteligência exibido diretamente na ficha do fornecedor, com badge de cor por faixa de risco.</t>
+          <t>CNPJs exibidos no padrão visual brasileiro em todos os módulos. Consistência garantida por função de formatação centralizada.</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-07 Apresentar score e classificação</t>
+          <t>PRD de Fornecedor · F-04 Cadastrar fornecedor</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
@@ -6967,9 +6967,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr"/>
@@ -6995,22 +6995,22 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Aba Acessos no cadastro</t>
+          <t>Edição com trilha de auditoria</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Quem do fornecedor acessa o portal, com papel, alcance, último acesso e situação, mais os convites pendentes com prazo de expiração.</t>
+          <t>Cada alteração de campo no cadastro registra: campo editado, valor anterior, novo valor, usuário que editou e data/hora. Histórico append-only — não pode ser apagado.</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-09 Listar quem acessa o portal</t>
+          <t>PRD de Fornecedor · F-06 Registrar auditoria do cadastro</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
@@ -7018,9 +7018,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr"/>
@@ -7046,22 +7046,22 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Convite, reenvio e cancelamento</t>
+          <t>Multi-contratos no cadastro</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>O operador convida por e-mail escolhendo papel e CNPJs do grupo, e nunca define senha. Reenviar invalida o link anterior.</t>
+          <t>Campo que vincula mais de um contrato vigente ao mesmo fornecedor. Visível no cadastro com status de cada contrato (ativo/encerrado/suspenso).</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-10 Convidar uma pessoa</t>
+          <t>PRD de Fornecedor · F-05 Editar fornecedor</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
@@ -7097,22 +7097,22 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Revogação com motivo e trilha</t>
+          <t>Score de conformidade no cadastro</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Corta o acesso na hora e encerra as sessões abertas. O acesso revogado continua na lista — apagá-lo apagaria a autoria dos comprovantes já enviados.</t>
+          <t>Score calculado pelo módulo Inteligência exibido diretamente na ficha do fornecedor, com badge de cor por faixa de risco.</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-12 Revogar acesso com motivo</t>
+          <t>PRD de Fornecedor · F-07 Apresentar score e classificação</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -7120,21 +7120,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J126" s="11" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr"/>
       <c r="L126" s="3" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
       <c r="N126" s="7" t="inlineStr"/>
@@ -7156,22 +7148,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Importação de fornecedores e grupos por CSV</t>
+          <t>Aba Acessos no cadastro</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Um arquivo cria, atualiza e monta o grupo econômico pela coluna de matriz, resolvido em segunda passada — a filial pode vir antes da matriz.</t>
+          <t>Quem do fornecedor acessa o portal, com papel, alcance, último acesso e situação, mais os convites pendentes com prazo de expiração.</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-13 Cadastrar e atualizar por CSV</t>
+          <t>PRD de Fornecedor · F-09 Listar quem acessa o portal</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
@@ -7207,17 +7199,17 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Importação de status e de convites em massa</t>
+          <t>Convite, reenvio e cancelamento</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Ativar, inativar ou bloquear em lote, com motivo; e convidar muita gente de uma vez, ignorando quem já tem acesso ativo.</t>
+          <t>O operador convida por e-mail escolhendo papel e CNPJs do grupo, e nunca define senha. Reenviar invalida o link anterior.</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-15 Atualizar status e convidar em massa</t>
+          <t>PRD de Fornecedor · F-10 Convidar uma pessoa</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -7258,22 +7250,22 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Pré-visualização e relatório da importação</t>
+          <t>Revogação com motivo e trilha</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Antes de gravar, mostra o que será criado, atualizado, ignorado e recusado, e quantos acessos mudam de alcance. Depois, o relatório traz linha a linha o que falhou e o que fazer.</t>
+          <t>Corta o acesso na hora e encerra as sessões abertas. O acesso revogado continua na lista — apagá-lo apagaria a autoria dos comprovantes já enviados.</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-16 Conferir antes de gravar e receber o relatório</t>
+          <t>PRD de Fornecedor · F-12 Revogar acesso com motivo</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
@@ -7317,22 +7309,22 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Histórico de lotes de importação</t>
+          <t>Importação de fornecedores e grupos por CSV</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Cada importação vira um lote com autor, data, contagens e o arquivo original — a resposta para “quem inativou estes fornecedores?”.</t>
+          <t>Um arquivo cria, atualiza e monta o grupo econômico pela coluna de matriz, resolvido em segunda passada — a filial pode vir antes da matriz.</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor · F-17 Guardar o histórico de lotes</t>
+          <t>PRD de Fornecedor · F-13 Cadastrar e atualizar por CSV</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
@@ -7368,22 +7360,22 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Representantes fiscais por CPF</t>
+          <t>Importação de status e de convites em massa</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Quem responde pelo fornecedor perante o Fisco, identificado por CPF. Não se confunde com contato: a documentação oficial trata o dado como essencial ao cálculo correto do crédito.</t>
+          <t>Ativar, inativar ou bloquear em lote, com motivo; e convidar muita gente de uma vez, ignorando quem já tem acesso ativo.</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor</t>
+          <t>PRD de Fornecedor · F-15 Atualizar status e convidar em massa</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
@@ -7391,9 +7383,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr"/>
@@ -7419,22 +7411,22 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Cadastro recebido do ERP</t>
+          <t>Pré-visualização e relatório da importação</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Razão social, situação cadastral, natureza jurídica, regime e atividade chegam por integração, em vez de digitados.</t>
+          <t>Antes de gravar, mostra o que será criado, atualizado, ignorado e recusado, e quantos acessos mudam de alcance. Depois, o relatório traz linha a linha o que falhou e o que fazer.</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>PRD de Fornecedor</t>
+          <t>PRD de Fornecedor · F-16 Conferir antes de gravar e receber o relatório</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -7447,8 +7439,16 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="J132" s="3" t="inlineStr"/>
-      <c r="K132" s="3" t="inlineStr"/>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L132" s="3" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
       <c r="N132" s="7" t="inlineStr"/>
@@ -7465,22 +7465,22 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Organização</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Hierarquia CNPJ: Matriz + Filiais</t>
+          <t>Histórico de lotes de importação</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Visualização da estrutura do grupo econômico com CNPJ da matriz e todos os CNPJs de filiais vinculados. Status de conformidade fiscal exibido por entidade.</t>
+          <t>Cada importação vira um lote com autor, data, contagens e o arquivo original — a resposta para “quem inativou estes fornecedores?”.</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>PRD de Organização · F-01 Listar CNPJs agrupados por grupo econômico</t>
+          <t>PRD de Fornecedor · F-17 Guardar o histórico de lotes</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -7516,27 +7516,27 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Organização</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Status de conformidade por entidade</t>
+          <t>Representantes fiscais por CPF</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Indicador de conformidade fiscal (créditos em risco, inconsistências abertas, vencimentos próximos) calculado individualmente para cada CNPJ da hierarquia.</t>
+          <t>Quem responde pelo fornecedor perante o Fisco, identificado por CPF. Não se confunde com contato: a documentação oficial trata o dado como essencial ao cálculo correto do crédito.</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Organização</t>
+          <t>PRD de Fornecedor</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -7544,9 +7544,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr"/>
@@ -7567,27 +7567,27 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Organização</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Apuração Assistida na sidebar</t>
+          <t>Cadastro recebido do ERP</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Dados da Apuração Assistida do Governo (CG-IBS/RFB) exibidos na sidebar da aplicação, permitindo consulta rápida sem sair do contexto de trabalho atual.</t>
+          <t>Razão social, situação cadastral, natureza jurídica, regime e atividade chegam por integração, em vez de digitados.</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>Não descrita no PRD de Organização</t>
+          <t>PRD de Fornecedor</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
@@ -7595,9 +7595,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I135" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr"/>
@@ -7623,12 +7623,12 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Filtro Grupo Econômico — sincroniza tudo</t>
+          <t>Hierarquia CNPJ: Matriz + Filiais</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Seletor de CNPJ no header da aplicação que ao ser alterado recalcula nfListaFiltradaGlobal e dispara sincronizarTudo(), propagando o filtro para todos os módulos simultaneamente.</t>
+          <t>Visualização da estrutura do grupo econômico com CNPJ da matriz e todos os CNPJs de filiais vinculados. Status de conformidade fiscal exibido por entidade.</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -7674,22 +7674,22 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Auditoria de alterações cadastrais</t>
+          <t>Status de conformidade por entidade</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Histórico de mudanças na organização (razão social, CNPJs, responsáveis) com registro de usuário, data e campo alterado.</t>
+          <t>Indicador de conformidade fiscal (créditos em risco, inconsistências abertas, vencimentos próximos) calculado individualmente para cada CNPJ da hierarquia.</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>PRD de Organização · F-05 Registrar auditoria do cadastro</t>
+          <t>Não descrita no PRD de Organização</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
@@ -7697,9 +7697,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr"/>
@@ -7725,22 +7725,22 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Enquadramento por órgão para o ressarcimento</t>
+          <t>Apuração Assistida na sidebar</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Programa de conformidade e prazo de análise na Receita e no Comitê Gestor, pedido centralizado na matriz e impedimentos do IBS registrados. Define o prazo de cada pedido.</t>
+          <t>Dados da Apuração Assistida do Governo (CG-IBS/RFB) exibidos na sidebar da aplicação, permitindo consulta rápida sem sair do contexto de trabalho atual.</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
+          <t>Não descrita no PRD de Organização</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -7748,9 +7748,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I138" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr"/>
@@ -7766,32 +7766,32 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>DFs filtrados pelo CNPJ próprio</t>
+          <t>Filtro Grupo Econômico — sincroniza tudo</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Fornecedor autenticado visualiza exclusivamente os documentos fiscais emitidos para o seu CNPJ — sem acesso a dados de outros fornecedores ou do adquirente.</t>
+          <t>Seletor de CNPJ no header da aplicação que ao ser alterado recalcula nfListaFiltradaGlobal e dispara sincronizarTudo(), propagando o filtro para todos os módulos simultaneamente.</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-01 Listar os documentos do próprio CNPJ</t>
+          <t>PRD de Organização · F-01 Listar CNPJs agrupados por grupo econômico</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>IBS e CBS separados por RF</t>
+          <t>Auditoria de alterações cadastrais</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Status de cada imposto (IBS e CBS) exibido individualmente por RF, sem agrupamento. Permite ao fornecedor identificar qual imposto tem pendência.</t>
+          <t>Histórico de mudanças na organização (razão social, CNPJs, responsáveis) com registro de usuário, data e campo alterado.</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-02 Separar IBS e CBS por registro</t>
+          <t>PRD de Organização · F-05 Registrar auditoria do cadastro</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -7850,9 +7850,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I140" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J140" s="3" t="inlineStr"/>
@@ -7868,32 +7868,32 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Portais</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Portal Fornecedor</t>
+          <t>Organização</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Grupo econômico: Matriz + Filiais</t>
+          <t>Enquadramento por órgão para o ressarcimento</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Fornecedor com grupo econômico pode visualizar DFs de todos os CNPJs do grupo (Matriz + Filiais) em painel consolidado.</t>
+          <t>Programa de conformidade e prazo de análise na Receita e no Comitê Gestor, pedido centralizado na matriz e impedimentos do IBS registrados. Define o prazo de cada pedido.</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-03 Enxergar o grupo econômico</t>
+          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
@@ -7929,22 +7929,22 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Envio de comprovante RAD/PIX</t>
+          <t>DFs filtrados pelo CNPJ próprio</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Formulário de upload de comprovante de pagamento (PIX ou guia RAD) anexado ao RF específico. Notifica o adquirente e desbloqueia o processo de apropriação do crédito.</t>
+          <t>Fornecedor autenticado visualiza exclusivamente os documentos fiscais emitidos para o seu CNPJ — sem acesso a dados de outros fornecedores ou do adquirente.</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-04 Enviar comprovante de recolhimento</t>
+          <t>PRD de Portal do Fornecedor · F-01 Listar os documentos do próprio CNPJ</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -7957,16 +7957,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J142" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K142" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J142" s="3" t="inlineStr"/>
+      <c r="K142" s="3" t="inlineStr"/>
       <c r="L142" s="3" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
       <c r="N142" s="7" t="inlineStr"/>
@@ -7988,22 +7980,22 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Contestação de DFs vencidos</t>
+          <t>IBS e CBS separados por RF</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Fluxo formal de contestação para DFs com prazo vencido: texto justificado, evidências em anexo e envio ao adquirente para análise.</t>
+          <t>Status de cada imposto (IBS e CBS) exibido individualmente por RF, sem agrupamento. Permite ao fornecedor identificar qual imposto tem pendência.</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-05 Contestar documento vencido</t>
+          <t>PRD de Portal do Fornecedor · F-02 Separar IBS e CBS por registro</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
@@ -8011,9 +8003,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I143" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr"/>
@@ -8039,22 +8031,22 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Chat com adquirente</t>
+          <t>Grupo econômico: Matriz + Filiais</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Canal de comunicação direto dentro do portal para dúvidas ou negociações sobre DFs específicos, sem necessidade de contato por e-mail externo.</t>
+          <t>Fornecedor com grupo econômico pode visualizar DFs de todos os CNPJs do grupo (Matriz + Filiais) em painel consolidado.</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-06 Conversar com o adquirente</t>
+          <t>PRD de Portal do Fornecedor · F-03 Enxergar o grupo econômico</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -8090,22 +8082,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Score de conformidade próprio</t>
+          <t>Envio de comprovante RAD/PIX</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Fornecedor visualiza seu próprio score de conformidade fiscal calculado pelo adquirente, com detalhamento dos critérios que impactam negativamente a pontuação.</t>
+          <t>Formulário de upload de comprovante de pagamento (PIX ou guia RAD) anexado ao RF específico. Notifica o adquirente e desbloqueia o processo de apropriação do crédito.</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-07 Ver o próprio score de conformidade</t>
+          <t>PRD de Portal do Fornecedor · F-04 Enviar comprovante de recolhimento</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
@@ -8113,13 +8105,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I145" s="10" t="inlineStr">
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J145" s="3" t="inlineStr"/>
-      <c r="K145" s="3" t="inlineStr"/>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
       <c r="N145" s="7" t="inlineStr"/>
@@ -8141,22 +8141,22 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Período multi-select</t>
+          <t>Contestação de DFs vencidos</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Mesmo componente de seleção de meses individuais do portal cliente. Propaga o filtro de período por todos os módulos do portal do fornecedor.</t>
+          <t>Fluxo formal de contestação para DFs com prazo vencido: texto justificado, evidências em anexo e envio ao adquirente para análise.</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-08 Recortar por período</t>
+          <t>PRD de Portal do Fornecedor · F-05 Contestar documento vencido</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -8164,9 +8164,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I146" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I146" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr"/>
@@ -8192,22 +8192,22 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Contratos globais visíveis</t>
+          <t>Chat com adquirente</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Lista dos contratos vigentes entre o fornecedor e o adquirente, com modelo (RAD/Fornecedor), vigência e condições relevantes para o ciclo de crédito.</t>
+          <t>Canal de comunicação direto dentro do portal para dúvidas ou negociações sobre DFs específicos, sem necessidade de contato por e-mail externo.</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-09 Consultar os contratos vigentes</t>
+          <t>PRD de Portal do Fornecedor · F-06 Conversar com o adquirente</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
@@ -8243,22 +8243,22 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Aviso de recolhimento assumido pelo adquirente</t>
+          <t>Score de conformidade próprio</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Quando o adquirente assume o recolhimento de um documento, o fornecedor vê o aviso de não recolher. Se recolher assim mesmo, o excedente volta a ele em até três dias úteis, mas o caixa já saiu duas vezes.</t>
+          <t>Fornecedor visualiza seu próprio score de conformidade fiscal calculado pelo adquirente, com detalhamento dos critérios que impactam negativamente a pontuação.</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-10 Ver o aviso de recolhimento assumido</t>
+          <t>PRD de Portal do Fornecedor · F-07 Ver o próprio score de conformidade</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -8294,22 +8294,22 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Convite e acesso por senha própria</t>
+          <t>Período multi-select</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>O fornecedor entra pelo portal com credencial dele, criada ao aceitar um convite de uso único com validade de 7 dias. Antes disso, o portal só era alcançado por troca de perfil na sessão do operador.</t>
+          <t>Mesmo componente de seleção de meses individuais do portal cliente. Propaga o filtro de período por todos os módulos do portal do fornecedor.</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-11 Entrar com credencial própria</t>
+          <t>PRD de Portal do Fornecedor · F-08 Recortar por período</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
@@ -8345,22 +8345,22 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Papéis Responsável e Leitura</t>
+          <t>Contratos globais visíveis</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Responsável envia comprovante, contesta e conversa pelo chat; Leitura vê o mesmo e não age. É a única distinção que muda o risco do acesso externo.</t>
+          <t>Lista dos contratos vigentes entre o fornecedor e o adquirente, com modelo (RAD/Fornecedor), vigência e condições relevantes para o ciclo de crédito.</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor · F-12 Agir conforme o papel</t>
+          <t>PRD de Portal do Fornecedor · F-09 Consultar os contratos vigentes</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
@@ -8396,22 +8396,22 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Painel de abertura do fornecedor</t>
+          <t>Aviso de recolhimento assumido pelo adquirente</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>A posição do próprio fornecedor antes das listagens: documentos do período, o que depende dele e o que gerou ocorrência.</t>
+          <t>Quando o adquirente assume o recolhimento de um documento, o fornecedor vê o aviso de não recolher. Se recolher assim mesmo, o excedente volta a ele em até três dias úteis, mas o caixa já saiu duas vezes.</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor</t>
+          <t>PRD de Portal do Fornecedor · F-10 Ver o aviso de recolhimento assumido</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
@@ -8447,17 +8447,17 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Edição restrita a contato e responsáveis</t>
+          <t>Convite e acesso por senha própria</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>O fornecedor corrige cadastro, nunca dado fiscal, com trilha de autor, data e valor anterior. O que ele contesta, contesta por ocorrência.</t>
+          <t>O fornecedor entra pelo portal com credencial dele, criada ao aceitar um convite de uso único com validade de 7 dias. Antes disso, o portal só era alcançado por troca de perfil na sessão do operador.</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor</t>
+          <t>PRD de Portal do Fornecedor · F-11 Entrar com credencial própria</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -8470,9 +8470,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I152" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr"/>
@@ -8498,22 +8498,22 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Exportação registrada do recorte visível</t>
+          <t>Papéis Responsável e Leitura</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Sai só o que ele já enxerga em tela, e a exportação fica registrada — é saída de dado do perímetro da organização.</t>
+          <t>Responsável envia comprovante, contesta e conversa pelo chat; Leitura vê o mesmo e não age. É a única distinção que muda o risco do acesso externo.</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>PRD de Portal do Fornecedor</t>
+          <t>PRD de Portal do Fornecedor · F-12 Agir conforme o papel</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
@@ -8521,9 +8521,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I153" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr"/>
@@ -8549,17 +8549,17 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Painel inicial do fornecedor</t>
+          <t>Painel de abertura do fornecedor</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>O que ele deve, o que já foi recolhido e o que vence a seguir, em quatro números. É a tela que responde “preciso fazer alguma coisa hoje?” antes de qualquer listagem.</t>
-        </is>
-      </c>
-      <c r="F154" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>A posição do próprio fornecedor antes das listagens: documentos do período, o que depende dele e o que gerou ocorrência.</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Portal do Fornecedor</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -8567,14 +8567,14 @@
           <t>Analítico</t>
         </is>
       </c>
-      <c r="H154" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr"/>
@@ -8600,32 +8600,32 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Comprovantes de pagamento disponíveis ao fornecedor</t>
+          <t>Edição restrita a contato e responsáveis</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Quando o adquirente recolhe — por RAD ou por recolhimento assumido —, o comprovante fica disponível ao fornecedor no próprio documento. Hoje o fluxo existe só na direção contrária: o fornecedor envia o dele.</t>
-        </is>
-      </c>
-      <c r="F155" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>O fornecedor corrige cadastro, nunca dado fiscal, com trilha de autor, data e valor anterior. O que ele contesta, contesta por ocorrência.</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Portal do Fornecedor</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
-        </is>
-      </c>
-      <c r="H155" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J155" s="3" t="inlineStr"/>
@@ -8646,22 +8646,22 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Tela de login</t>
+          <t>Exportação registrada do recorte visível</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Autenticação client-side com credenciais (Admin/Positivo123@). Sessão persistida em sessionStorage — não requer backend. Tela de login bloqueia acesso a qualquer módulo antes da autenticação.</t>
-        </is>
-      </c>
-      <c r="F156" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Sai só o que ele já enxerga em tela, e a exportação fica registrada — é saída de dado do perímetro da organização.</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Portal do Fornecedor</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -8674,9 +8674,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I156" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J156" s="3" t="inlineStr"/>
@@ -8697,17 +8697,17 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Perfis: Cliente e Fornecedor</t>
+          <t>Painel inicial do fornecedor</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Após login, o usuário seleciona o perfil: Cliente (adquirente — acesso completo a todos os módulos) ou Fornecedor (acesso restrito ao portal com dados filtrados pelo CNPJ do fornecedor).</t>
+          <t>O que ele deve, o que já foi recolhido e o que vence a seguir, em quatro números. É a tela que responde “preciso fazer alguma coisa hoje?” antes de qualquer listagem.</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I157" s="6" t="inlineStr">
@@ -8748,17 +8748,17 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Auth · Design System</t>
+          <t>Portal Fornecedor</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Troca de perfil in-session</t>
+          <t>Comprovantes de pagamento disponíveis ao fornecedor</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Card do usuário no header e modal de configurações permitem alternar de perfil durante a sessão sem necessidade de novo login.</t>
+          <t>Quando o adquirente recolhe — por RAD ou por recolhimento assumido —, o comprovante fica disponível ao fornecedor no próprio documento. Hoje o fluxo existe só na direção contrária: o fornecedor envia o dele.</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H158" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I158" s="6" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Tokens CSS globais + PALETTE JS</t>
+          <t>Tela de login</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Todas as cores da interface definidas como variáveis CSS (--teal, --blue, --red etc.) e objeto PALETTE no JS. Nenhum valor hexadecimal inline no código — consistência visual garantida centralmente.</t>
+          <t>Autenticação client-side com credenciais (Admin/Positivo123@). Sessão persistida em sessionStorage — não requer backend. Tela de login bloqueia acesso a qualquer módulo antes da autenticação.</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Sidebar teal colapsável + localStorage</t>
+          <t>Perfis: Cliente e Fornecedor</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Toggle de 56px com transição CSS suave entre expandida (labels visíveis) e colapsada (ícones com tooltips). Estado persistido em localStorage — mantido entre sessões e recarregamentos.</t>
+          <t>Após login, o usuário seleciona o perfil: Cliente (adquirente — acesso completo a todos os módulos) ou Fornecedor (acesso restrito ao portal com dados filtrados pelo CNPJ do fornecedor).</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Tema claro/escuro automático</t>
+          <t>Troca de perfil in-session</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>prefers-color-scheme detecta o tema do sistema operacional e aplica automaticamente. Override manual disponível via atributo data-theme. Tokens redefinidos para cada tema sem hardcode de cores.</t>
+          <t>Card do usuário no header e modal de configurações permitem alternar de perfil durante a sessão sem necessidade de novo login.</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>shBuildFilterPanel — filtros padronizados</t>
+          <t>Tokens CSS globais + PALETTE JS</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Função geradora de painéis de filtro colapsáveis com design unificado (classe sh-fp). Aplicada em Créditos, Débitos, Pagamentos, Inconsistências, Contratos, Fornecedores, Organização e Portal Fornecedor.</t>
+          <t>Todas as cores da interface definidas como variáveis CSS (--teal, --blue, --red etc.) e objeto PALETTE no JS. Nenhum valor hexadecimal inline no código — consistência visual garantida centralmente.</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>RF Core — 10 colunas uniformes</t>
+          <t>Sidebar teal colapsável + localStorage</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Conjunto padronizado de colunas presente em todas as listagens de RF do sistema: ID RF, Tipo Fiscal, DF Vinculado, Entidade, Data, Valor, Status do Crédito, Status de Registro, Método de Pagamento e Extinção. Filtros obrigatórios em todas as colunas.</t>
+          <t>Toggle de 56px com transição CSS suave entre expandida (labels visíveis) e colapsada (ícones com tooltips). Estado persistido em localStorage — mantido entre sessões e recarregamentos.</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>ESC fecha qualquer modal</t>
+          <t>Tema claro/escuro automático</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Atalho de teclado global — qualquer overlay aberto no sistema (modais de detalhe NF, RF, inconsistência, fornecedor, contrato) responde ao ESC e fecha sem ação adicional do usuário.</t>
+          <t>prefers-color-scheme detecta o tema do sistema operacional e aplica automaticamente. Override manual disponível via atributo data-theme. Tokens redefinidos para cada tema sem hardcode de cores.</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
@@ -9110,12 +9110,12 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Tooltip de coluna como padrão de projeto</t>
+          <t>shBuildFilterPanel — filtros padronizados</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Toda coluna declarada no catálogo de tabelas ganha explicação no cabeçalho, aplicada sempre do mesmo jeito. 104 colunas documentadas nas nove listagens; coluna nova só é publicada se souber se explicar.</t>
+          <t>Função geradora de painéis de filtro colapsáveis com design unificado (classe sh-fp). Aplicada em Créditos, Débitos, Pagamentos, Inconsistências, Contratos, Fornecedores, Organização e Portal Fornecedor.</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
@@ -9133,9 +9133,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I165" s="13" t="inlineStr">
-        <is>
-          <t>Fora</t>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J165" s="3" t="inlineStr"/>
@@ -9161,12 +9161,12 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Documentação de produto dentro da aplicação</t>
+          <t>RF Core — 10 colunas uniformes</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Hub de PRDs, mapa de funcionalidades e changelog acessíveis pela própria aplicação, sem depender de link externo. Quem opera e quem especifica leem a mesma versão.</t>
+          <t>Conjunto padronizado de colunas presente em todas as listagens de RF do sistema: ID RF, Tipo Fiscal, DF Vinculado, Entidade, Data, Valor, Status do Crédito, Status de Registro, Método de Pagamento e Extinção. Filtros obrigatórios em todas as colunas.</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
@@ -9184,9 +9184,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I166" s="13" t="inlineStr">
-        <is>
-          <t>Fora</t>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J166" s="3" t="inlineStr"/>
@@ -9212,17 +9212,17 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Rotas diretas para telas e abas</t>
+          <t>ESC fecha qualquer modal</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Endereços próprios para cada tela e aba, de forma que um link leve direto ao ponto certo da aplicação — usado em documentação, no hub de PRDs e no compartilhamento entre pessoas.</t>
-        </is>
-      </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Início · Seção 01 Contexto e posicionamento</t>
+          <t>Atalho de teclado global — qualquer overlay aberto no sistema (modais de detalhe NF, RF, inconsistência, fornecedor, contrato) responde ao ESC e fecha sem ação adicional do usuário.</t>
+        </is>
+      </c>
+      <c r="F167" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -9235,9 +9235,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I167" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J167" s="3" t="inlineStr"/>
@@ -9263,17 +9263,17 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Contador de filtros ativos sempre visível</t>
+          <t>Tooltip de coluna como padrão de projeto</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Número filtrado nunca se confunde com total. Um indicador sob filtro, sem sinal de filtro, é erro de leitura esperando acontecer.</t>
-        </is>
-      </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Arcabouço de interface · Seção 02 Painel de filtros</t>
+          <t>Toda coluna declarada no catálogo de tabelas ganha explicação no cabeçalho, aplicada sempre do mesmo jeito. 104 colunas documentadas nas nove listagens; coluna nova só é publicada se souber se explicar.</t>
+        </is>
+      </c>
+      <c r="F168" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -9286,9 +9286,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I168" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>Fora</t>
         </is>
       </c>
       <c r="J168" s="3" t="inlineStr"/>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Filtro aplicado só sob confirmação</t>
+          <t>Documentação de produto dentro da aplicação</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>O recorte inteiro é montado antes de a listagem ser refeita, em vez de recarregar a cada campo alterado.</t>
-        </is>
-      </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Arcabouço de interface · Seção 02 Painel de filtros</t>
+          <t>Hub de PRDs, mapa de funcionalidades e changelog acessíveis pela própria aplicação, sem depender de link externo. Quem opera e quem especifica leem a mesma versão.</t>
+        </is>
+      </c>
+      <c r="F169" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -9337,9 +9337,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I169" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>Fora</t>
         </is>
       </c>
       <c r="J169" s="3" t="inlineStr"/>
@@ -9365,17 +9365,17 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Paginação com retorno à primeira página</t>
+          <t>Rotas diretas para telas e abas</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Mudar o recorte devolve a listagem ao início, para não mostrar a página 5 de um conjunto que acabou de mudar.</t>
+          <t>Endereços próprios para cada tela e aba, de forma que um link leve direto ao ponto certo da aplicação — usado em documentação, no hub de PRDs e no compartilhamento entre pessoas.</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>PRD de Arcabouço de interface · Seção 03 Pagina&amp;ccedil;&amp;atilde;o e busca</t>
+          <t>PRD de Início · Seção 01 Contexto e posicionamento</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -9388,9 +9388,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I170" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I170" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr"/>
@@ -9416,17 +9416,17 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Alcance da busca declarado por módulo</t>
+          <t>Contador de filtros ativos sempre visível</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Cada módulo diz quais identificadores a própria busca encontra. Sem essa declaração, ninguém nota o que a busca deixou de fora.</t>
+          <t>Número filtrado nunca se confunde com total. Um indicador sob filtro, sem sinal de filtro, é erro de leitura esperando acontecer.</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>PRD de Arcabouço de interface · Seção 03 Pagina&amp;ccedil;&amp;atilde;o e busca</t>
+          <t>PRD de Arcabouço de interface · Seção 02 Painel de filtros</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -9467,17 +9467,17 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Gerenciador de colunas com persistência por usuário</t>
+          <t>Filtro aplicado só sob confirmação</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Seleção, ordem e restauração do padrão, por listagem e por usuário, valendo também para a exportação.</t>
+          <t>O recorte inteiro é montado antes de a listagem ser refeita, em vez de recarregar a cada campo alterado.</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>PRD de Arcabouço de interface · Seção 04 Gerenciador de colunas</t>
+          <t>PRD de Arcabouço de interface · Seção 02 Painel de filtros</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -9518,32 +9518,32 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Login via SSO corporativo</t>
+          <t>Paginação com retorno à primeira página</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Entrada pelo provedor de identidade da empresa (SAML 2.0 ou OIDC), com provisionamento e revogação vindos de lá. Não existe no produto: hoje o acesso é uma senha no código.</t>
-        </is>
-      </c>
-      <c r="F173" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Mudar o recorte devolve a listagem ao início, para não mostrar a página 5 de um conjunto que acabou de mudar.</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Arcabouço de interface · Seção 03 Pagina&amp;ccedil;&amp;atilde;o e busca</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="H173" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J173" s="3" t="inlineStr"/>
@@ -9559,32 +9559,32 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Políticas de execução sem limite de quantidade</t>
+          <t>Alcance da busca declarado por módulo</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>A organização cria quantas políticas precisar. Cada uma declara o que cobre, quando roda e quanta decisão humana existe — substituindo a relação um-para-um com o CNPJ comprador.</t>
+          <t>Cada módulo diz quais identificadores a própria busca encontra. Sem essa declaração, ninguém nota o que a busca deixou de fora.</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-03 Criar e editar política</t>
+          <t>PRD de Arcabouço de interface · Seção 03 Pagina&amp;ccedil;&amp;atilde;o e busca</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr">
@@ -9592,9 +9592,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I174" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I174" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J174" s="3" t="inlineStr"/>
@@ -9610,32 +9610,32 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por CNPJ</t>
+          <t>Gerenciador de colunas com persistência por usuário</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>A política cobre um ou mais CNPJs compradores. Todo registro fiscal de método RAD desses estabelecimentos entra na janela. Use quando a régua é do estabelecimento.</t>
+          <t>Seleção, ordem e restauração do padrão, por listagem e por usuário, valendo também para a exportação.</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>PRD de Arcabouço de interface · Seção 04 Gerenciador de colunas</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr">
@@ -9643,21 +9643,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I175" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J175" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K175" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J175" s="3" t="inlineStr"/>
+      <c r="K175" s="3" t="inlineStr"/>
       <c r="L175" s="3" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
       <c r="N175" s="7" t="inlineStr"/>
@@ -9669,37 +9661,37 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Portais</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Execução RAD</t>
+          <t>Auth · Design System</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por contrato</t>
+          <t>Login via SSO corporativo</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>A política cobre um ou mais contratos de método RAD, em qualquer CNPJ comprador. Use quando a régua é do acordo — um contrato de insumo com prazo próprio.</t>
-        </is>
-      </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>Entrada pelo provedor de identidade da empresa (SAML 2.0 ou OIDC), com provisionamento e revogação vindos de lá. Não existe no produto: hoje o acesso é uma senha no código.</t>
+        </is>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H176" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I176" s="6" t="inlineStr">
@@ -9707,16 +9699,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J176" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K176" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J176" s="3" t="inlineStr"/>
+      <c r="K176" s="3" t="inlineStr"/>
       <c r="L176" s="3" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
       <c r="N176" s="7" t="inlineStr"/>
@@ -9738,17 +9722,17 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Orquestração por faixa de valor</t>
+          <t>Políticas de execução sem limite de quantidade</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>A política cobre as guias cujo valor cai numa faixa. Separa grão fino de alto valor sem respeitar fronteira de estabelecimento.</t>
+          <t>A organização cria quantas políticas precisar. Cada uma declara o que cobre, quando roda e quanta decisão humana existe — substituindo a relação um-para-um com o CNPJ comprador.</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
+          <t>PRD de Execução RAD · F-03 Criar e editar política</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -9761,9 +9745,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I177" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J177" s="3" t="inlineStr"/>
@@ -9789,12 +9773,12 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Quatro bases de comparação da faixa</t>
+          <t>Orquestração por CNPJ</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>A faixa incide sobre o valor da guia CBS/IBS, o imposto total do documento, o valor da nota ou o valor líquido. R$ 400 mil de nota e R$ 400 mil de guia descrevem conjuntos diferentes.</t>
+          <t>A política cobre um ou mais CNPJs compradores. Todo registro fiscal de método RAD desses estabelecimentos entra na janela. Use quando a régua é do estabelecimento.</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -9812,13 +9796,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I178" s="10" t="inlineStr">
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J178" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J178" s="3" t="inlineStr"/>
-      <c r="K178" s="3" t="inlineStr"/>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L178" s="3" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
       <c r="N178" s="7" t="inlineStr"/>
@@ -9840,17 +9832,17 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Três modos de operação</t>
+          <t>Orquestração por contrato</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Automático gera e entrega sem intervenção — é o estado pretendido. Assistido aguarda aprovação a cada janela, como passo transitório. Manual não age.</t>
+          <t>A política cobre um ou mais contratos de método RAD, em qualquer CNPJ comprador. Use quando a régua é do acordo — um contrato de insumo com prazo próprio.</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-03 Criar e editar política</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -9863,13 +9855,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I179" s="10" t="inlineStr">
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J179" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J179" s="3" t="inlineStr"/>
-      <c r="K179" s="3" t="inlineStr"/>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
       <c r="N179" s="7" t="inlineStr"/>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Janela de execução configurável</t>
+          <t>Orquestração por faixa de valor</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Dias do mês em seleção múltipla, hora e antecedência em dias sobre o vencimento da guia.</t>
+          <t>A política cobre as guias cujo valor cai numa faixa. Separa grão fino de alto valor sem respeitar fronteira de estabelecimento.</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-05 Definir a janela de execução</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -9914,9 +9914,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I180" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I180" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J180" s="3" t="inlineStr"/>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Critérios de inclusão por valor e flag</t>
+          <t>Quatro bases de comparação da faixa</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Valor mínimo por guia e as flags que retêm a nota fora do lote — glosado, vencido, inconsistência. A nota retida não é descartada: aparece na fila com o motivo.</t>
+          <t>A faixa incide sobre o valor da guia CBS/IBS, o imposto total do documento, o valor da nota ou o valor líquido. R$ 400 mil de nota e R$ 400 mil de guia descrevem conjuntos diferentes.</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-06 Definir critérios de inclusão</t>
+          <t>PRD de Execução RAD · F-04 Escolher o modelo de orquestração</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -9965,9 +9965,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I181" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J181" s="3" t="inlineStr"/>
@@ -9993,22 +9993,22 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Simulação da próxima execução</t>
+          <t>Três modos de operação</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Antes de salvar, calcula quantas guias e que valor a política produziria hoje, e para onde elas iriam. Converte a política de promessa em número conferível.</t>
+          <t>Automático gera e entrega sem intervenção — é o estado pretendido. Assistido aguarda aprovação a cada janela, como passo transitório. Manual não age.</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-12 Mostrar o lote antes de acontecer</t>
+          <t>PRD de Execução RAD · F-03 Criar e editar política</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
@@ -10044,22 +10044,22 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Detecção de cobertura repetida</t>
+          <t>Janela de execução configurável</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Mesmo CNPJ ou mesmo contrato em duas políticas, ou faixas que se cruzam sobre a mesma base, barram o salvamento nomeando a política dona.</t>
+          <t>Dias do mês em seleção múltipla, hora e antecedência em dias sobre o vencimento da guia.</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-08 Validar antes de salvar</t>
+          <t>PRD de Execução RAD · F-05 Definir a janela de execução</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
@@ -10067,9 +10067,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I183" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J183" s="3" t="inlineStr"/>
@@ -10095,22 +10095,22 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Alerta de sobreposição entre modelos</t>
+          <t>Critérios de inclusão por valor e flag</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Entre modelos diferentes a colisão só existe sobre notas concretas. A listagem mede quais registros são reivindicados por mais de uma política ativa e nomeia o par.</t>
+          <t>Valor mínimo por guia e as flags que retêm a nota fora do lote — glosado, vencido, inconsistência. A nota retida não é descartada: aparece na fila com o motivo.</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-02 Alertar sobreposição entre políticas ativas</t>
+          <t>PRD de Execução RAD · F-06 Definir critérios de inclusão</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
@@ -10118,9 +10118,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I184" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J184" s="3" t="inlineStr"/>
@@ -10146,22 +10146,22 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Listagem de políticas com lote ao vivo</t>
+          <t>Simulação da próxima execução</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Uma linha por política, com orquestração, cobertura em texto, modo, janela e quantas guias produziria na próxima janela — calculado no render.</t>
+          <t>Antes de salvar, calcula quantas guias e que valor a política produziria hoje, e para onde elas iriam. Converte a política de promessa em número conferível.</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-01 Listar as políticas com sua cobertura</t>
+          <t>PRD de Execução RAD · F-12 Mostrar o lote antes de acontecer</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr">
@@ -10169,9 +10169,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I185" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J185" s="3" t="inlineStr"/>
@@ -10197,22 +10197,22 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Ativação e pausa em massa</t>
+          <t>Detecção de cobertura repetida</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Seleção múltipla de políticas, útil em fechamento contábil ou incidente de integração. Cada mudança entra no histórico da política.</t>
+          <t>Mesmo CNPJ ou mesmo contrato em duas políticas, ou faixas que se cruzam sobre a mesma base, barram o salvamento nomeando a política dona.</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-10 Ativar e pausar em massa</t>
+          <t>PRD de Execução RAD · F-08 Validar antes de salvar</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
@@ -10248,22 +10248,22 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Auditoria com diff campo a campo</t>
+          <t>Alerta de sobreposição entre modelos</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Criação, edição, ativação, pausa e execução antecipada, com autor, momento e o de/para de cada campo alterado. O editor trabalha sobre cópia: cancelar desfaz.</t>
+          <t>Entre modelos diferentes a colisão só existe sobre notas concretas. A listagem mede quais registros são reivindicados por mais de uma política ativa e nomeia o par.</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-09 Registrar o histórico de alterações</t>
+          <t>PRD de Execução RAD · F-02 Alertar sobreposição entre políticas ativas</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr">
@@ -10271,21 +10271,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J187" s="11" t="inlineStr">
+      <c r="I187" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="K187" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J187" s="3" t="inlineStr"/>
+      <c r="K187" s="3" t="inlineStr"/>
       <c r="L187" s="3" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
       <c r="N187" s="7" t="inlineStr"/>
@@ -10307,22 +10299,22 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Vínculo com a conexão de destino</t>
+          <t>Listagem de políticas com lote ao vivo</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Só conexões do tipo RAD ↔ ERP aparecem no seletor, com a saúde da conexão à vista. Sem conexão, a guia é gerada e fica na plataforma.</t>
+          <t>Uma linha por política, com orquestração, cobertura em texto, modo, janela e quantas guias produziria na próxima janela — calculado no render.</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD · F-07 Vincular a conexão de destino</t>
+          <t>PRD de Execução RAD · F-01 Listar as políticas com sua cobertura</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr">
@@ -10330,9 +10322,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I188" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J188" s="3" t="inlineStr"/>
@@ -10358,17 +10350,17 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Emissão da guia nos dois órgãos</t>
+          <t>Ativação e pausa em massa</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>O SplitHub emite a guia de RAD na Receita Federal para a CBS e no Comitê Gestor para o IBS.</t>
+          <t>Seleção múltipla de políticas, útil em fechamento contábil ou incidente de integração. Cada mudança entra no histórico da política.</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD</t>
+          <t>PRD de Execução RAD · F-10 Ativar e pausar em massa</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -10409,22 +10401,22 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Comprovante de pagamento recebido do ERP</t>
+          <t>Auditoria com diff campo a campo</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>O ERP paga a guia e devolve o comprovante, em PIX ou boleto, com os identificadores da transação.</t>
+          <t>Criação, edição, ativação, pausa e execução antecipada, com autor, momento e o de/para de cada campo alterado. O editor trabalha sobre cópia: cancelar desfaz.</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD</t>
+          <t>PRD de Execução RAD · F-09 Registrar o histórico de alterações</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
@@ -10432,13 +10424,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I190" s="10" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J190" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J190" s="3" t="inlineStr"/>
-      <c r="K190" s="3" t="inlineStr"/>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L190" s="3" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
       <c r="N190" s="7" t="inlineStr"/>
@@ -10460,22 +10460,22 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Apropriação do crédito reconhecida pelo ente fiscal</t>
+          <t>Vínculo com a conexão de destino</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>O pagamento do RAD opera a apropriação do crédito pelo comprador, e o reconhecimento vem da integração com o Fisco — não do comprovante.</t>
+          <t>Só conexões do tipo RAD ↔ ERP aparecem no seletor, com a saúde da conexão à vista. Sem conexão, a guia é gerada e fica na plataforma.</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>PRD de Execução RAD</t>
+          <t>PRD de Execução RAD · F-07 Vincular a conexão de destino</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Conciliação financeira do recolhimento</t>
+          <t>Emissão da guia nos dois órgãos</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Confronto entre o que o Fisco reconheceu e o comprovante que o ERP enviou. Divergência dos dois lados vira ocorrência.</t>
+          <t>O SplitHub emite a guia de RAD na Receita Federal para a CBS e no Comitê Gestor para o IBS.</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr">
@@ -10557,27 +10557,27 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Catálogo dos seis contextos da API</t>
+          <t>Comprovante de pagamento recebido do ERP</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Ingestão de DFs, fornecedores, contratos, RAD ↔ ERP, garantia de crédito e automações — cada um com endpoints, eventos, escopos e limites derivados da documentação publicada.</t>
+          <t>O ERP paga a guia e devolve o comprovante, em PIX ou boleto, com os identificadores da transação.</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-02 Escolher o tipo no catálogo</t>
+          <t>PRD de Execução RAD</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
@@ -10585,21 +10585,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J193" s="11" t="inlineStr">
+      <c r="I193" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="K193" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J193" s="3" t="inlineStr"/>
+      <c r="K193" s="3" t="inlineStr"/>
       <c r="L193" s="3" t="inlineStr"/>
       <c r="M193" s="7" t="inlineStr"/>
       <c r="N193" s="7" t="inlineStr"/>
@@ -10616,27 +10608,27 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Conexões nas duas direções</t>
+          <t>Apropriação do crédito reconhecida pelo ente fiscal</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Entrada, quando o ERP chama a API do SplitHub; saída, quando o SplitHub chama o endpoint do ERP; e bidirecional, no caso do RAD.</t>
+          <t>O pagamento do RAD opera a apropriação do crédito pelo comprador, e o reconhecimento vem da integração com o Fisco — não do comprovante.</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-01 Listar conexões agrupadas por direção</t>
+          <t>PRD de Execução RAD</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
@@ -10667,27 +10659,27 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Integrações</t>
+          <t>Execução RAD</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Assistente de nova conexão em três passos</t>
+          <t>Conciliação financeira do recolhimento</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Tipo, configuração e credenciais. O tipo escolhido determina o que a plataforma pede e o que emite ao final.</t>
+          <t>Confronto entre o que o Fisco reconheceu e o comprovante que o ERP enviou. Divergência dos dois lados vira ocorrência.</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-02 Escolher o tipo no catálogo</t>
+          <t>PRD de Execução RAD</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
@@ -10723,22 +10715,22 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Emissão de credencial de API</t>
+          <t>Catálogo dos seis contextos da API</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>client_id e client_secret, trocados por um JWT. Fecha o vão que a documentação de autenticação declarava não especificar — antes, cada cliente era integrado fora do produto.</t>
+          <t>Ingestão de DFs, fornecedores, contratos, RAD ↔ ERP, garantia de crédito e automações — cada um com endpoints, eventos, escopos e limites derivados da documentação publicada.</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-05 Emitir credenciais com exibição única</t>
+          <t>PRD de Integrações · F-02 Escolher o tipo no catálogo</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
@@ -10746,13 +10738,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I196" s="10" t="inlineStr">
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J196" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J196" s="3" t="inlineStr"/>
-      <c r="K196" s="3" t="inlineStr"/>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L196" s="3" t="inlineStr"/>
       <c r="M196" s="7" t="inlineStr"/>
       <c r="N196" s="7" t="inlineStr"/>
@@ -10774,22 +10774,22 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Exibição única do segredo</t>
+          <t>Conexões nas duas direções</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>O valor aparece em claro uma só vez; a plataforma guarda apenas o hash. Fechada a tela, o painel mostra os quatro últimos caracteres.</t>
+          <t>Entrada, quando o ERP chama a API do SplitHub; saída, quando o SplitHub chama o endpoint do ERP; e bidirecional, no caso do RAD.</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-05 Emitir credenciais com exibição única</t>
+          <t>PRD de Integrações · F-01 Listar conexões agrupadas por direção</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr">
@@ -10825,22 +10825,22 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Escopos por contexto</t>
+          <t>Assistente de nova conexão em três passos</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>Cada escopo declara o que o JWT poderá fazer. Os destrutivos não vêm marcados por padrão; chamada fora do escopo retorna 403.</t>
+          <t>Tipo, configuração e credenciais. O tipo escolhido determina o que a plataforma pede e o que emite ao final.</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-04 Configurar escopos, destino e alcance</t>
+          <t>PRD de Integrações · F-02 Escolher o tipo no catálogo</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr">
@@ -10876,17 +10876,17 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Rotação com janela de sobreposição</t>
+          <t>Emissão de credencial de API</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>O segredo anterior segue válido por 24 horas, para dar janela de troca sem derrubar a integração. Na conexão bidirecional, as duas rotações são independentes.</t>
+          <t>client_id e client_secret, trocados por um JWT. Fecha o vão que a documentação de autenticação declarava não especificar — antes, cada cliente era integrado fora do produto.</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-07 Rotacionar o segredo com janela de sobreposição</t>
+          <t>PRD de Integrações · F-05 Emitir credenciais com exibição única</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -10927,22 +10927,22 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Exemplo da primeira chamada</t>
+          <t>Exibição única do segredo</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>O curl do login e da chamada autenticada, montado com os valores reais — ou o cálculo do HMAC do header de assinatura, no caso das conexões de saída.</t>
+          <t>O valor aparece em claro uma só vez; a plataforma guarda apenas o hash. Fechada a tela, o painel mostra os quatro últimos caracteres.</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-06 Montar o exemplo da primeira chamada</t>
+          <t>PRD de Integrações · F-05 Emitir credenciais com exibição única</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Alcance por CNPJ</t>
+          <t>Escopos por contexto</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>A conexão pode ser restringida a um subconjunto de estabelecimentos. Uma credencial de filial não deveria enviar documento de outra.</t>
+          <t>Cada escopo declara o que o JWT poderá fazer. Os destrutivos não vêm marcados por padrão; chamada fora do escopo retorna 403.</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
@@ -11029,22 +11029,22 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Health check por conexão</t>
+          <t>Rotação com janela de sobreposição</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Estado operacional, degradado, fora do ar ou sem tráfego, com disponibilidade em 24h, 7 e 30 dias e latência p50/p95.</t>
+          <t>O segredo anterior segue válido por 24 horas, para dar janela de troca sem derrubar a integração. Na conexão bidirecional, as duas rotações são independentes.</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-10 Classificar a saúde de cada conexão</t>
+          <t>PRD de Integrações · F-07 Rotacionar o segredo com janela de sobreposição</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
@@ -11080,22 +11080,22 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Sonda ativa e observação passiva</t>
+          <t>Exemplo da primeira chamada</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Conexão de saída é sondada com evento de teste. Conexão de entrada não tem o que sondar — quem chama é o ERP —, e ali a leitura vem do tráfego recebido.</t>
+          <t>O curl do login e da chamada autenticada, montado com os valores reais — ou o cálculo do HMAC do header de assinatura, no caso das conexões de saída.</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-11 Executar health check sob demanda</t>
+          <t>PRD de Integrações · F-06 Montar o exemplo da primeira chamada</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
@@ -11131,22 +11131,22 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Histórico de incidentes</t>
+          <t>Alcance por CNPJ</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Severidade, causa classificada, duração, impacto quantificado e linha do tempo com detecção, alerta, diagnóstico e resolução.</t>
+          <t>A conexão pode ser restringida a um subconjunto de estabelecimentos. Uma credencial de filial não deveria enviar documento de outra.</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-12 Registrar o histórico de incidentes</t>
+          <t>PRD de Integrações · F-04 Configurar escopos, destino e alcance</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
@@ -11182,22 +11182,22 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Log de entregas com inspeção de payload</t>
+          <t>Health check por conexão</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Evento, chave do documento, tentativas e status HTTP, com o JSON exato transmitido. Sem isso, depurar divergência com o ERP vira troca de e-mails.</t>
+          <t>Estado operacional, degradado, fora do ar ou sem tráfego, com disponibilidade em 24h, 7 e 30 dias e latência p50/p95.</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-14 Listar e inspecionar entregas</t>
+          <t>PRD de Integrações · F-10 Classificar a saúde de cada conexão</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr">
@@ -11233,22 +11233,22 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Reenvio de entrega</t>
+          <t>Sonda ativa e observação passiva</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Individual ou em lote. A especificação diz que o SplitHub reenvia até receber 200 OK, mas não define o teto — o reenvio manual cobre o caso em que a automática desiste.</t>
+          <t>Conexão de saída é sondada com evento de teste. Conexão de entrada não tem o que sondar — quem chama é o ERP —, e ali a leitura vem do tráfego recebido.</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-15 Reenviar entrega</t>
+          <t>PRD de Integrações · F-11 Executar health check sob demanda</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">
@@ -11284,22 +11284,22 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Comprovantes recebidos do ERP</t>
+          <t>Histórico de incidentes</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Chamadas ao endpoint de comprovante, com identificador da guia, meio, valor e resultado. As rejeitadas aparecem isoladas, com o motivo.</t>
+          <t>Severidade, causa classificada, duração, impacto quantificado e linha do tempo com detecção, alerta, diagnóstico e resolução.</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-16 Listar comprovantes recebidos e isolar rejeitados</t>
+          <t>PRD de Integrações · F-12 Registrar o histórico de incidentes</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
@@ -11307,21 +11307,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I207" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J207" s="11" t="inlineStr">
+      <c r="I207" s="10" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="K207" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J207" s="3" t="inlineStr"/>
+      <c r="K207" s="3" t="inlineStr"/>
       <c r="L207" s="3" t="inlineStr"/>
       <c r="M207" s="7" t="inlineStr"/>
       <c r="N207" s="7" t="inlineStr"/>
@@ -11343,22 +11335,22 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Teste de conexão</t>
+          <t>Log de entregas com inspeção de payload</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Dispara um evento de teste com payload fictício e mostra a resposta HTTP. Valida a URL antes de a política de execução depender dela.</t>
+          <t>Evento, chave do documento, tentativas e status HTTP, com o JSON exato transmitido. Sem isso, depurar divergência com o ERP vira troca de e-mails.</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · F-08 Testar conexão</t>
+          <t>PRD de Integrações · F-14 Listar e inspecionar entregas</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H208" s="3" t="inlineStr">
@@ -11394,22 +11386,22 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Webhook do ciclo do crédito ao ERP</t>
+          <t>Reenvio de entrega</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Toda mudança de status do crédito dispara evento para o ERP — registrado, apropriado, utilizado e glosado —, com envio e entrega registrados no histórico do registro fiscal e do documento.</t>
+          <t>Individual ou em lote. A especificação diz que o SplitHub reenvia até receber 200 OK, mas não define o teto — o reenvio manual cobre o caso em que a automática desiste.</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · Seção 01 Contexto e posicionamento</t>
+          <t>PRD de Integrações · F-15 Reenviar entrega</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr">
@@ -11445,22 +11437,22 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Comprovante de recolhimento recebido do ERP</t>
+          <t>Comprovantes recebidos do ERP</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>O comprovante chega pela integração e entra na trilha antes da apropriação do crédito, conciliado com o pagamento.</t>
+          <t>Chamadas ao endpoint de comprovante, com identificador da guia, meio, valor e resultado. As rejeitadas aparecem isoladas, com o motivo.</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações · Seção 01 Contexto e posicionamento</t>
+          <t>PRD de Integrações · F-16 Listar comprovantes recebidos e isolar rejeitados</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr">
@@ -11468,13 +11460,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I210" s="10" t="inlineStr">
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J210" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J210" s="3" t="inlineStr"/>
-      <c r="K210" s="3" t="inlineStr"/>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L210" s="3" t="inlineStr"/>
       <c r="M210" s="7" t="inlineStr"/>
       <c r="N210" s="7" t="inlineStr"/>
@@ -11496,17 +11496,17 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Evento de mudança de estado do débito</t>
+          <t>Teste de conexão</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>O contrato público prevê o aviso ao ERP quando um débito é extinto, com os créditos que o abateram. O produto ainda não emite nada quando o débito muda.</t>
+          <t>Dispara um evento de teste com payload fictício e mostra a resposta HTTP. Valida a URL antes de a política de execução depender dela.</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações</t>
+          <t>PRD de Integrações · F-08 Testar conexão</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -11547,22 +11547,22 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Eventos da guia de RAD ao ERP</t>
+          <t>Webhook do ciclo do crédito ao ERP</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>Guia gerada, individual ou em lote, com número, vencimento, chave PIX, código de barras, PDF e o valor líquido ao fornecedor.</t>
+          <t>Toda mudança de status do crédito dispara evento para o ERP — registrado, apropriado, utilizado e glosado —, com envio e entrega registrados no histórico do registro fiscal e do documento.</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações</t>
+          <t>PRD de Integrações · Seção 01 Contexto e posicionamento</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
@@ -11598,17 +11598,17 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Evento de comprovante processado</t>
+          <t>Comprovante de recolhimento recebido do ERP</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>Confirma ao ERP o processamento do comprovante, com protocolo e situação na Receita.</t>
+          <t>O comprovante chega pela integração e entra na trilha antes da apropriação do crédito, conciliado com o pagamento.</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>PRD de Integrações</t>
+          <t>PRD de Integrações · Seção 01 Contexto e posicionamento</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -11649,22 +11649,22 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Inscrição do ERP nos eventos de automação</t>
+          <t>Evento de mudança de estado do débito</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>O ERP registra a própria URL e escolhe os eventos; lista vazia recebe todos.</t>
+          <t>O contrato público prevê o aviso ao ERP quando um débito é extinto, com os créditos que o abateram. O produto ainda não emite nada quando o débito muda.</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações</t>
+          <t>PRD de Integrações</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
@@ -11672,9 +11672,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I214" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I214" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr"/>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Ambientes de teste e de produção</t>
+          <t>Eventos da guia de RAD ao ERP</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>Sandbox separado da produção, com credencial própria, para o cliente integrar sem tocar em dado real.</t>
+          <t>Guia gerada, individual ou em lote, com número, vencimento, chave PIX, código de barras, PDF e o valor líquido ao fornecedor.</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr">
@@ -11751,32 +11751,32 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Integração com a Receita Federal — CBS</t>
+          <t>Evento de comprovante processado</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>Apuração assistida da CBS na Plataforma da RFB: autenticação, solicitação e retirada do resultado apurado por período. É a metade federal do confronto que hoje a conciliação simula.</t>
-        </is>
-      </c>
-      <c r="F216" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Confirma ao ERP o processamento do comprovante, com protocolo e situação na Receita.</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Integrações</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H216" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I216" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I216" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J216" s="3" t="inlineStr"/>
@@ -11802,17 +11802,17 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Integração com o Comitê Gestor — IBS</t>
+          <t>Inscrição do ERP nos eventos de automação</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>Apuração assistida do IBS no CG-IBS: credencial própria, recebimento por webhook e arquivo diferencial, com a conta corrente fiscal por operação. É a outra metade do confronto.</t>
-        </is>
-      </c>
-      <c r="F217" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>O ERP registra a própria URL e escolhe os eventos; lista vazia recebe todos.</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -11820,14 +11820,14 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="H217" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I217" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I217" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J217" s="3" t="inlineStr"/>
@@ -11853,32 +11853,32 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Integração RAD</t>
+          <t>Ambientes de teste e de produção</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>Geração e liquidação da guia de recolhimento pelo adquirente junto ao órgão arrecadador, com retorno do pagamento. Hoje a guia é produzida dentro do produto e o comprovante volta à mão.</t>
-        </is>
-      </c>
-      <c r="F218" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Sandbox separado da produção, com credencial própria, para o cliente integrar sem tocar em dado real.</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Integrações</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="H218" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="I218" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I218" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J218" s="3" t="inlineStr"/>
@@ -11904,12 +11904,12 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Integração Databricks para comprovantes</t>
+          <t>Integração com a Receita Federal — CBS</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>Ingestão de comprovantes de recolhimento a partir do lakehouse do cliente, em vez de upload arquivo a arquivo. É o que alimenta a conciliação financeira em volume.</t>
+          <t>Apuração assistida da CBS na Plataforma da RFB: autenticação, solicitação e retirada do resultado apurado por período. É a metade federal do confronto que hoje a conciliação simula.</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
@@ -11945,37 +11945,37 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Painel unificado da jornada do documento</t>
+          <t>Integração com o Comitê Gestor — IBS</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>Cinco marcos por documento — ingestão, confirmação do governo, IBS pago, CBS pago e crédito apropriado — com o volume parado em cada um. Mostra onde a jornada trava antes de o crédito estar garantido.</t>
-        </is>
-      </c>
-      <c r="F220" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Conciliação IBS/CBS · F-05 Apresentar o painel unificado</t>
+          <t>Apuração assistida do IBS no CG-IBS: credencial própria, recebimento por webhook e arquivo diferencial, com a conta corrente fiscal por operação. É a outra metade do confronto.</t>
+        </is>
+      </c>
+      <c r="F220" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
-        </is>
-      </c>
-      <c r="H220" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H220" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I220" s="6" t="inlineStr">
@@ -11996,37 +11996,37 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Confronto com a Apuração Assistida</t>
+          <t>Integração RAD</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>Compara o que o SplitHub apurou com o que a Apuração Assistida devolveu, documento a documento. Divergência vira inconsistência CAPUR, por tributo.</t>
-        </is>
-      </c>
-      <c r="F221" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Conciliação IBS/CBS · F-01 Confrontar valores com a Apuração Assistida</t>
+          <t>Geração e liquidação da guia de recolhimento pelo adquirente junto ao órgão arrecadador, com retorno do pagamento. Hoje a guia é produzida dentro do produto e o comprovante volta à mão.</t>
+        </is>
+      </c>
+      <c r="F221" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
-        </is>
-      </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H221" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I221" s="6" t="inlineStr">
@@ -12047,37 +12047,37 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Conciliação</t>
+          <t>Integrações</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Conciliação financeira pelos comprovantes</t>
+          <t>Integração Databricks para comprovantes</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>Confere o valor recolhido contra o valor devido usando os comprovantes recebidos. Divergência vira inconsistência CFIN, por tributo.</t>
-        </is>
-      </c>
-      <c r="F222" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Conciliação IBS/CBS · F-02 Derivar a conciliação financeira dos comprovantes</t>
+          <t>Ingestão de comprovantes de recolhimento a partir do lakehouse do cliente, em vez de upload arquivo a arquivo. É o que alimenta a conciliação financeira em volume.</t>
+        </is>
+      </c>
+      <c r="F222" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
-        </is>
-      </c>
-      <c r="H222" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H222" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
         </is>
       </c>
       <c r="I222" s="6" t="inlineStr">
@@ -12108,22 +12108,22 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Sequenciamento das duas conciliações</t>
+          <t>Painel unificado da jornada do documento</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>A conciliação financeira só é avaliada depois de a apuração fechar. Conciliar pagamento contra um valor que o governo ainda não confirmou produz divergência falsa.</t>
+          <t>Cinco marcos por documento — ingestão, confirmação do governo, IBS pago, CBS pago e crédito apropriado — com o volume parado em cada um. Mostra onde a jornada trava antes de o crédito estar garantido.</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-03 Sequenciar os dois processos</t>
+          <t>PRD de Conciliação IBS/CBS · F-05 Apresentar o painel unificado</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
@@ -12159,22 +12159,22 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Próxima ação sugerida por documento</t>
+          <t>Confronto com a Apuração Assistida</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>Cada documento carrega a ação que destrava a jornada: cobrar comprovante, abrir inconsistência, reprocessar a apuração ou apropriar o crédito.</t>
+          <t>Compara o que o SplitHub apurou com o que a Apuração Assistida devolveu, documento a documento. Divergência vira inconsistência CAPUR, por tributo.</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-04 Sugerir a próxima ação por documento</t>
+          <t>PRD de Conciliação IBS/CBS · F-01 Confrontar valores com a Apuração Assistida</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H224" s="3" t="inlineStr">
@@ -12187,16 +12187,8 @@
           <t>M0</t>
         </is>
       </c>
-      <c r="J224" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K224" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J224" s="3" t="inlineStr"/>
+      <c r="K224" s="3" t="inlineStr"/>
       <c r="L224" s="3" t="inlineStr"/>
       <c r="M224" s="7" t="inlineStr"/>
       <c r="N224" s="7" t="inlineStr"/>
@@ -12218,22 +12210,22 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Listagem de registros com oito filtros</t>
+          <t>Conciliação financeira pelos comprovantes</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>Registros fiscais filtrados por tipo de documento, estado CAPUR, estado CFIN, tributo, entidade, período, valor e fornecedor.</t>
+          <t>Confere o valor recolhido contra o valor devido usando os comprovantes recebidos. Divergência vira inconsistência CFIN, por tributo.</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-06 Listar registros fiscais com oito filtros</t>
+          <t>PRD de Conciliação IBS/CBS · F-02 Derivar a conciliação financeira dos comprovantes</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
@@ -12269,17 +12261,17 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Propagação do resultado para documento e registros</t>
+          <t>Sequenciamento das duas conciliações</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>O resultado da conciliação de cada registro sobe para o documento pela regra de pior estado, e o documento só fica conciliado quando IBS e CBS fecham.</t>
+          <t>A conciliação financeira só é avaliada depois de a apuração fechar. Conciliar pagamento contra um valor que o governo ainda não confirmou produz divergência falsa.</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-07 Propagar o resultado para documento e registros</t>
+          <t>PRD de Conciliação IBS/CBS · F-03 Sequenciar os dois processos</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -12320,22 +12312,22 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Recorte por múltiplos períodos</t>
+          <t>Próxima ação sugerida por documento</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Seleção de várias competências ao mesmo tempo, porque divergência de apuração costuma aparecer na virada do mês.</t>
+          <t>Cada documento carrega a ação que destrava a jornada: cobrar comprovante, abrir inconsistência, reprocessar a apuração ou apropriar o crédito.</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS · F-08 Recortar por múltiplos períodos</t>
+          <t>PRD de Conciliação IBS/CBS · F-04 Sugerir a próxima ação por documento</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
@@ -12379,17 +12371,17 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Situação tributária por tributo na conciliação</t>
+          <t>Listagem de registros com oito filtros</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>O código de situação que o Fisco registrou, por IBS e por CBS. É o campo que decide se a linha gera crédito: conciliar valor sem conciliar situação esconde a divergência que mais importa.</t>
+          <t>Registros fiscais filtrados por tipo de documento, estado CAPUR, estado CFIN, tributo, entidade, período, valor e fornecedor.</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>PRD de Conciliação IBS/CBS</t>
+          <t>PRD de Conciliação IBS/CBS · F-06 Listar registros fiscais com oito filtros</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -12402,9 +12394,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I228" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I228" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J228" s="3" t="inlineStr"/>
@@ -12425,27 +12417,27 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Resumo por tributo na competência</t>
+          <t>Propagação do resultado para documento e registros</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>Saldo inicial, créditos apropriados, créditos utilizados em compensação, débitos, débitos extintos e tributo a pagar, com IBS e CBS em linhas próprias. Crédito ressarcido não conta como utilizado.</t>
-        </is>
-      </c>
-      <c r="F229" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>O resultado da conciliação de cada registro sobe para o documento pela regra de pior estado, e o documento só fica conciliado quando IBS e CBS fecham.</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Conciliação IBS/CBS · F-07 Propagar o resultado para documento e registros</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
@@ -12476,27 +12468,27 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Posição detalhada de créditos e débitos</t>
+          <t>Recorte por múltiplos períodos</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>Abre o resumo em créditos a apropriar, apropriados e utilizados, e em débitos extintos e em aberto, com o percentual de cada faixa.</t>
-        </is>
-      </c>
-      <c r="F230" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Seleção de várias competências ao mesmo tempo, porque divergência de apuração costuma aparecer na virada do mês.</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Conciliação IBS/CBS · F-08 Recortar por múltiplos períodos</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
@@ -12504,13 +12496,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I230" s="10" t="inlineStr">
+      <c r="I230" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J230" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="J230" s="3" t="inlineStr"/>
-      <c r="K230" s="3" t="inlineStr"/>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L230" s="3" t="inlineStr"/>
       <c r="M230" s="7" t="inlineStr"/>
       <c r="N230" s="7" t="inlineStr"/>
@@ -12527,27 +12527,27 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Apuração IBS/CBS</t>
+          <t>Conciliação</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Cálculo da competência</t>
+          <t>Situação tributária por tributo na conciliação</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>Recalcula a apuração a partir dos documentos e registros do período, registrando data e hora da última execução.</t>
-        </is>
-      </c>
-      <c r="F231" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>O código de situação que o Fisco registrou, por IBS e por CBS. É o campo que decide se a linha gera crédito: conciliar valor sem conciliar situação esconde a divergência que mais importa.</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Conciliação IBS/CBS</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
@@ -12555,9 +12555,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I231" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I231" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J231" s="3" t="inlineStr"/>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Conclusão e reabertura da apuração</t>
+          <t>Resumo por tributo na competência</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>Fecha a competência para congelar a posição, e permite reabrir quando um documento retardatário ou uma conciliação muda o resultado.</t>
+          <t>Saldo inicial, créditos apropriados, créditos utilizados em compensação, débitos, débitos extintos e tributo a pagar, com IBS e CBS em linhas próprias. Crédito ressarcido não conta como utilizado.</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Abas Resumo, Créditos e Débitos</t>
+          <t>Posição detalhada de créditos e débitos</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>Três recortes da mesma competência: o consolidado por tributo, a composição do crédito e a composição do débito.</t>
+          <t>Abre o resumo em créditos a apropriar, apropriados e utilizados, e em débitos extintos e em aberto, com o percentual de cada faixa.</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
@@ -12657,9 +12657,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I233" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I233" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J233" s="3" t="inlineStr"/>
@@ -12685,12 +12685,12 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Navegação entre competências</t>
+          <t>Cálculo da competência</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>Troca de período com o estado da apuração visível — calculada, concluída ou reaberta.</t>
+          <t>Recalcula a apuração a partir dos documentos e registros do período, registrando data e hora da última execução.</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Exportação da apuração</t>
+          <t>Conclusão e reabertura da apuração</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>Gera o arquivo da posição apurada para conferência fora do sistema e para anexar ao fechamento contábil.</t>
+          <t>Fecha a competência para congelar a posição, e permite reabrir quando um documento retardatário ou uma conciliação muda o resultado.</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
@@ -12759,9 +12759,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I235" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I235" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J235" s="3" t="inlineStr"/>
@@ -12787,22 +12787,22 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Saída para ressarcimento no transporte do saldo</t>
+          <t>Abas Resumo, Créditos e Débitos</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>O saldo que vai para intenção ou pedido não é transportado para compensação, e o crédito ressarcido fica fora dos utilizados — não abate tributo a pagar.</t>
-        </is>
-      </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
+          <t>Três recortes da mesma competência: o consolidado por tributo, a composição do crédito e a composição do débito.</t>
+        </is>
+      </c>
+      <c r="F236" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H236" s="3" t="inlineStr">
@@ -12810,9 +12810,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I236" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I236" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J236" s="3" t="inlineStr"/>
@@ -12838,22 +12838,22 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Uso do crédito na ordem do art. 53</t>
+          <t>Navegação entre competências</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>A apuração cobre primeiro o saldo a recolher vencido, depois os débitos do próprio período, e o que sobra vira saldo credor. Por tributo, sem cruzar IBS e CBS.</t>
-        </is>
-      </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Apuração IBS/CBS · Seção 03 A ordem de uso do crédito</t>
+          <t>Troca de período com o estado da apuração visível — calculada, concluída ou reaberta.</t>
+        </is>
+      </c>
+      <c r="F237" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H237" s="3" t="inlineStr">
@@ -12861,9 +12861,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I237" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I237" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J237" s="3" t="inlineStr"/>
@@ -12889,22 +12889,22 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Saldo credor transportado entre períodos</t>
+          <t>Exportação da apuração</t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>O saldo final de um período abre o seguinte e é consumido antes do crédito novo, aparecendo identificado como saldo anterior com o documento de origem.</t>
-        </is>
-      </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Apuração IBS/CBS · Seção 04 O período de apuração</t>
+          <t>Gera o arquivo da posição apurada para conferência fora do sistema e para anexar ao fechamento contábil.</t>
+        </is>
+      </c>
+      <c r="F238" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
@@ -12940,22 +12940,22 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Compensação parcial com vínculo dos dois lados</t>
+          <t>Saída para ressarcimento no transporte do saldo</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>Um crédito pode abater vários débitos e um débito receber vários créditos. Cada abatimento registra origem, destino e valor, e alimenta as listagens, o detalhe do registro e o histórico.</t>
+          <t>O saldo que vai para intenção ou pedido não é transportado para compensação, e o crédito ressarcido fica fora dos utilizados — não abate tributo a pagar.</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>PRD de Apuração IBS/CBS · Seção 03 A ordem de uso do crédito</t>
+          <t>PRD de Ressarcimento · Seção 09 Integração com os outros módulos</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
@@ -12991,22 +12991,22 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Devolução de deferimento parcial</t>
+          <t>Uso do crédito na ordem do art. 53</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>O crédito não reconhecido num pedido de ressarcimento volta ao saldo na data da decisão e aparece na apuração daquele período como devolução.</t>
+          <t>A apuração cobre primeiro o saldo a recolher vencido, depois os débitos do próprio período, e o que sobra vira saldo credor. Por tributo, sem cruzar IBS e CBS.</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>PRD de Apuração IBS/CBS · Seção 04 O período de apuração</t>
+          <t>PRD de Apuração IBS/CBS · Seção 03 A ordem de uso do crédito</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H240" s="3" t="inlineStr">
@@ -13042,22 +13042,22 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Reabertura restrita, com justificativa e trilha</t>
+          <t>Saldo credor transportado entre períodos</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>Reabrir desfaz compensação registrada. Só administrador reabre, com justificativa, e todo vínculo desfeito entra na trilha do crédito e do débito.</t>
+          <t>O saldo final de um período abre o seguinte e é consumido antes do crédito novo, aparecendo identificado como saldo anterior com o documento de origem.</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>PRD de Apuração IBS/CBS</t>
+          <t>PRD de Apuração IBS/CBS · Seção 04 O período de apuração</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
@@ -13093,22 +13093,22 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Bloqueio da reabertura com pedido de ressarcimento em análise</t>
+          <t>Compensação parcial com vínculo dos dois lados</t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>Período cujo saldo já foi comprometido com o órgão não reabre.</t>
+          <t>Um crédito pode abater vários débitos e um débito receber vários créditos. Cada abatimento registra origem, destino e valor, e alimenta as listagens, o detalhe do registro e o histórico.</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>PRD de Apuração IBS/CBS</t>
+          <t>PRD de Apuração IBS/CBS · Seção 03 A ordem de uso do crédito</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Crédito a apropriar como medida de risco da cadeia</t>
+          <t>Devolução de deferimento parcial</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>O estoque de crédito travado pela dependência do pagamento do fornecedor — o número que mede o risco da cadeia de fornecedores.</t>
+          <t>O crédito não reconhecido num pedido de ressarcimento volta ao saldo na data da decisão e aparece na apuração daquele período como devolução.</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>PRD de Apuração IBS/CBS</t>
+          <t>PRD de Apuração IBS/CBS · Seção 04 O período de apuração</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H243" s="3" t="inlineStr">
@@ -13185,32 +13185,32 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Assistente Tributário</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Chat livre sobre a legislação</t>
+          <t>Reabertura restrita, com justificativa e trilha</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>Pergunta aberta sobre IBS, CBS e split payment respondida a partir das fontes indexadas, com a referência do dispositivo.</t>
+          <t>Reabrir desfaz compensação registrada. Só administrador reabre, com justificativa, e todo vínculo desfeito entra na trilha do crédito e do débito.</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-15 Responder perguntas sobre a legislação</t>
+          <t>PRD de Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
@@ -13218,9 +13218,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I244" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I244" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J244" s="3" t="inlineStr"/>
@@ -13236,32 +13236,32 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Assistente Tributário</t>
+          <t>Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Diagnóstico guiado por árvore de decisão</t>
+          <t>Bloqueio da reabertura com pedido de ressarcimento em análise</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>Fluxo de perguntas fechadas que leva o operador até o enquadramento do caso, sem depender de ele saber formular a pergunta certa.</t>
+          <t>Período cujo saldo já foi comprometido com o órgão não reabre.</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-16 Conduzir um diagnóstico guiado</t>
+          <t>PRD de Apuração IBS/CBS</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
@@ -13269,9 +13269,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I245" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I245" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J245" s="3" t="inlineStr"/>
@@ -13287,42 +13287,42 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Apuração IBS/CBS</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>Crédito a apropriar como medida de risco da cadeia</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>O estoque de crédito travado pela dependência do pagamento do fornecedor — o número que mede o risco da cadeia de fornecedores.</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Apuração IBS/CBS</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
           <t>Analítico</t>
         </is>
       </c>
-      <c r="C246" s="3" t="inlineStr">
-        <is>
-          <t>Assistente Tributário</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>Fontes indexadas com link para a norma</t>
-        </is>
-      </c>
-      <c r="E246" s="4" t="inlineStr">
-        <is>
-          <t>LC 214/2025 e Decreto 12.955/2026 indexados e acessíveis, com as notas técnicas da RFB em indexação.</t>
-        </is>
-      </c>
-      <c r="F246" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Analytics · F-17 Listar e abrir as fontes indexadas</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>Listagem</t>
-        </is>
-      </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I246" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I246" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J246" s="3" t="inlineStr"/>
@@ -13348,22 +13348,22 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>Histórico de conversas</t>
+          <t>Chat livre sobre a legislação</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>Conversas anteriores preservadas na lateral, para retomar um diagnóstico sem refazer o caminho.</t>
+          <t>Pergunta aberta sobre IBS, CBS e split payment respondida a partir das fontes indexadas, com a referência do dispositivo.</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics · F-18 Preservar o histórico de conversas</t>
+          <t>PRD de Analytics · F-15 Responder perguntas sobre a legislação</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
@@ -13399,22 +13399,22 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Resposta ancorada nos números da base</t>
+          <t>Diagnóstico guiado por árvore de decisão</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>A resposta cita os números de onde saiu, respeita o recorte da tela e nunca soma os dois tributos. O assistente responde e leva à tela; não executa ação.</t>
+          <t>Fluxo de perguntas fechadas que leva o operador até o enquadramento do caso, sem depender de ele saber formular a pergunta certa.</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>PRD de Analytics</t>
+          <t>PRD de Analytics · F-16 Conduzir um diagnóstico guiado</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H248" s="3" t="inlineStr">
@@ -13440,32 +13440,32 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Assistente Tributário</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Relatórios agendados por módulo</t>
+          <t>Fontes indexadas com link para a norma</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>Envio recorrente de crédito, débito, inconsistências, pagamentos ou consolidado, com destinatários, recorrência, dia e hora e formato.</t>
+          <t>LC 214/2025 e Decreto 12.955/2026 indexados e acessíveis, com as notas técnicas da RFB em indexação.</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-01 Agendar relatório por módulo</t>
+          <t>PRD de Analytics · F-17 Listar e abrir as fontes indexadas</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H249" s="3" t="inlineStr">
@@ -13473,9 +13473,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I249" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I249" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J249" s="3" t="inlineStr"/>
@@ -13491,32 +13491,32 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Assistente Tributário</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Ativação, edição e exclusão de agendamento</t>
+          <t>Histórico de conversas</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>Liga e desliga um relatório sem perder a configuração, e mostra último e próximo envio.</t>
+          <t>Conversas anteriores preservadas na lateral, para retomar um diagnóstico sem refazer o caminho.</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-02 Ligar, desligar e excluir agendamento</t>
+          <t>PRD de Analytics · F-18 Preservar o histórico de conversas</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H250" s="3" t="inlineStr">
@@ -13524,9 +13524,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I250" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I250" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J250" s="3" t="inlineStr"/>
@@ -13542,32 +13542,32 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Automações</t>
+          <t>Assistente Tributário</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Integração ITSM por evento</t>
+          <t>Resposta ancorada nos números da base</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>Quatro eventos do produto — nova inconsistência, status alterado, registro próximo do vencimento e conciliação parada — abrem chamado no sistema de ITSM, cada um ligável em separado.</t>
+          <t>A resposta cita os números de onde saiu, respeita o recorte da tela e nunca soma os dois tributos. O assistente responde e leva à tela; não executa ação.</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-04 Escolher quais eventos abrem chamado</t>
+          <t>PRD de Analytics</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
@@ -13580,16 +13580,8 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="J251" s="11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="K251" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="J251" s="3" t="inlineStr"/>
+      <c r="K251" s="3" t="inlineStr"/>
       <c r="L251" s="3" t="inlineStr"/>
       <c r="M251" s="7" t="inlineStr"/>
       <c r="N251" s="7" t="inlineStr"/>
@@ -13611,17 +13603,17 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Mapeamento dos campos do chamado</t>
+          <t>Relatórios agendados por módulo</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>Título, prioridade e categoria montados por template com variáveis do registro, para o chamado chegar tratável do outro lado.</t>
+          <t>Envio recorrente de crédito, débito, inconsistências, pagamentos ou consolidado, com destinatários, recorrência, dia e hora e formato.</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-05 Montar o chamado por template</t>
+          <t>PRD de Automações · F-01 Agendar relatório por módulo</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -13662,22 +13654,22 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Histórico de chamados abertos</t>
+          <t>Ativação, edição e exclusão de agendamento</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>Evento, registro, status HTTP e número do chamado de cada envio, inclusive os que falharam.</t>
+          <t>Liga e desliga um relatório sem perder a configuração, e mostra último e próximo envio.</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-06 Acompanhar o histórico de envios ao ITSM</t>
+          <t>PRD de Automações · F-02 Ligar, desligar e excluir agendamento</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H253" s="3" t="inlineStr">
@@ -13713,17 +13705,17 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Régua de cobrança pré-vencimento</t>
+          <t>Integração ITSM por evento</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>Sequência de avisos antes do vencimento, com gatilho em dias, número máximo de envios e intervalo entre eles.</t>
+          <t>Quatro eventos do produto — nova inconsistência, status alterado, registro próximo do vencimento e conciliação parada — abrem chamado no sistema de ITSM, cada um ligável em separado.</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-07 Criar régua de cobrança pelo assistente</t>
+          <t>PRD de Automações · F-04 Escolher quais eventos abrem chamado</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -13736,13 +13728,21 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I254" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J254" s="3" t="inlineStr"/>
-      <c r="K254" s="3" t="inlineStr"/>
+      <c r="I254" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J254" s="11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L254" s="3" t="inlineStr"/>
       <c r="M254" s="7" t="inlineStr"/>
       <c r="N254" s="7" t="inlineStr"/>
@@ -13764,17 +13764,17 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Régua de cobrança pós-vencimento</t>
+          <t>Mapeamento dos campos do chamado</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>Sequência de cobranças depois do vencimento, com escalada gerencial e abertura de chamado quando a mora persiste.</t>
+          <t>Título, prioridade e categoria montados por template com variáveis do registro, para o chamado chegar tratável do outro lado.</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-07 Criar régua de cobrança pelo assistente</t>
+          <t>PRD de Automações · F-05 Montar o chamado por template</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -13787,9 +13787,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I255" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I255" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J255" s="3" t="inlineStr"/>
@@ -13815,22 +13815,22 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Etapas da régua com canal e condição</t>
+          <t>Histórico de chamados abertos</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>Cada etapa define o dia relativo ao vencimento, o canal e a condição de disparo, e pode escalar para a régua seguinte.</t>
+          <t>Evento, registro, status HTTP e número do chamado de cada envio, inclusive os que falharam.</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-08 Desenhar as etapas da régua</t>
+          <t>PRD de Automações · F-06 Acompanhar o histórico de envios ao ITSM</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
@@ -13838,9 +13838,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I256" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I256" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J256" s="3" t="inlineStr"/>
@@ -13866,17 +13866,17 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Template de mensagem com variáveis</t>
+          <t>Régua de cobrança pré-vencimento</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>Assunto e corpo com fornecedor, registro, tributo, valor, vencimento e dias de atraso preenchidos no envio.</t>
+          <t>Sequência de avisos antes do vencimento, com gatilho em dias, número máximo de envios e intervalo entre eles.</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-09 Escrever a mensagem com variáveis</t>
+          <t>PRD de Automações · F-07 Criar régua de cobrança pelo assistente</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -13917,22 +13917,22 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Disparos por fornecedor e etapa</t>
+          <t>Régua de cobrança pós-vencimento</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>Histórico do que foi enviado, para quem, em que etapa e com que resultado — entregue, aberto, devolvido ou convertido em chamado.</t>
+          <t>Sequência de cobranças depois do vencimento, com escalada gerencial e abertura de chamado quando a mora persiste.</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-11 Acompanhar os disparos por fornecedor</t>
+          <t>PRD de Automações · F-07 Criar régua de cobrança pelo assistente</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
@@ -13968,22 +13968,22 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Auditoria da régua com motivo</t>
+          <t>Etapas da régua com canal e condição</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>Criação, ativação e cada alteração de parâmetro ficam registradas com autor, data e justificativa.</t>
+          <t>Cada etapa define o dia relativo ao vencimento, o canal e a condição de disparo, e pode escalar para a régua seguinte.</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações · F-12 Auditar a régua</t>
+          <t>PRD de Automações · F-08 Desenhar as etapas da régua</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
@@ -14019,22 +14019,22 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Evento de automação executada e de falha</t>
+          <t>Template de mensagem com variáveis</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>O ERP recebe o resultado de cada automação, com gatilho, ação, duração e o erro quando houver.</t>
+          <t>Assunto e corpo com fornecedor, registro, tributo, valor, vencimento e dias de atraso preenchidos no envio.</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>PRD de Automações</t>
+          <t>PRD de Automações · F-09 Escrever a mensagem com variáveis</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
@@ -14042,9 +14042,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I260" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I260" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J260" s="3" t="inlineStr"/>
@@ -14070,27 +14070,27 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Motor de execução das automações</t>
+          <t>Disparos por fornecedor e etapa</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>O que faz a régua disparar: avaliação diária dos registros contra as etapas, respeito ao teto de envios e ao intervalo, e registro do disparo. Não existe hoje — o módulo desenha automações e não executa nenhuma.</t>
-        </is>
-      </c>
-      <c r="F261" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Histórico do que foi enviado, para quem, em que etapa e com que resultado — entregue, aberto, devolvido ou convertido em chamado.</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações · F-11 Acompanhar os disparos por fornecedor</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H261" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I261" s="6" t="inlineStr">
@@ -14121,27 +14121,27 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Envio de e-mail transacional</t>
+          <t>Auditoria da régua com motivo</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>Provedor de envio, com registro de entrega e devolução. Serve à régua e também ao convite do fornecedor, que hoje é simulado na tela. Sem ele, régua ativa é régua que não cobra ninguém.</t>
-        </is>
-      </c>
-      <c r="F262" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Criação, ativação e cada alteração de parâmetro ficam registradas com autor, data e justificativa.</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações · F-12 Auditar a régua</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
-        </is>
-      </c>
-      <c r="H262" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I262" s="6" t="inlineStr">
@@ -14167,27 +14167,27 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Listagem de membros da organização</t>
+          <t>Evento de automação executada e de falha</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>Usuário, e-mail, perfil, último acesso e situação, com o total de ativos, administradores, convites pendentes e inativos.</t>
-        </is>
-      </c>
-      <c r="F263" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>O ERP recebe o resultado de cada automação, com gatilho, ação, duração e o erro quando houver.</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Automações</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
@@ -14218,17 +14218,17 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Perfis de acesso</t>
+          <t>Motor de execução das automações</t>
         </is>
       </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
-          <t>Administrador, Analista Fiscal, Controller e Auditor, cada um com o alcance declarado por módulo e a permissão de agir ou só ler.</t>
+          <t>O que faz a régua disparar: avaliação diária dos registros contra as etapas, respeito ao teto de envios e ao intervalo, e registro do disparo. Não existe hoje — o módulo desenha automações e não executa nenhuma.</t>
         </is>
       </c>
       <c r="F264" s="12" t="inlineStr">
@@ -14241,14 +14241,14 @@
           <t>Configuração</t>
         </is>
       </c>
-      <c r="H264" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="I264" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="H264" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+      <c r="I264" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J264" s="3" t="inlineStr"/>
@@ -14269,17 +14269,17 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Usuários e Acessos</t>
+          <t>Automações</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Convite de usuário</t>
+          <t>Envio de e-mail transacional</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>Convida por e-mail com o perfil já definido, e reenvia o convite que não foi aceito.</t>
+          <t>Provedor de envio, com registro de entrega e devolução. Serve à régua e também ao convite do fornecedor, que hoje é simulado na tela. Sem ele, régua ativa é régua que não cobra ninguém.</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
@@ -14289,17 +14289,17 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
-        </is>
-      </c>
-      <c r="H265" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="I265" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H265" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+      <c r="I265" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J265" s="3" t="inlineStr"/>
@@ -14325,12 +14325,12 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Revogação e reativação de acesso</t>
+          <t>Listagem de membros da organização</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
-          <t>Corta o acesso sem apagar o usuário, preservando a trilha do que ele fez, e devolve o acesso quando necessário.</t>
+          <t>Usuário, e-mail, perfil, último acesso e situação, com o total de ativos, administradores, convites pendentes e inativos.</t>
         </is>
       </c>
       <c r="F266" s="12" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H266" s="3" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Abas por situação do acesso</t>
+          <t>Perfis de acesso</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>Todos, ativos, pendentes e inativos, para achar rápido quem está sem acesso ou com convite parado.</t>
+          <t>Administrador, Analista Fiscal, Controller e Auditor, cada um com o alcance declarado por módulo e a permissão de agir ou só ler.</t>
         </is>
       </c>
       <c r="F267" s="12" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H267" s="3" t="inlineStr">
@@ -14427,12 +14427,12 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Painel de acessos externos</t>
+          <t>Convite de usuário</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr">
         <is>
-          <t>Todos os acessos de fornecedores numa tela, com busca, filtro por situação e a trilha recente. Responde quem, de fora da organização, enxerga os dados hoje.</t>
+          <t>Convida por e-mail com o perfil já definido, e reenvia o convite que não foi aceito.</t>
         </is>
       </c>
       <c r="F268" s="12" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
@@ -14450,17 +14450,13 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I268" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J268" s="3" t="inlineStr"/>
-      <c r="K268" s="3" t="inlineStr">
-        <is>
-          <t>Toshio · 15/09/2026</t>
-        </is>
-      </c>
+      <c r="K268" s="3" t="inlineStr"/>
       <c r="L268" s="3" t="inlineStr"/>
       <c r="M268" s="7" t="inlineStr"/>
       <c r="N268" s="7" t="inlineStr"/>
@@ -14482,22 +14478,22 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Catálogo de perfis com o que cada um pode</t>
+          <t>Revogação e reativação de acesso</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
-          <t>Administrador, Fiscal, Tesouraria, Leitura e Fornecedor. O perfil de Tesouraria é pressuposto pelo Ressarcimento e não existia no cadastro.</t>
-        </is>
-      </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Organização</t>
+          <t>Corta o acesso sem apagar o usuário, preservando a trilha do que ele fez, e devolve o acesso quando necessário.</t>
+        </is>
+      </c>
+      <c r="F269" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
@@ -14533,22 +14529,22 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Revogação que derruba a sessão aberta</t>
+          <t>Abas por situação do acesso</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
-          <t>Revogar sem encerrar a sessão deixa uma janela em que o acesso revogado continua valendo.</t>
-        </is>
-      </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Organização</t>
+          <t>Todos, ativos, pendentes e inativos, para achar rápido quem está sem acesso ou com convite parado.</t>
+        </is>
+      </c>
+      <c r="F270" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H270" s="3" t="inlineStr">
@@ -14584,22 +14580,22 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Acesso de fornecedor por pessoa e CNPJ</t>
+          <t>Painel de acessos externos</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>A mesma pessoa pode atender vários fornecedores, com acessos independentes: revogar um não afeta os demais.</t>
-        </is>
-      </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>PRD de Organização</t>
+          <t>Todos os acessos de fornecedores numa tela, com busca, filtro por situação e a trilha recente. Responde quem, de fora da organização, enxerga os dados hoje.</t>
+        </is>
+      </c>
+      <c r="F271" s="12" t="inlineStr">
+        <is>
+          <t>Sem PRD</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H271" s="3" t="inlineStr">
@@ -14607,13 +14603,17 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I271" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I271" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J271" s="3" t="inlineStr"/>
-      <c r="K271" s="3" t="inlineStr"/>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>Toshio · 15/09/2026</t>
+        </is>
+      </c>
       <c r="L271" s="3" t="inlineStr"/>
       <c r="M271" s="7" t="inlineStr"/>
       <c r="N271" s="7" t="inlineStr"/>
@@ -14635,22 +14635,22 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Encerramento programado do acesso</t>
+          <t>Catálogo de perfis com o que cada um pode</t>
         </is>
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
-          <t>O acesso do fornecedor termina junto com o contrato, sem depender de alguém lembrar.</t>
+          <t>Administrador, Fiscal, Tesouraria, Leitura e Fornecedor. O perfil de Tesouraria é pressuposto pelo Ressarcimento e não existia no cadastro.</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>PRD de Contratos</t>
+          <t>PRD de Organização</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H272" s="3" t="inlineStr">
@@ -14658,9 +14658,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I272" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I272" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J272" s="3" t="inlineStr"/>
@@ -14676,32 +14676,32 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>Saldo credor por período e tributo</t>
+          <t>Revogação que derruba a sessão aberta</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
+          <t>Revogar sem encerrar a sessão deixa uma janela em que o acesso revogado continua valendo.</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
+          <t>PRD de Organização</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H273" s="3" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Comparar compensar e ressarcir</t>
+          <t>Acesso de fornecedor por pessoa e CNPJ</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
-          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
+          <t>A mesma pessoa pode atender vários fornecedores, com acessos independentes: revogar um não afeta os demais.</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
+          <t>PRD de Organização</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H274" s="3" t="inlineStr">
@@ -14760,9 +14760,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I274" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I274" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J274" s="3" t="inlineStr"/>
@@ -14778,27 +14778,27 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Declarar e cancelar a intenção</t>
+          <t>Encerramento programado do acesso</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
+          <t>O acesso do fornecedor termina junto com o contrato, sem depender de alguém lembrar.</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
+          <t>PRD de Contratos</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -14811,9 +14811,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I275" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I275" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J275" s="3" t="inlineStr"/>
@@ -14839,22 +14839,22 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Montar o pedido de CBS por documento</t>
+          <t>Saldo credor por período e tributo</t>
         </is>
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
+          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
+          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H276" s="3" t="inlineStr">
@@ -14890,22 +14890,22 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
+          <t>Comparar compensar e ressarcir</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
+          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
+          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H277" s="3" t="inlineStr">
@@ -14913,9 +14913,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I277" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I277" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J277" s="3" t="inlineStr"/>
@@ -14941,22 +14941,22 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Listagem de pedidos do tributo</t>
+          <t>Declarar e cancelar a intenção</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
-          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
+          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
+          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H278" s="3" t="inlineStr">
@@ -14992,22 +14992,22 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Acompanhar análise e fiscalização</t>
+          <t>Montar o pedido de CBS por documento</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
+          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
+          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H279" s="3" t="inlineStr">
@@ -15043,17 +15043,17 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Registrar decisão e cancelamento</t>
+          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
-          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
+          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
+          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -15094,22 +15094,22 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Conciliar o recebimento com Selic</t>
+          <t>Listagem de pedidos do tributo</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
+          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
+          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H281" s="3" t="inlineStr">
@@ -15145,22 +15145,22 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Previsão de entrada de caixa por tributo</t>
+          <t>Acompanhar análise e fiscalização</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
-          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
+          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
+          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H282" s="3" t="inlineStr">
@@ -15168,9 +15168,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I282" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I282" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J282" s="3" t="inlineStr"/>
@@ -15196,22 +15196,22 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Alertas de prazo do ressarcimento</t>
+          <t>Registrar decisão e cancelamento</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
+          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
+          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H283" s="3" t="inlineStr">
@@ -15247,22 +15247,22 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Conferência do saldo com a Receita (CBS)</t>
+          <t>Conciliar o recebimento com Selic</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
+          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
+          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H284" s="3" t="inlineStr">
@@ -15298,22 +15298,22 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Trilha de auditoria do pedido</t>
+          <t>Previsão de entrada de caixa por tributo</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
+          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-13 Auditar</t>
+          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr">
@@ -15321,9 +15321,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I285" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I285" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J285" s="3" t="inlineStr"/>
@@ -15349,22 +15349,22 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Impedimentos do IBS</t>
+          <t>Alertas de prazo do ressarcimento</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
+          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
+          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H286" s="3" t="inlineStr">
@@ -15400,22 +15400,22 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Registrar o pedido de IBS (protocolo)</t>
+          <t>Conferência do saldo com a Receita (CBS)</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
@@ -15435,13 +15435,166 @@
       <c r="N287" s="7" t="inlineStr"/>
       <c r="O287" s="8" t="inlineStr"/>
     </row>
+    <row r="288">
+      <c r="A288" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="inlineStr">
+        <is>
+          <t>Trilha de auditoria do pedido</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
+        </is>
+      </c>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-13 Auditar</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I288" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J288" s="3" t="inlineStr"/>
+      <c r="K288" s="3" t="inlineStr"/>
+      <c r="L288" s="3" t="inlineStr"/>
+      <c r="M288" s="7" t="inlineStr"/>
+      <c r="N288" s="7" t="inlineStr"/>
+      <c r="O288" s="8" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="inlineStr">
+        <is>
+          <t>Impedimentos do IBS</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I289" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J289" s="3" t="inlineStr"/>
+      <c r="K289" s="3" t="inlineStr"/>
+      <c r="L289" s="3" t="inlineStr"/>
+      <c r="M289" s="7" t="inlineStr"/>
+      <c r="N289" s="7" t="inlineStr"/>
+      <c r="O289" s="8" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D290" s="4" t="inlineStr">
+        <is>
+          <t>Registrar o pedido de IBS (protocolo)</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+        </is>
+      </c>
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I290" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J290" s="3" t="inlineStr"/>
+      <c r="K290" s="3" t="inlineStr"/>
+      <c r="L290" s="3" t="inlineStr"/>
+      <c r="M290" s="7" t="inlineStr"/>
+      <c r="N290" s="7" t="inlineStr"/>
+      <c r="O290" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O287"/>
+  <autoFilter ref="A1:O290"/>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M287" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
+    <dataValidation sqref="M2:M290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
       <formula1>"M0,M1,M2,Fora"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N287" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
+    <dataValidation sqref="N2:N290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15589,15 +15742,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId155"/>
@@ -15637,18 +15790,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId206"/>
@@ -15671,9 +15824,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F269" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId231"/>
@@ -15690,6 +15843,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId247"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15899,7 +16055,7 @@
         <v>7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>1</v>
@@ -15908,7 +16064,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -16438,7 +16594,7 @@
         <v>113</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>35</v>
@@ -16447,7 +16603,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -17733,7 +17889,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>v2.7.1</t>
+          <t>v2.8</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17913,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Mapa de Funcionalidades v2.7</t>
+          <t>Mapa de Funcionalidades v2.8</t>
         </is>
       </c>
     </row>
@@ -17769,7 +17925,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>286 funcionalidades · 21 módulos · 277 do mapa + 9 novas</t>
+          <t>289 funcionalidades · 21 módulos · 280 do mapa + 9 novas</t>
         </is>
       </c>
     </row>
@@ -17781,7 +17937,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>113 · 136 · 35 · 2</t>
+          <t>113 · 139 · 35 · 2</t>
         </is>
       </c>
     </row>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Como revisar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$296</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revisões'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O294"/>
+  <dimension ref="A1:O296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2139,9 +2139,9 @@
           <t>Risco/Inc.</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2190,9 +2190,9 @@
           <t>Listagem</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Um painel por tributo, com a partição, a conferência da soma, o prazo do art. 54 mais próximo e a última leitura do órgão.</t>
+          <t>Quadro CBS × IBS com os registros fiscais e as parcelas de cada tributo, a conferência da soma, o prazo do art. 54 mais próximo e a última leitura do órgão. O mesmo quadro serve ao detalhe do RF.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2241,9 +2241,9 @@
           <t>Listagem</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Razão do RF: cada movimento leva uma quantia de uma parcela para outra, com causa, fonte e vínculo. É a fonte da partição — a soma dos movimentos é o saldo de cada parcela.</t>
+          <t>Razão do RF: cada movimento leva uma quantia de uma parcela para outra, com causa, fonte e vínculo, numa trilha de auditoria filtrável. A soma dos movimentos é o saldo de cada parcela.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2292,9 +2292,9 @@
           <t>Listagem</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>Nova</t>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -14534,12 +14534,12 @@
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
-          <t>Usuário, e-mail, perfil, último acesso e situação, com o total de ativos, administradores, convites pendentes e inativos.</t>
-        </is>
-      </c>
-      <c r="F270" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Usuário, e-mail, perfil, último acesso e situação, com busca e filtro por perfil. Os indicadores contam ativos, administradores, convites pendentes e quem está sem acesso há 90 dias, candidato à revisão de acessos.</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>Administrador, Analista Fiscal, Controller e Auditor, cada um com o alcance declarado por módulo e a permissão de agir ou só ler.</t>
-        </is>
-      </c>
-      <c r="F271" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Um perfil por usuário, válido em toda a organização. Só o administrador troca o perfil, sempre com motivo, e ninguém altera o próprio.</t>
+        </is>
+      </c>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
-          <t>Convida por e-mail com o perfil já definido, e reenvia o convite que não foi aceito.</t>
-        </is>
-      </c>
-      <c r="F272" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Convida por e-mail com o perfil já definido. O convite vale 7 dias e, pelo link, a pessoa cria a própria senha no primeiro acesso; o vencido pode ser reenviado, com link novo, ou cancelado.</t>
+        </is>
+      </c>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -14687,12 +14687,12 @@
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>Corta o acesso sem apagar o usuário, preservando a trilha do que ele fez, e devolve o acesso quando necessário.</t>
-        </is>
-      </c>
-      <c r="F273" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Desativa sem apagar o usuário, com motivo, preservando a trilha do que ele fez, e reativa com o perfil anterior. O último administrador ativo não pode ser desativado.</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -14733,17 +14733,17 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Abas por situação do acesso</t>
+          <t>Filtro por situação do acesso</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
-          <t>Todos, ativos, pendentes e inativos, para achar rápido quem está sem acesso ou com convite parado.</t>
-        </is>
-      </c>
-      <c r="F274" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Ativo, convite pendente, convite vencido e inativo, para achar rápido quem está sem acesso ou com convite parado.</t>
+        </is>
+      </c>
+      <c r="F274" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>Administrador, Fiscal, Tesouraria, Leitura e Fornecedor. O perfil de Tesouraria é pressuposto pelo Ressarcimento e não existia no cadastro.</t>
+          <t>Administrador, Fiscal, Tesouraria, Leitura e Fornecedor, cada um com o que pode fazer, na tela de usuários e no próprio convite. O perfil de Tesouraria é pressuposto pelo Ressarcimento e não existia no cadastro.</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>PRD de Organização</t>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>Revogar sem encerrar a sessão deixa uma janela em que o acesso revogado continua valendo.</t>
+          <t>Desativar encerra as sessões abertas na hora, e o administrador também pode encerrá-las sem desativar. Sem isso, o acesso revogado continua valendo até a sessão expirar.</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>PRD de Organização</t>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -15033,27 +15033,27 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Saldo credor por período e tributo</t>
+          <t>Histórico do usuário</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
-          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
+          <t>Convite, aceite, troca de perfil, desativação, reativação e sessões encerradas, com autor, data e motivo. Responde quem deu ou tirou um acesso, e por quê.</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -15084,32 +15084,32 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Comparar compensar e ressarcir</t>
+          <t>Redefinição de senha pelo administrador</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
+          <t>Envia ao usuário um link de uso único para criar senha nova. O administrador nunca vê nem define a senha de outra pessoa.</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H281" s="3" t="inlineStr">
@@ -15117,9 +15117,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I281" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I281" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J281" s="3" t="inlineStr"/>
@@ -15145,22 +15145,22 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Declarar e cancelar a intenção</t>
+          <t>Saldo credor por período e tributo</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
-          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
+          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
+          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H282" s="3" t="inlineStr">
@@ -15196,22 +15196,22 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Montar o pedido de CBS por documento</t>
+          <t>Comparar compensar e ressarcir</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
+          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
+          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H283" s="3" t="inlineStr">
@@ -15219,9 +15219,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I283" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I283" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J283" s="3" t="inlineStr"/>
@@ -15247,17 +15247,17 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
+          <t>Declarar e cancelar a intenção</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
+          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
+          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -15298,22 +15298,22 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Listagem de pedidos do tributo</t>
+          <t>Montar o pedido de CBS por documento</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
+          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
+          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr">
@@ -15349,22 +15349,22 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Acompanhar análise e fiscalização</t>
+          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
+          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
+          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H286" s="3" t="inlineStr">
@@ -15400,22 +15400,22 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Registrar decisão e cancelamento</t>
+          <t>Listagem de pedidos do tributo</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
+          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
+          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
@@ -15451,22 +15451,22 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Conciliar o recebimento com Selic</t>
+          <t>Acompanhar análise e fiscalização</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
-          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
+          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
+          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H288" s="3" t="inlineStr">
@@ -15502,22 +15502,22 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Previsão de entrada de caixa por tributo</t>
+          <t>Registrar decisão e cancelamento</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
+          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
+          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H289" s="3" t="inlineStr">
@@ -15525,9 +15525,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I289" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I289" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J289" s="3" t="inlineStr"/>
@@ -15553,22 +15553,22 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Alertas de prazo do ressarcimento</t>
+          <t>Conciliar o recebimento com Selic</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
+          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
+          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H290" s="3" t="inlineStr">
@@ -15604,22 +15604,22 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Conferência do saldo com a Receita (CBS)</t>
+          <t>Previsão de entrada de caixa por tributo</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
+          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
+          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
@@ -15627,9 +15627,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I291" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I291" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J291" s="3" t="inlineStr"/>
@@ -15655,22 +15655,22 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Trilha de auditoria do pedido</t>
+          <t>Alertas de prazo do ressarcimento</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
-          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
+          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-13 Auditar</t>
+          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H292" s="3" t="inlineStr">
@@ -15706,17 +15706,17 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Impedimentos do IBS</t>
+          <t>Conferência do saldo com a Receita (CBS)</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
-          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
+          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
+          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -15757,22 +15757,22 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Registrar o pedido de IBS (protocolo)</t>
+          <t>Trilha de auditoria do pedido</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
-          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+          <t>PRD de Ressarcimento · F-13 Auditar</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H294" s="3" t="inlineStr">
@@ -15792,13 +15792,115 @@
       <c r="N294" s="7" t="inlineStr"/>
       <c r="O294" s="8" t="inlineStr"/>
     </row>
+    <row r="295">
+      <c r="A295" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>Impedimentos do IBS</t>
+        </is>
+      </c>
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
+        </is>
+      </c>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I295" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J295" s="3" t="inlineStr"/>
+      <c r="K295" s="3" t="inlineStr"/>
+      <c r="L295" s="3" t="inlineStr"/>
+      <c r="M295" s="7" t="inlineStr"/>
+      <c r="N295" s="7" t="inlineStr"/>
+      <c r="O295" s="8" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>Registrar o pedido de IBS (protocolo)</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+        </is>
+      </c>
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I296" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J296" s="3" t="inlineStr"/>
+      <c r="K296" s="3" t="inlineStr"/>
+      <c r="L296" s="3" t="inlineStr"/>
+      <c r="M296" s="7" t="inlineStr"/>
+      <c r="N296" s="7" t="inlineStr"/>
+      <c r="O296" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O294"/>
+  <autoFilter ref="A1:O296"/>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
+    <dataValidation sqref="M2:M296" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
       <formula1>"M0,M1,M2,Fora"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
+    <dataValidation sqref="N2:N296" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16035,25 +16137,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId258"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16180,7 +16289,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>O módulo que a tese defende entra quase inteiro: 11 de 14. Ficam fora três gráficos analíticos — eles explicam o crédito, não o garantem. O Top 5 e Top 10 de fornecedores subiu na revisão de 15/09: saber de quem cobrar primeiro é operação, não análise. O painel Ressarcimento no ciclo do crédito entra em M1 (D17): o M0 do módulo não muda.</t>
+          <t>O módulo que a tese defende entra quase inteiro: 11 de 14. Ficam fora três gráficos analíticos — eles explicam o crédito, não o garantem. O Top 5 e Top 10 de fornecedores subiu na revisão de 15/09: saber de quem cobrar primeiro é operação, não análise. O painel Ressarcimento no ciclo do crédito entra em M1 (D17): o M0 do módulo não muda. A parcialidade (D19) passou ao mapa em 26/10, com o protótipo incorporado ao master: partição por tributo, selo por tributo, detalhe com as duas partições e histórico de movimentos, as quatro em M0.</t>
         </is>
       </c>
     </row>
@@ -16743,7 +16852,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>1</v>
@@ -16752,11 +16861,11 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Multiusuário interno é consequência de adoção. A exceção é o painel de acessos externos, que entrou no M0 junto com o acesso do fornecedor — e foi confirmado na revisão de 15/09.</t>
+          <t>Multiusuário interno é consequência de adoção. A exceção é o painel de acessos externos, que entrou no M0 junto com o acesso do fornecedor — e foi confirmado na revisão de 15/09. A gestão de usuários implementada em 26/10 trouxe o histórico do usuário e a redefinição de senha pelo administrador, as duas em M1 com o resto do módulo. O que a autenticação muda no M0 está na D20, em aberto.</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16911,7 @@
         <v>117</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>35</v>
@@ -16811,7 +16920,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -18097,7 +18206,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>v2.9</t>
+          <t>v2.10</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18218,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18230,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Mapa de Funcionalidades v2.8</t>
+          <t>Mapa de Funcionalidades v2.9</t>
         </is>
       </c>
     </row>
@@ -18133,7 +18242,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>293 funcionalidades · 21 módulos · 280 do mapa + 13 novas</t>
+          <t>295 funcionalidades · 21 módulos · 286 do mapa + 9 novas</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18254,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>117 · 139 · 35 · 2</t>
+          <t>117 · 141 · 35 · 2</t>
         </is>
       </c>
     </row>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Como revisar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$297</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revisões'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O296"/>
+  <dimension ref="A1:O297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Após login, o usuário seleciona o perfil: Cliente (adquirente — acesso completo a todos os módulos) ou Fornecedor (acesso restrito ao portal com dados filtrados pelo CNPJ do fornecedor).</t>
-        </is>
-      </c>
-      <c r="F164" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Duas portas de entrada: quem é da organização entra com um dos quatro perfis internos, e o fornecedor entra no portal, restrito aos CNPJs do próprio acesso. O perfil vem do acesso de quem entrou, não de uma escolha na tela.</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -9110,12 +9110,12 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Troca de perfil in-session</t>
+          <t>Tokens CSS globais + PALETTE JS</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Card do usuário no header e modal de configurações permitem alternar de perfil durante a sessão sem necessidade de novo login.</t>
+          <t>Todas as cores da interface definidas como variáveis CSS (--teal, --blue, --red etc.) e objeto PALETTE no JS. Nenhum valor hexadecimal inline no código — consistência visual garantida centralmente.</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Tokens CSS globais + PALETTE JS</t>
+          <t>Sidebar teal colapsável + localStorage</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Todas as cores da interface definidas como variáveis CSS (--teal, --blue, --red etc.) e objeto PALETTE no JS. Nenhum valor hexadecimal inline no código — consistência visual garantida centralmente.</t>
+          <t>Toggle de 56px com transição CSS suave entre expandida (labels visíveis) e colapsada (ícones com tooltips). Estado persistido em localStorage — mantido entre sessões e recarregamentos.</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Sidebar teal colapsável + localStorage</t>
+          <t>Tema claro/escuro automático</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Toggle de 56px com transição CSS suave entre expandida (labels visíveis) e colapsada (ícones com tooltips). Estado persistido em localStorage — mantido entre sessões e recarregamentos.</t>
+          <t>prefers-color-scheme detecta o tema do sistema operacional e aplica automaticamente. Override manual disponível via atributo data-theme. Tokens redefinidos para cada tema sem hardcode de cores.</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Tema claro/escuro automático</t>
+          <t>shBuildFilterPanel — filtros padronizados</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>prefers-color-scheme detecta o tema do sistema operacional e aplica automaticamente. Override manual disponível via atributo data-theme. Tokens redefinidos para cada tema sem hardcode de cores.</t>
+          <t>Função geradora de painéis de filtro colapsáveis com design unificado (classe sh-fp). Aplicada em Créditos, Débitos, Pagamentos, Inconsistências, Contratos, Fornecedores, Organização e Portal Fornecedor.</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>shBuildFilterPanel — filtros padronizados</t>
+          <t>RF Core — 10 colunas uniformes</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Função geradora de painéis de filtro colapsáveis com design unificado (classe sh-fp). Aplicada em Créditos, Débitos, Pagamentos, Inconsistências, Contratos, Fornecedores, Organização e Portal Fornecedor.</t>
+          <t>Conjunto padronizado de colunas presente em todas as listagens de RF do sistema: ID RF, Tipo Fiscal, DF Vinculado, Entidade, Data, Valor, Status do Crédito, Status de Registro, Método de Pagamento e Extinção. Filtros obrigatórios em todas as colunas.</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>RF Core — 10 colunas uniformes</t>
+          <t>ESC fecha qualquer modal</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Conjunto padronizado de colunas presente em todas as listagens de RF do sistema: ID RF, Tipo Fiscal, DF Vinculado, Entidade, Data, Valor, Status do Crédito, Status de Registro, Método de Pagamento e Extinção. Filtros obrigatórios em todas as colunas.</t>
+          <t>Atalho de teclado global — qualquer overlay aberto no sistema (modais de detalhe NF, RF, inconsistência, fornecedor, contrato) responde ao ESC e fecha sem ação adicional do usuário.</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>ESC fecha qualquer modal</t>
+          <t>Tooltip de coluna como padrão de projeto</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Atalho de teclado global — qualquer overlay aberto no sistema (modais de detalhe NF, RF, inconsistência, fornecedor, contrato) responde ao ESC e fecha sem ação adicional do usuário.</t>
+          <t>Toda coluna declarada no catálogo de tabelas ganha explicação no cabeçalho, aplicada sempre do mesmo jeito. 104 colunas documentadas nas nove listagens; coluna nova só é publicada se souber se explicar.</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
@@ -9439,9 +9439,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>Fora</t>
         </is>
       </c>
       <c r="J171" s="3" t="inlineStr"/>
@@ -9467,12 +9467,12 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Tooltip de coluna como padrão de projeto</t>
+          <t>Documentação de produto dentro da aplicação</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Toda coluna declarada no catálogo de tabelas ganha explicação no cabeçalho, aplicada sempre do mesmo jeito. 104 colunas documentadas nas nove listagens; coluna nova só é publicada se souber se explicar.</t>
+          <t>Hub de PRDs, mapa de funcionalidades e changelog acessíveis pela própria aplicação, sem depender de link externo. Quem opera e quem especifica leem a mesma versão.</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
@@ -9518,17 +9518,17 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Documentação de produto dentro da aplicação</t>
+          <t>Rotas diretas para telas e abas</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Hub de PRDs, mapa de funcionalidades e changelog acessíveis pela própria aplicação, sem depender de link externo. Quem opera e quem especifica leem a mesma versão.</t>
-        </is>
-      </c>
-      <c r="F173" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Endereços próprios para cada tela e aba, de forma que um link leve direto ao ponto certo da aplicação — usado em documentação, no hub de PRDs e no compartilhamento entre pessoas.</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Início · Seção 01 Contexto e posicionamento</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -9541,9 +9541,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>Fora</t>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J173" s="3" t="inlineStr"/>
@@ -9569,17 +9569,17 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Rotas diretas para telas e abas</t>
+          <t>Contador de filtros ativos sempre visível</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Endereços próprios para cada tela e aba, de forma que um link leve direto ao ponto certo da aplicação — usado em documentação, no hub de PRDs e no compartilhamento entre pessoas.</t>
+          <t>Número filtrado nunca se confunde com total. Um indicador sob filtro, sem sinal de filtro, é erro de leitura esperando acontecer.</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>PRD de Início · Seção 01 Contexto e posicionamento</t>
+          <t>PRD de Arcabouço de interface · Seção 02 Painel de filtros</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Contador de filtros ativos sempre visível</t>
+          <t>Filtro aplicado só sob confirmação</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Número filtrado nunca se confunde com total. Um indicador sob filtro, sem sinal de filtro, é erro de leitura esperando acontecer.</t>
+          <t>O recorte inteiro é montado antes de a listagem ser refeita, em vez de recarregar a cada campo alterado.</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
@@ -9643,9 +9643,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I175" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J175" s="3" t="inlineStr"/>
@@ -9671,17 +9671,17 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Filtro aplicado só sob confirmação</t>
+          <t>Paginação com retorno à primeira página</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>O recorte inteiro é montado antes de a listagem ser refeita, em vez de recarregar a cada campo alterado.</t>
+          <t>Mudar o recorte devolve a listagem ao início, para não mostrar a página 5 de um conjunto que acabou de mudar.</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>PRD de Arcabouço de interface · Seção 02 Painel de filtros</t>
+          <t>PRD de Arcabouço de interface · Seção 03 Pagina&amp;ccedil;&amp;atilde;o e busca</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Paginação com retorno à primeira página</t>
+          <t>Alcance da busca declarado por módulo</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Mudar o recorte devolve a listagem ao início, para não mostrar a página 5 de um conjunto que acabou de mudar.</t>
+          <t>Cada módulo diz quais identificadores a própria busca encontra. Sem essa declaração, ninguém nota o que a busca deixou de fora.</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
@@ -9745,9 +9745,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I177" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I177" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J177" s="3" t="inlineStr"/>
@@ -9773,17 +9773,17 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Alcance da busca declarado por módulo</t>
+          <t>Gerenciador de colunas com persistência por usuário</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Cada módulo diz quais identificadores a própria busca encontra. Sem essa declaração, ninguém nota o que a busca deixou de fora.</t>
+          <t>Seleção, ordem e restauração do padrão, por listagem e por usuário, valendo também para a exportação.</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>PRD de Arcabouço de interface · Seção 03 Pagina&amp;ccedil;&amp;atilde;o e busca</t>
+          <t>PRD de Arcabouço de interface · Seção 04 Gerenciador de colunas</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -9796,9 +9796,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I178" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J178" s="3" t="inlineStr"/>
@@ -9824,32 +9824,32 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Gerenciador de colunas com persistência por usuário</t>
+          <t>Login próprio por e-mail e senha</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Seleção, ordem e restauração do padrão, por listagem e por usuário, valendo também para a exportação.</t>
+          <t>E-mail e senha da própria pessoa, em provedor de identidade gerenciado, com convite, primeiro acesso, recuperação de senha, sessão de 30 minutos sem uso e trilha de entrada. Não existe no produto: hoje o acesso é uma senha no código. Entrou no MVP pela D20, no lugar do SSO.</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>PRD de Arcabouço de interface · Seção 04 Gerenciador de colunas</t>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="H179" s="3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="I179" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H179" s="11" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
         </is>
       </c>
       <c r="J179" s="3" t="inlineStr"/>
@@ -9880,12 +9880,12 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Entrada pelo provedor de identidade da empresa (SAML 2.0 ou OIDC), com provisionamento e revogação vindos de lá. Não existe no produto: hoje o acesso é uma senha no código.</t>
-        </is>
-      </c>
-      <c r="F180" s="12" t="inlineStr">
-        <is>
-          <t>Sem PRD</t>
+          <t>Entrada pelo provedor de identidade da empresa (SAML 2.0 ou OIDC), com provisionamento e revogação vindos de lá pelo SCIM. Fase 2 da gestão de usuários (D-USR-08); desceu do M0 pela D20.</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -9898,9 +9898,9 @@
           <t>Nova</t>
         </is>
       </c>
-      <c r="I180" s="6" t="inlineStr">
-        <is>
-          <t>M0</t>
+      <c r="I180" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J180" s="3" t="inlineStr"/>
@@ -15135,32 +15135,32 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>Ressarcimento</t>
+          <t>Usuários e Acessos</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Saldo credor por período e tributo</t>
+          <t>Escopo por CNPJ do usuário</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
-          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
+          <t>Cada usuário vê toda a organização ou só os CNPJs selecionados, e o Administrador vê sempre tudo. A troca é do administrador, com motivo, e fica na trilha. Quem tem só parte de uma empresa não vê a apuração nem o saldo dela, que são da empresa inteira. No protótipo o escopo é atribuído e registrado; o recorte das telas vem com o login de verdade.</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
+          <t>PRD de Organização · Seção 15 Usu&amp;aacute;rios e acessos</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H282" s="3" t="inlineStr">
@@ -15196,22 +15196,22 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Comparar compensar e ressarcir</t>
+          <t>Saldo credor por período e tributo</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
+          <t>Por período e por tributo, na matriz: saldo inicial, apropriado, compensado, saldo credor, o que saiu para ressarcimento e o transportado. É a base da decisão de compensar ou pedir o dinheiro.</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
+          <t>PRD de Ressarcimento · F-01 Ver o saldo credor do tributo</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H283" s="3" t="inlineStr">
@@ -15219,9 +15219,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I283" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I283" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J283" s="3" t="inlineStr"/>
@@ -15247,22 +15247,22 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Declarar e cancelar a intenção</t>
+          <t>Comparar compensar e ressarcir</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
+          <t>Para o período em curso, as duas hipóteses lado a lado: uso do saldo, quando o dinheiro volta e a correção estimada pela Selic.</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
+          <t>PRD de Ressarcimento · F-02 Comparar compensar e ressarcir</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H284" s="3" t="inlineStr">
@@ -15270,9 +15270,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I284" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I284" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J284" s="3" t="inlineStr"/>
@@ -15298,17 +15298,17 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Montar o pedido de CBS por documento</t>
+          <t>Declarar e cancelar a intenção</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
+          <t>Intenção do tributo até o último dia útil do período, com o efeito mostrado antes e aprovação acima do limite. Reserva o saldo; cancelada ou vencida, o saldo volta a compensar.</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
+          <t>PRD de Ressarcimento · F-03 Declarar e cancelar a intenção</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -15349,17 +15349,17 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
+          <t>Montar o pedido de CBS por documento</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
+          <t>Escolhe os documentos do saldo reservado que entram no pedido. O que fica de fora volta a compensar desde a data do pedido.</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
+          <t>PRD de Ressarcimento · F-04 Montar o pedido de CBS</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -15400,22 +15400,22 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Listagem de pedidos do tributo</t>
+          <t>Registrar o pedido de CBS (PER/DCOMP)</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
+          <t>Número do PER/DCOMP e data de transmissão. Calcula o fim da análise e a data do pagamento por silêncio do Fisco.</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
+          <t>PRD de Ressarcimento · F-05 Registrar o pedido de CBS</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
@@ -15451,22 +15451,22 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Acompanhar análise e fiscalização</t>
+          <t>Listagem de pedidos do tributo</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
-          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
+          <t>Pedidos com identificador no órgão, valor, prazo, contagem regressiva, situação e valor deferido.</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
+          <t>PRD de Ressarcimento · F-06 Listar os pedidos do tributo</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H288" s="3" t="inlineStr">
@@ -15502,22 +15502,22 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Registrar decisão e cancelamento</t>
+          <t>Acompanhar análise e fiscalização</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
+          <t>Fiscalização suspende o prazo e tem limite de 360 dias. Mostra quando o prazo do Fisco se esgota sem manifestação.</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
+          <t>PRD de Ressarcimento · F-07 Acompanhar análise, exigência e fiscalização</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H289" s="3" t="inlineStr">
@@ -15553,17 +15553,17 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Conciliar o recebimento com Selic</t>
+          <t>Registrar decisão e cancelamento</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
+          <t>Deferido, deferido parcial, indeferido ou cancelado, cada um devolvendo o remanescente à compensação a partir da data que a norma define.</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
+          <t>PRD de Ressarcimento · F-08 Registrar a decisão e o cancelamento</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -15604,22 +15604,22 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Previsão de entrada de caixa por tributo</t>
+          <t>Conciliar o recebimento com Selic</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
+          <t>Recebido contra deferido corrigido. Extingue os créditos do pedido com o método Ressarcimento, e só aqui o status do crédito muda.</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
+          <t>PRD de Ressarcimento · F-09 Conciliar o recebimento</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>Analítico</t>
+          <t>Ação</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
@@ -15627,9 +15627,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I291" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
+      <c r="I291" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
         </is>
       </c>
       <c r="J291" s="3" t="inlineStr"/>
@@ -15655,22 +15655,22 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Alertas de prazo do ressarcimento</t>
+          <t>Previsão de entrada de caixa por tributo</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
-          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
+          <t>Deferidos e em análise, datados pelo prazo legal, com correção estimada. Uma previsão para CBS e outra para IBS.</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
+          <t>PRD de Ressarcimento · F-10 Prever a entrada de caixa do tributo</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>Configuração</t>
+          <t>Analítico</t>
         </is>
       </c>
       <c r="H292" s="3" t="inlineStr">
@@ -15678,9 +15678,9 @@
           <t>Mapa</t>
         </is>
       </c>
-      <c r="I292" s="10" t="inlineStr">
-        <is>
-          <t>M1</t>
+      <c r="I292" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
         </is>
       </c>
       <c r="J292" s="3" t="inlineStr"/>
@@ -15706,22 +15706,22 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Conferência do saldo com a Receita (CBS)</t>
+          <t>Alertas de prazo do ressarcimento</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
-          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
+          <t>Intenção, pedido, fim da análise e pagamento por silêncio, por tributo, na tela e como eventos da régua de Automações.</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
+          <t>PRD de Ressarcimento · F-11 Alertar os prazos do tributo</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Configuração</t>
         </is>
       </c>
       <c r="H293" s="3" t="inlineStr">
@@ -15757,22 +15757,22 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Trilha de auditoria do pedido</t>
+          <t>Conferência do saldo com a Receita (CBS)</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
-          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
+          <t>Documento com saldo divergente na API de créditos da CBS sai do pedido e abre inconsistência. Evita pedir o que a Receita não reconhece.</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-13 Auditar</t>
+          <t>PRD de Ressarcimento · F-12 Conferir com a Receita</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>Listagem</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H294" s="3" t="inlineStr">
@@ -15808,22 +15808,22 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Impedimentos do IBS</t>
+          <t>Trilha de auditoria do pedido</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
+          <t>Quem declarou, aprovou, cancelou, registrou e decidiu, com data e valor, na linha do tempo de cada pedido.</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
+          <t>PRD de Ressarcimento · F-13 Auditar</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>Risco/Inc.</t>
+          <t>Listagem</t>
         </is>
       </c>
       <c r="H295" s="3" t="inlineStr">
@@ -15859,22 +15859,22 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Registrar o pedido de IBS (protocolo)</t>
+          <t>Impedimentos do IBS</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
-          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+          <t>Auto de infração, cadastro irregular, notificação pendente ou débito exigível podem levar ao indeferimento do pedido de IBS. Aparece como alerta antes da intenção e do pedido.</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+          <t>PRD de Ressarcimento · F-14 Verificar impedimentos do IBS</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>Ação</t>
+          <t>Risco/Inc.</t>
         </is>
       </c>
       <c r="H296" s="3" t="inlineStr">
@@ -15894,13 +15894,64 @@
       <c r="N296" s="7" t="inlineStr"/>
       <c r="O296" s="8" t="inlineStr"/>
     </row>
+    <row r="297">
+      <c r="A297" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>Ressarcimento</t>
+        </is>
+      </c>
+      <c r="D297" s="4" t="inlineStr">
+        <is>
+          <t>Registrar o pedido de IBS (protocolo)</t>
+        </is>
+      </c>
+      <c r="E297" s="4" t="inlineStr">
+        <is>
+          <t>Protocolo emitido pelo Comitê Gestor, data e valor. Acompanha o canal que o Comitê vier a definir.</t>
+        </is>
+      </c>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>PRD de Ressarcimento · F-15 Registrar o pedido de IBS</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I297" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J297" s="3" t="inlineStr"/>
+      <c r="K297" s="3" t="inlineStr"/>
+      <c r="L297" s="3" t="inlineStr"/>
+      <c r="M297" s="7" t="inlineStr"/>
+      <c r="N297" s="7" t="inlineStr"/>
+      <c r="O297" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O296"/>
+  <autoFilter ref="A1:O297"/>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M296" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
+    <dataValidation sqref="M2:M297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
       <formula1>"M0,M1,M2,Fora"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N296" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
+    <dataValidation sqref="N2:N297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16055,114 +16106,118 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F267" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F270" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F271" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F272" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F273" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F274" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F276" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F277" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F278" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F279" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F280" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F281" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F282" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F283" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F284" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F285" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F286" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F287" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F288" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F289" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F290" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F291" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F292" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId262"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16625,10 +16680,10 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>3</v>
@@ -16641,7 +16696,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Login, perfis e o sistema de design, mais o selo de modo demonstração da troca de perfil. O SSO corporativo continua sendo a única funcionalidade do MVP que não existe em parte alguma.</t>
+          <t>Login, perfis e o sistema de design. Pela D20, de 26/10, o MVP entra com o login próprio por e-mail e senha, que ainda não existe, e o SSO corporativo desce a M1, para a fase 2 com o SCIM. A troca de perfil saiu do inventário: é só do protótipo (D-USR-06).</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16907,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>1</v>
@@ -16861,11 +16916,11 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Multiusuário interno é consequência de adoção. A exceção é o painel de acessos externos, que entrou no M0 junto com o acesso do fornecedor — e foi confirmado na revisão de 15/09. A gestão de usuários implementada em 26/10 trouxe o histórico do usuário e a redefinição de senha pelo administrador, as duas em M1 com o resto do módulo. O que a autenticação muda no M0 está na D20, em aberto.</t>
+          <t>Multiusuário interno é consequência de adoção. A exceção é o painel de acessos externos, que entrou no M0 junto com o acesso do fornecedor — e foi confirmado na revisão de 15/09. A gestão de usuários implementada em 26/10 trouxe o histórico do usuário e a redefinição de senha pelo administrador, as duas em M1 com o resto do módulo. O escopo por CNPJ (D-USR-05) também entra em M1, pelo critério: é multiusuário, e a cadeia do crédito fecha sem ele. O que a autenticação muda no M0 está na D20.</t>
         </is>
       </c>
     </row>
@@ -16908,10 +16963,10 @@
         </is>
       </c>
       <c r="C24" s="15" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>35</v>
@@ -16920,7 +16975,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -18206,7 +18261,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>v2.10</t>
+          <t>v2.11</t>
         </is>
       </c>
     </row>
@@ -18230,7 +18285,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Mapa de Funcionalidades v2.9</t>
+          <t>Mapa de Funcionalidades v2.10</t>
         </is>
       </c>
     </row>
@@ -18242,7 +18297,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>295 funcionalidades · 21 módulos · 286 do mapa + 9 novas</t>
+          <t>296 funcionalidades · 21 módulos · 286 do mapa + 10 novas</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18309,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>117 · 141 · 35 · 2</t>
+          <t>116 · 143 · 35 · 2</t>
         </is>
       </c>
     </row>

--- a/src/docs/priorizacao-mvp.xlsx
+++ b/src/docs/priorizacao-mvp.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Como revisar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Priorização'!$A$1:$O$317</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revisões'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O297"/>
+  <dimension ref="A1:O317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15945,13 +15945,1033 @@
       <c r="N297" s="7" t="inlineStr"/>
       <c r="O297" s="8" t="inlineStr"/>
     </row>
+    <row r="298">
+      <c r="A298" s="3" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>Empresa do grupo econômico</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>Escolhe a empresa pelo CNPJ raiz, com a matriz que centraliza o recolhimento; competências, saldos, divergências, guias e histórico passam a ser dela.</t>
+        </is>
+      </c>
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-01 Escolher a empresa do grupo</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>Configuração</t>
+        </is>
+      </c>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I298" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J298" s="3" t="inlineStr"/>
+      <c r="K298" s="3" t="inlineStr"/>
+      <c r="L298" s="3" t="inlineStr"/>
+      <c r="M298" s="7" t="inlineStr"/>
+      <c r="N298" s="7" t="inlineStr"/>
+      <c r="O298" s="8" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
+        <is>
+          <t>Competências com a etapa e o prazo do ente</t>
+        </is>
+      </c>
+      <c r="E299" s="4" t="inlineStr">
+        <is>
+          <t>Carrossel do exercício com a etapa de cada tributo na Receita Federal e no Comitê Gestor — em apuração, entrega, ajustes, vencimento — e os dias até o prazo.</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-02 Competências com a etapa e o prazo</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I299" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J299" s="3" t="inlineStr"/>
+      <c r="K299" s="3" t="inlineStr"/>
+      <c r="L299" s="3" t="inlineStr"/>
+      <c r="M299" s="7" t="inlineStr"/>
+      <c r="N299" s="7" t="inlineStr"/>
+      <c r="O299" s="8" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>Visão consolidada sem somar tributos</t>
+        </is>
+      </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>CBS e IBS lado a lado: saldo do SplitHub, saldo do ente, diferença, divergências e guia. Os saldos dos dois tributos nunca se somam.</t>
+        </is>
+      </c>
+      <c r="F300" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-03 Visão consolidada da competência</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I300" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J300" s="3" t="inlineStr"/>
+      <c r="K300" s="3" t="inlineStr"/>
+      <c r="L300" s="3" t="inlineStr"/>
+      <c r="M300" s="7" t="inlineStr"/>
+      <c r="N300" s="7" t="inlineStr"/>
+      <c r="O300" s="8" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>Desembolso da competência</t>
+        </is>
+      </c>
+      <c r="E301" s="4" t="inlineStr">
+        <is>
+          <t>As duas guias do mês e o total de caixa, com os entes nomeados. É a visão da tesouraria; não é saldo e não entra em apuração.</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-04 Desembolso da competência</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I301" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J301" s="3" t="inlineStr"/>
+      <c r="K301" s="3" t="inlineStr"/>
+      <c r="L301" s="3" t="inlineStr"/>
+      <c r="M301" s="7" t="inlineStr"/>
+      <c r="N301" s="7" t="inlineStr"/>
+      <c r="O301" s="8" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>Demonstrativo SplitHub × ente</t>
+        </is>
+      </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>As linhas do art. 44 com três colunas — SplitHub, ente e diferença —, o resultado antes do PCONT, o saldo atualizado e os créditos a apropriar.</t>
+        </is>
+      </c>
+      <c r="F302" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-05 Demonstrativo SplitHub × ente</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I302" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J302" s="3" t="inlineStr"/>
+      <c r="K302" s="3" t="inlineStr"/>
+      <c r="L302" s="3" t="inlineStr"/>
+      <c r="M302" s="7" t="inlineStr"/>
+      <c r="N302" s="7" t="inlineStr"/>
+      <c r="O302" s="8" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>Detalhamento até o conta corrente da operação</t>
+        </is>
+      </c>
+      <c r="E303" s="4" t="inlineStr">
+        <is>
+          <t>Linha, origem, documento por contraparte e o conta corrente da nota no SplitHub ao lado do ente, com busca, filtro de divergência e CSV.</t>
+        </is>
+      </c>
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-06 Detalhamento até a nota</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I303" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J303" s="3" t="inlineStr"/>
+      <c r="K303" s="3" t="inlineStr"/>
+      <c r="L303" s="3" t="inlineStr"/>
+      <c r="M303" s="7" t="inlineStr"/>
+      <c r="N303" s="7" t="inlineStr"/>
+      <c r="O303" s="8" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr">
+        <is>
+          <t>Recalcular, fechar e reabrir por tributo</t>
+        </is>
+      </c>
+      <c r="E304" s="4" t="inlineStr">
+        <is>
+          <t>O ciclo que era da tela da Apuração IBS/CBS, agora por tributo: recalcular a partir dos documentos, fechar com justificativa quando há divergência e reabrir.</t>
+        </is>
+      </c>
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-07 Recalcular, fechar e reabrir</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I304" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J304" s="3" t="inlineStr"/>
+      <c r="K304" s="3" t="inlineStr"/>
+      <c r="L304" s="3" t="inlineStr"/>
+      <c r="M304" s="7" t="inlineStr"/>
+      <c r="N304" s="7" t="inlineStr"/>
+      <c r="O304" s="8" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="inlineStr">
+        <is>
+          <t>Linha do tempo da competência por ente</t>
+        </is>
+      </c>
+      <c r="E305" s="4" t="inlineStr">
+        <is>
+          <t>Trilhos da Receita Federal e do Comitê Gestor e as etapas E1 a E8, da apuração do mês à extinção, com o que aconteceu em cada uma.</t>
+        </is>
+      </c>
+      <c r="F305" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-08 Linha do tempo por ente</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I305" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J305" s="3" t="inlineStr"/>
+      <c r="K305" s="3" t="inlineStr"/>
+      <c r="L305" s="3" t="inlineStr"/>
+      <c r="M305" s="7" t="inlineStr"/>
+      <c r="N305" s="7" t="inlineStr"/>
+      <c r="O305" s="8" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>Divergências por tributo e natureza, com chamado</t>
+        </is>
+      </c>
+      <c r="E306" s="4" t="inlineStr">
+        <is>
+          <t>Toda diferença num documento abre chamado sozinha. Lista com valores, efeito no saldo do ente e tipo do catálogo, filtrada por tributo e por crédito ou débito.</t>
+        </is>
+      </c>
+      <c r="F306" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-09 Divergências por tributo e natureza</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>Risco/Inc.</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I306" s="6" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J306" s="3" t="inlineStr"/>
+      <c r="K306" s="3" t="inlineStr"/>
+      <c r="L306" s="3" t="inlineStr"/>
+      <c r="M306" s="7" t="inlineStr"/>
+      <c r="N306" s="7" t="inlineStr"/>
+      <c r="O306" s="8" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>Decisão registrada por divergência</t>
+        </is>
+      </c>
+      <c r="E307" s="4" t="inlineStr">
+        <is>
+          <t>Aguardar o reflexo, aceitar, ajustar no portal, importar ou corrigir, com quem e quando. O ajuste entra no valor sugerido da guia; emitir sem decidir pede justificativa.</t>
+        </is>
+      </c>
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-10 Decisão por divergência</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I307" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J307" s="3" t="inlineStr"/>
+      <c r="K307" s="3" t="inlineStr"/>
+      <c r="L307" s="3" t="inlineStr"/>
+      <c r="M307" s="7" t="inlineStr"/>
+      <c r="N307" s="7" t="inlineStr"/>
+      <c r="O307" s="8" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>Emissão do DARF da CBS</t>
+        </is>
+      </c>
+      <c r="E308" s="4" t="inlineStr">
+        <is>
+          <t>Guia do saldo pela Receita Federal, no valor do ente após os ajustes, do SplitHub ou outro. A emissão por API foi anunciada pela Receita, ainda sem documentação.</t>
+        </is>
+      </c>
+      <c r="F308" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-11 Emitir o DARF da CBS</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I308" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J308" s="3" t="inlineStr"/>
+      <c r="K308" s="3" t="inlineStr"/>
+      <c r="L308" s="3" t="inlineStr"/>
+      <c r="M308" s="7" t="inlineStr"/>
+      <c r="N308" s="7" t="inlineStr"/>
+      <c r="O308" s="8" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="inlineStr">
+        <is>
+          <t>Guia do IBS registrada do portal</t>
+        </is>
+      </c>
+      <c r="E309" s="4" t="inlineStr">
+        <is>
+          <t>Enquanto o Comitê Gestor não emite por API, a guia do portal entra com linha digitável, valor e PDF, e o resto do fluxo funciona igual.</t>
+        </is>
+      </c>
+      <c r="F309" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-12 Registrar a guia do IBS do portal</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I309" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J309" s="3" t="inlineStr"/>
+      <c r="K309" s="3" t="inlineStr"/>
+      <c r="L309" s="3" t="inlineStr"/>
+      <c r="M309" s="7" t="inlineStr"/>
+      <c r="N309" s="7" t="inlineStr"/>
+      <c r="O309" s="8" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="inlineStr">
+        <is>
+          <t>Simulação de pagamento parcial</t>
+        </is>
+      </c>
+      <c r="E310" s="4" t="inlineStr">
+        <is>
+          <t>Quantas notas um valor extingue na ordem cronológica e quais clientes ficam sem crédito. Explica o efeito de pagar menos antes de pagar.</t>
+        </is>
+      </c>
+      <c r="F310" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-13 Simular o pagamento parcial</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I310" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J310" s="3" t="inlineStr"/>
+      <c r="K310" s="3" t="inlineStr"/>
+      <c r="L310" s="3" t="inlineStr"/>
+      <c r="M310" s="7" t="inlineStr"/>
+      <c r="N310" s="7" t="inlineStr"/>
+      <c r="O310" s="8" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr">
+        <is>
+          <t>Envio ao ERP e comprovante de volta</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="inlineStr">
+        <is>
+          <t>pcont.guide_issued leva a guia, a apuração do mês e a decomposição; o comprovante volta por POST /v1/pcont/proofs.</t>
+        </is>
+      </c>
+      <c r="F311" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-14 Enviar ao ERP e receber o comprovante</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I311" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J311" s="3" t="inlineStr"/>
+      <c r="K311" s="3" t="inlineStr"/>
+      <c r="L311" s="3" t="inlineStr"/>
+      <c r="M311" s="7" t="inlineStr"/>
+      <c r="N311" s="7" t="inlineStr"/>
+      <c r="O311" s="8" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="inlineStr">
+        <is>
+          <t>Acompanhamento até a extinção</t>
+        </is>
+      </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>Processamento pelo ente com as notas extintas e os clientes liberados; cancelar, substituir quando o saldo muda e emitir a guia do restante.</t>
+        </is>
+      </c>
+      <c r="F312" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-15 Acompanhar até a extinção</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I312" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J312" s="3" t="inlineStr"/>
+      <c r="K312" s="3" t="inlineStr"/>
+      <c r="L312" s="3" t="inlineStr"/>
+      <c r="M312" s="7" t="inlineStr"/>
+      <c r="N312" s="7" t="inlineStr"/>
+      <c r="O312" s="8" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>Encargos simulados de atraso</t>
+        </is>
+      </c>
+      <c r="E313" s="4" t="inlineStr">
+        <is>
+          <t>Multa e juros quando a guia passa do vencimento sem pagamento, simulados como no RAD.</t>
+        </is>
+      </c>
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-16 Encargos simulados de atraso</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H313" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I313" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J313" s="3" t="inlineStr"/>
+      <c r="K313" s="3" t="inlineStr"/>
+      <c r="L313" s="3" t="inlineStr"/>
+      <c r="M313" s="7" t="inlineStr"/>
+      <c r="N313" s="7" t="inlineStr"/>
+      <c r="O313" s="8" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>Histórico com retrato do demonstrativo</t>
+        </is>
+      </c>
+      <c r="E314" s="4" t="inlineStr">
+        <is>
+          <t>Guias por tributo e competência, com a linha do tempo e o demonstrativo congelado na emissão, mesmo que o ente mude depois.</t>
+        </is>
+      </c>
+      <c r="F314" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-17 Histórico com retrato</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I314" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J314" s="3" t="inlineStr"/>
+      <c r="K314" s="3" t="inlineStr"/>
+      <c r="L314" s="3" t="inlineStr"/>
+      <c r="M314" s="7" t="inlineStr"/>
+      <c r="N314" s="7" t="inlineStr"/>
+      <c r="O314" s="8" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>Exportação do demonstrativo</t>
+        </is>
+      </c>
+      <c r="E315" s="4" t="inlineStr">
+        <is>
+          <t>CSV do tributo ou da competência, e do detalhamento por documento.</t>
+        </is>
+      </c>
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-18 Exportar</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I315" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J315" s="3" t="inlineStr"/>
+      <c r="K315" s="3" t="inlineStr"/>
+      <c r="L315" s="3" t="inlineStr"/>
+      <c r="M315" s="7" t="inlineStr"/>
+      <c r="N315" s="7" t="inlineStr"/>
+      <c r="O315" s="8" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>Painel executivo do grupo econômico</t>
+        </is>
+      </c>
+      <c r="E316" s="4" t="inlineStr">
+        <is>
+          <t>Grupo ou empresa por competência: indicadores por tributo, alertas, tabela das empresas, saldo por mês, composição, mapa de etapas e funil das guias.</t>
+        </is>
+      </c>
+      <c r="F316" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-19 Painel executivo do grupo</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>Analítico</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I316" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="J316" s="3" t="inlineStr"/>
+      <c r="K316" s="3" t="inlineStr"/>
+      <c r="L316" s="3" t="inlineStr"/>
+      <c r="M316" s="7" t="inlineStr"/>
+      <c r="N316" s="7" t="inlineStr"/>
+      <c r="O316" s="8" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr">
+        <is>
+          <t>Auditoria das ações</t>
+        </is>
+      </c>
+      <c r="E317" s="4" t="inlineStr">
+        <is>
+          <t>Trilha encadeada por hash de tudo que muda o estado do módulo — tela, API e sistema —, com quem, antes e depois e motivo; filtros, integridade e CSV.</t>
+        </is>
+      </c>
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>PRD de PCONT · F-20 Auditoria das ações</t>
+        </is>
+      </c>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>Listagem</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="I317" s="10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J317" s="3" t="inlineStr"/>
+      <c r="K317" s="3" t="inlineStr"/>
+      <c r="L317" s="3" t="inlineStr"/>
+      <c r="M317" s="7" t="inlineStr"/>
+      <c r="N317" s="7" t="inlineStr"/>
+      <c r="O317" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O297"/>
+  <autoFilter ref="A1:O317"/>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
+    <dataValidation sqref="M2:M317" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use M0, M1, M2 ou Fora." promptTitle="Faixa revisada" prompt="Preencha apenas quando discordar da faixa proposta." type="list">
       <formula1>"M0,M1,M2,Fora"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
+    <dataValidation sqref="N2:N317" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Concorda com a faixa proposta?" prompt="Deixe em branco o que ainda não revisou." type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16218,6 +17238,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId261"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId282"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16229,7 +17269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16956,26 +17996,58 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Operacional</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>PCONT</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Entrou no app em 29/10/2026 (AV-PC). Seis no M0, pelo critério: a empresa do grupo, a competência, a visão consolidada, o demonstrativo contra o ente, o ciclo recalcular–fechar–reabrir — que era da tela da Apuração e continua contado lá também — e as divergências com chamado, porque crédito que o ente não reconhece é crédito que falhou e precisa virar tratável. A guia do saldo, o ERP, o histórico e a auditoria ficam em M1: pagar o próprio saldo é obrigação a partir de 2027, mas a cadeia do crédito fecha sem a guia sair daqui — ela pode sair do portal. Três em M2, que explicam em vez de garantir: a simulação de parcial, os encargos e o painel executivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C24" s="15" t="n">
-        <v>116</v>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>143</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="F24" s="15" t="n">
+      <c r="C25" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>154</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="F25" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="15" t="n">
-        <v>296</v>
+      <c r="G25" s="15" t="n">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -18261,7 +19333,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>v2.11</t>
+          <t>v2.12</t>
         </is>
       </c>
     </row>
@@ -18273,7 +19345,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
     </row>
@@ -18285,7 +19357,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Mapa de Funcionalidades v2.10</t>
+          <t>Mapa de Funcionalidades v2.11</t>
         </is>
       </c>
     </row>
@@ -18297,7 +19369,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>296 funcionalidades · 21 módulos · 286 do mapa + 10 novas</t>
+          <t>316 funcionalidades · 22 módulos · 306 do mapa + 10 novas</t>
         </is>
       </c>
     </row>
@@ -18309,7 +19381,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>116 · 143 · 35 · 2</t>
+          <t>122 · 154 · 38 · 2</t>
         </is>
       </c>
     </row>
